--- a/data/MetalliCan/pre_cleaned_data/land_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_df.xlsx
@@ -1,37 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_6C41C2EF917B0B309F2C4C6E45281C57787871F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{068AC7DB-DCA6-4AA2-B673-228364A7D470}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$131</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1238,8 +1216,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1302,21 +1280,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1354,7 +1324,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1388,7 +1358,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1423,10 +1392,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1599,24 +1567,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J131"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="81.6328125" customWidth="1"/>
-    <col min="9" max="9" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1648,7 +1603,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1671,10 +1626,10 @@
         <v>363</v>
       </c>
       <c r="J2">
-        <v>1499689.8654100001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1499689.86541</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1694,7 +1649,7 @@
         <v>1396088.878773147</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1714,10 +1669,10 @@
         <v>304</v>
       </c>
       <c r="J4">
-        <v>7967834.6375599997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>7967834.63756</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1737,10 +1692,10 @@
         <v>305</v>
       </c>
       <c r="J5">
-        <v>416736.86034155951</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>416736.8603415595</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1763,10 +1718,10 @@
         <v>364</v>
       </c>
       <c r="J6">
-        <v>13233210.388599999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>13233210.3886</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1792,7 +1747,7 @@
         <v>22527998.6785</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1815,10 +1770,10 @@
         <v>366</v>
       </c>
       <c r="J8">
-        <v>11531646.543500001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>11531646.5435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1835,10 +1790,10 @@
         <v>308</v>
       </c>
       <c r="J9">
-        <v>7682504.7611060319</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>7682504.761106032</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1864,7 +1819,7 @@
         <v>4950459.91493</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1881,10 +1836,10 @@
         <v>309</v>
       </c>
       <c r="J11">
-        <v>199723.49810779991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>199723.4981077999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1904,10 +1859,10 @@
         <v>310</v>
       </c>
       <c r="J12">
-        <v>63924259.804899998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>63924259.8049</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1924,10 +1879,10 @@
         <v>306</v>
       </c>
       <c r="J13">
-        <v>5776459.4296462554</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>5776459.429646255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1947,7 +1902,7 @@
         <v>1931027.417599746</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1973,7 +1928,7 @@
         <v>12606786.4826</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2002,7 +1957,7 @@
         <v>330003.3338055482</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2019,10 +1974,10 @@
         <v>313</v>
       </c>
       <c r="J17">
-        <v>5670439.7954879999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>5670439.795488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2042,10 +1997,10 @@
         <v>314</v>
       </c>
       <c r="J18">
-        <v>1058100.0927489479</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1058100.092748948</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2077,7 +2032,7 @@
         <v>363438.296974</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2106,10 +2061,10 @@
         <v>370</v>
       </c>
       <c r="J20">
-        <v>2410689.2217360381</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2410689.221736038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2129,10 +2084,10 @@
         <v>316</v>
       </c>
       <c r="J21">
-        <v>7481998.4830510933</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>7481998.483051093</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2152,7 +2107,7 @@
         <v>772974.2536339435</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2169,10 +2124,10 @@
         <v>317</v>
       </c>
       <c r="J23">
-        <v>255208.96920799999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>255208.969208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2189,10 +2144,10 @@
         <v>318</v>
       </c>
       <c r="J24">
-        <v>86936203.291251481</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>86936203.29125148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2215,10 +2170,10 @@
         <v>371</v>
       </c>
       <c r="J25">
-        <v>4789014.0375600001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>4789014.03756</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2241,7 +2196,7 @@
         <v>163254.62437129</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2261,10 +2216,10 @@
         <v>372</v>
       </c>
       <c r="J27">
-        <v>1152609.9603903999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1152609.9603904</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2284,10 +2239,10 @@
         <v>321</v>
       </c>
       <c r="J28">
-        <v>10572188.566137601</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>10572188.5661376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2307,10 +2262,10 @@
         <v>306</v>
       </c>
       <c r="J29">
-        <v>1510729.3693091241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1510729.369309124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2330,10 +2285,10 @@
         <v>313</v>
       </c>
       <c r="J30">
-        <v>681889.99643018574</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>681889.9964301857</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2353,10 +2308,10 @@
         <v>321</v>
       </c>
       <c r="J31">
-        <v>26104648.817951292</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>26104648.81795129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2382,10 +2337,10 @@
         <v>321</v>
       </c>
       <c r="J32">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2408,7 +2363,7 @@
         <v>4354811.166996506</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2431,10 +2386,10 @@
         <v>373</v>
       </c>
       <c r="J34">
-        <v>3064668.6931746709</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>3064668.693174671</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2454,10 +2409,10 @@
         <v>322</v>
       </c>
       <c r="J35">
-        <v>9992991.5686563142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>9992991.568656314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2483,7 +2438,7 @@
         <v>16826817.56129609</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2506,10 +2461,10 @@
         <v>373</v>
       </c>
       <c r="J37">
-        <v>126962.74509226839</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>126962.7450922684</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2526,10 +2481,10 @@
         <v>323</v>
       </c>
       <c r="J38">
-        <v>771997.92677291692</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>771997.9267729169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2546,10 +2501,10 @@
         <v>324</v>
       </c>
       <c r="J39">
-        <v>2695956.2107416778</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2695956.210741678</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2578,10 +2533,10 @@
         <v>375</v>
       </c>
       <c r="J40">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -2604,10 +2559,10 @@
         <v>373</v>
       </c>
       <c r="J41">
-        <v>22789723.436936211</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>22789723.43693621</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2630,10 +2585,10 @@
         <v>376</v>
       </c>
       <c r="J42">
-        <v>5804864.8944920022</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>5804864.894492002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2665,7 +2620,7 @@
         <v>1760913.595839669</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2694,10 +2649,10 @@
         <v>368</v>
       </c>
       <c r="J44">
-        <v>559241.26414497849</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>559241.2641449785</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2714,10 +2669,10 @@
         <v>328</v>
       </c>
       <c r="J45">
-        <v>2821612.2460802291</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2821612.246080229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -2734,10 +2689,10 @@
         <v>329</v>
       </c>
       <c r="J46">
-        <v>2460432.8206859031</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2460432.820685903</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2760,7 +2715,7 @@
         <v>3512631.992361845</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2780,7 +2735,7 @@
         <v>367462.345355</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -2806,10 +2761,10 @@
         <v>331</v>
       </c>
       <c r="J49">
-        <v>6838840.2467015907</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>6838840.246701591</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -2835,10 +2790,10 @@
         <v>332</v>
       </c>
       <c r="J50">
-        <v>2161806.0909095029</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2161806.090909503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -2858,7 +2813,7 @@
         <v>124954.6686331536</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -2881,10 +2836,10 @@
         <v>378</v>
       </c>
       <c r="J52">
-        <v>7405086.2285420913</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>7405086.228542091</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -2910,10 +2865,10 @@
         <v>332</v>
       </c>
       <c r="J53">
-        <v>1929968.1763706871</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1929968.176370687</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2945,7 +2900,7 @@
         <v>15428020.65126922</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -2962,10 +2917,10 @@
         <v>334</v>
       </c>
       <c r="J55">
-        <v>515060.95644264377</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>515060.9564426438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -2991,10 +2946,10 @@
         <v>335</v>
       </c>
       <c r="J56">
-        <v>3963061.6444813549</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>3963061.644481355</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -3011,10 +2966,10 @@
         <v>336</v>
       </c>
       <c r="J57">
-        <v>788132.08477646578</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>788132.0847764658</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -3040,10 +2995,10 @@
         <v>332</v>
       </c>
       <c r="J58">
-        <v>110803.86577744479</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>110803.8657774448</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -3066,10 +3021,10 @@
         <v>380</v>
       </c>
       <c r="J59">
-        <v>3503071.0617284952</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>3503071.061728495</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -3089,10 +3044,10 @@
         <v>337</v>
       </c>
       <c r="J60">
-        <v>989146.07241399994</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>989146.0724139999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -3118,7 +3073,7 @@
         <v>1874190.45757726</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -3141,10 +3096,10 @@
         <v>382</v>
       </c>
       <c r="J62">
-        <v>6139378.4953300003</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>6139378.49533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -3170,10 +3125,10 @@
         <v>305</v>
       </c>
       <c r="J63">
-        <v>1141145.8646362079</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1141145.864636208</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -3193,10 +3148,10 @@
         <v>325</v>
       </c>
       <c r="J64">
-        <v>240468.70558949231</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>240468.7055894923</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -3216,7 +3171,7 @@
         <v>242518.965983</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -3239,10 +3194,10 @@
         <v>383</v>
       </c>
       <c r="J66">
-        <v>8409093.1265900005</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>8409093.12659</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -3265,10 +3220,10 @@
         <v>384</v>
       </c>
       <c r="J67">
-        <v>10276967.100669291</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>10276967.10066929</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -3285,10 +3240,10 @@
         <v>340</v>
       </c>
       <c r="J68">
-        <v>386230.80603899999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>386230.806039</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>77</v>
       </c>
@@ -3311,10 +3266,10 @@
         <v>385</v>
       </c>
       <c r="J69">
-        <v>948677.90267675067</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>948677.9026767507</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -3337,10 +3292,10 @@
         <v>384</v>
       </c>
       <c r="J70">
-        <v>352884.57374953461</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>352884.5737495346</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -3366,10 +3321,10 @@
         <v>332</v>
       </c>
       <c r="J71">
-        <v>3063892.8050827952</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>3063892.805082795</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -3401,7 +3356,7 @@
         <v>1039802.195699128</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -3430,7 +3385,7 @@
         <v>21591249.4628</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -3459,10 +3414,10 @@
         <v>386</v>
       </c>
       <c r="J74">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -3485,10 +3440,10 @@
         <v>387</v>
       </c>
       <c r="J75">
-        <v>4202253.5385999996</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>4202253.5386</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -3514,10 +3469,10 @@
         <v>342</v>
       </c>
       <c r="J76">
-        <v>1788407.8192739999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1788407.819274</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -3543,7 +3498,7 @@
         <v>1550354.452950391</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
         <v>86</v>
       </c>
@@ -3569,7 +3524,7 @@
         <v>7249147.17667</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -3598,10 +3553,10 @@
         <v>388</v>
       </c>
       <c r="J79">
-        <v>24972920.132110279</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>24972920.13211028</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
         <v>88</v>
       </c>
@@ -3621,10 +3576,10 @@
         <v>321</v>
       </c>
       <c r="J80">
-        <v>15702687.604910919</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>15702687.60491092</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -3647,10 +3602,10 @@
         <v>343</v>
       </c>
       <c r="J81">
-        <v>346083.46304915362</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+        <v>346083.4630491536</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
         <v>90</v>
       </c>
@@ -3676,10 +3631,10 @@
         <v>344</v>
       </c>
       <c r="J82">
-        <v>1250800.9400651229</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1250800.940065123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
         <v>91</v>
       </c>
@@ -3705,7 +3660,7 @@
         <v>280723.3006520429</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -3731,10 +3686,10 @@
         <v>345</v>
       </c>
       <c r="J84">
-        <v>6630997.3292599991</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>6630997.329259999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -3763,7 +3718,7 @@
         <v>3714363.081590083</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -3780,10 +3735,10 @@
         <v>346</v>
       </c>
       <c r="J86">
-        <v>1267949.1779535899</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1267949.17795359</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" t="s">
         <v>95</v>
       </c>
@@ -3800,10 +3755,10 @@
         <v>347</v>
       </c>
       <c r="J87">
-        <v>848008.50587400002</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>848008.505874</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" t="s">
         <v>96</v>
       </c>
@@ -3823,7 +3778,7 @@
         <v>148601.7043568496</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -3846,10 +3801,10 @@
         <v>366</v>
       </c>
       <c r="J89">
-        <v>1445491.9253398541</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1445491.925339854</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
         <v>98</v>
       </c>
@@ -3875,10 +3830,10 @@
         <v>344</v>
       </c>
       <c r="J90">
-        <v>741138.95960838371</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+        <v>741138.9596083837</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -3907,7 +3862,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10">
       <c r="A92" t="s">
         <v>100</v>
       </c>
@@ -3924,10 +3879,10 @@
         <v>350</v>
       </c>
       <c r="J92">
-        <v>899806.32550548273</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>899806.3255054827</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
         <v>101</v>
       </c>
@@ -3950,10 +3905,10 @@
         <v>390</v>
       </c>
       <c r="J93">
-        <v>3436361.1128654238</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>3436361.112865424</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
         <v>102</v>
       </c>
@@ -3976,10 +3931,10 @@
         <v>388</v>
       </c>
       <c r="J94">
-        <v>2323252.9267690452</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2323252.926769045</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" t="s">
         <v>103</v>
       </c>
@@ -4002,10 +3957,10 @@
         <v>391</v>
       </c>
       <c r="J95">
-        <v>2475749.7725005322</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2475749.772500532</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -4022,10 +3977,10 @@
         <v>304</v>
       </c>
       <c r="J96">
-        <v>9487628.0863300003</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>9487628.08633</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -4042,10 +3997,10 @@
         <v>353</v>
       </c>
       <c r="J97">
-        <v>333307.12371929188</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>333307.1237192919</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" t="s">
         <v>106</v>
       </c>
@@ -4068,10 +4023,10 @@
         <v>392</v>
       </c>
       <c r="J98">
-        <v>6202897.0171400001</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>6202897.01714</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -4097,7 +4052,7 @@
         <v>1341835.17078</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -4120,10 +4075,10 @@
         <v>394</v>
       </c>
       <c r="J100">
-        <v>1113516.5997299999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1113516.59973</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" t="s">
         <v>109</v>
       </c>
@@ -4143,10 +4098,10 @@
         <v>343</v>
       </c>
       <c r="J101">
-        <v>2689687.0630099322</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2689687.063009932</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" t="s">
         <v>110</v>
       </c>
@@ -4166,10 +4121,10 @@
         <v>354</v>
       </c>
       <c r="J102">
-        <v>1248584.6715172599</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1248584.67151726</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" t="s">
         <v>111</v>
       </c>
@@ -4192,10 +4147,10 @@
         <v>395</v>
       </c>
       <c r="J103">
-        <v>5574423.9812850002</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>5574423.981285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
       <c r="A104" t="s">
         <v>112</v>
       </c>
@@ -4218,10 +4173,10 @@
         <v>396</v>
       </c>
       <c r="J104">
-        <v>19028718.451565798</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>19028718.4515658</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105" t="s">
         <v>113</v>
       </c>
@@ -4250,10 +4205,10 @@
         <v>397</v>
       </c>
       <c r="J105">
-        <v>2331098.7137656999</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2331098.7137657</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -4270,10 +4225,10 @@
         <v>311</v>
       </c>
       <c r="J106">
-        <v>6417855.9021505257</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>6417855.902150526</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107" t="s">
         <v>115</v>
       </c>
@@ -4296,7 +4251,7 @@
         <v>11904079.93924279</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10">
       <c r="A108" t="s">
         <v>116</v>
       </c>
@@ -4322,10 +4277,10 @@
         <v>305</v>
       </c>
       <c r="J108">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
       <c r="A109" t="s">
         <v>117</v>
       </c>
@@ -4345,7 +4300,7 @@
         <v>189687.8885015327</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10">
       <c r="A110" t="s">
         <v>118</v>
       </c>
@@ -4365,10 +4320,10 @@
         <v>357</v>
       </c>
       <c r="J110">
-        <v>4412887.4395813216</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>4412887.439581322</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
       <c r="A111" t="s">
         <v>119</v>
       </c>
@@ -4385,10 +4340,10 @@
         <v>358</v>
       </c>
       <c r="J111">
-        <v>708761.41470578162</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>708761.4147057816</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
       <c r="A112" t="s">
         <v>120</v>
       </c>
@@ -4414,7 +4369,7 @@
         <v>1600590.119251437</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
         <v>121</v>
       </c>
@@ -4431,10 +4386,10 @@
         <v>357</v>
       </c>
       <c r="J113">
-        <v>4345046.9537415411</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>4345046.953741541</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
         <v>122</v>
       </c>
@@ -4463,7 +4418,7 @@
         <v>10235647.18904726</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>123</v>
       </c>
@@ -4489,10 +4444,10 @@
         <v>357</v>
       </c>
       <c r="J115">
-        <v>1973892.4554655049</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1973892.455465505</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>124</v>
       </c>
@@ -4515,7 +4470,7 @@
         <v>5293594.021862885</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>125</v>
       </c>
@@ -4538,7 +4493,7 @@
         <v>3418676.16080696</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10">
       <c r="B118" t="s">
         <v>128</v>
       </c>
@@ -4558,10 +4513,10 @@
         <v>375</v>
       </c>
       <c r="J118">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="B119" t="s">
         <v>131</v>
       </c>
@@ -4581,10 +4536,10 @@
         <v>379</v>
       </c>
       <c r="J119">
-        <v>16569166.515905419</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>16569166.51590542</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
       <c r="B120" t="s">
         <v>133</v>
       </c>
@@ -4604,10 +4559,10 @@
         <v>388</v>
       </c>
       <c r="J120">
-        <v>28687283.213700362</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>28687283.21370036</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="B121" t="s">
         <v>132</v>
       </c>
@@ -4627,10 +4582,10 @@
         <v>386</v>
       </c>
       <c r="J121">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="B122" t="s">
         <v>138</v>
       </c>
@@ -4647,10 +4602,10 @@
         <v>305</v>
       </c>
       <c r="J122">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
       <c r="B123" t="s">
         <v>139</v>
       </c>
@@ -4667,10 +4622,10 @@
         <v>357</v>
       </c>
       <c r="J123">
-        <v>12209539.644512771</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>12209539.64451277</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="B124" t="s">
         <v>134</v>
       </c>
@@ -4690,10 +4645,10 @@
         <v>397</v>
       </c>
       <c r="J124">
-        <v>2677182.1768148541</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>2677182.176814854</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
       <c r="B125" t="s">
         <v>127</v>
       </c>
@@ -4710,10 +4665,10 @@
         <v>321</v>
       </c>
       <c r="J125">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
       <c r="B126" t="s">
         <v>137</v>
       </c>
@@ -4733,7 +4688,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10">
       <c r="B127" t="s">
         <v>135</v>
       </c>
@@ -4750,10 +4705,10 @@
         <v>344</v>
       </c>
       <c r="J127">
-        <v>1991939.8996735071</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>1991939.899673507</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
       <c r="B128" t="s">
         <v>126</v>
       </c>
@@ -4773,10 +4728,10 @@
         <v>398</v>
       </c>
       <c r="J128">
-        <v>3104130.8525155862</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.35">
+        <v>3104130.852515586</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10">
       <c r="B129" t="s">
         <v>136</v>
       </c>
@@ -4793,10 +4748,10 @@
         <v>345</v>
       </c>
       <c r="J129">
-        <v>6630997.3292599991</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>6630997.329259999</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10">
       <c r="B130" t="s">
         <v>130</v>
       </c>
@@ -4816,10 +4771,10 @@
         <v>368</v>
       </c>
       <c r="J130">
-        <v>33380023.309566759</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>33380023.30956676</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10">
       <c r="B131" t="s">
         <v>129</v>
       </c>
@@ -4839,17 +4794,10 @@
         <v>377</v>
       </c>
       <c r="J131">
-        <v>11427963.857514391</v>
+        <v>11427963.85751439</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J131" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="manufacturing"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/land_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_df.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_6C41C2EF917B0B309F2C4CA6DDE83F0D797871F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D573C790-D562-4DAB-AB28-2BBDA67A6334}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1216,8 +1225,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1280,13 +1289,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1324,7 +1341,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1358,6 +1375,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1392,9 +1410,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1567,11 +1586,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J131"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="45.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="220.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1603,7 +1634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1626,10 +1657,10 @@
         <v>363</v>
       </c>
       <c r="J2">
-        <v>1499689.86541</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>1499689.8654100001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1649,7 +1680,7 @@
         <v>1396088.878773147</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1669,10 +1700,10 @@
         <v>304</v>
       </c>
       <c r="J4">
-        <v>7967834.63756</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>7967834.6375599997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1692,10 +1723,10 @@
         <v>305</v>
       </c>
       <c r="J5">
-        <v>416736.8603415595</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>416736.86034155951</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1718,10 +1749,10 @@
         <v>364</v>
       </c>
       <c r="J6">
-        <v>13233210.3886</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>13233210.388599999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1747,7 +1778,7 @@
         <v>22527998.6785</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1770,10 +1801,10 @@
         <v>366</v>
       </c>
       <c r="J8">
-        <v>11531646.5435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>11531646.543500001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1790,10 +1821,10 @@
         <v>308</v>
       </c>
       <c r="J9">
-        <v>7682504.761106032</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>7682504.7611060319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1819,7 +1850,7 @@
         <v>4950459.91493</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1836,10 +1867,10 @@
         <v>309</v>
       </c>
       <c r="J11">
-        <v>199723.4981077999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>199723.49810779991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1859,10 +1890,10 @@
         <v>310</v>
       </c>
       <c r="J12">
-        <v>63924259.8049</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>63924259.804899998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1879,10 +1910,10 @@
         <v>306</v>
       </c>
       <c r="J13">
-        <v>5776459.429646255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>5776459.4296462554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1902,7 +1933,7 @@
         <v>1931027.417599746</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1928,7 +1959,7 @@
         <v>12606786.4826</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1957,7 +1988,7 @@
         <v>330003.3338055482</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1974,10 +2005,10 @@
         <v>313</v>
       </c>
       <c r="J17">
-        <v>5670439.795488</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>5670439.7954879999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1997,10 +2028,10 @@
         <v>314</v>
       </c>
       <c r="J18">
-        <v>1058100.092748948</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>1058100.0927489479</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2032,7 +2063,7 @@
         <v>363438.296974</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2061,10 +2092,10 @@
         <v>370</v>
       </c>
       <c r="J20">
-        <v>2410689.221736038</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>2410689.2217360381</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2084,10 +2115,10 @@
         <v>316</v>
       </c>
       <c r="J21">
-        <v>7481998.483051093</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>7481998.4830510933</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2107,7 +2138,7 @@
         <v>772974.2536339435</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2124,10 +2155,10 @@
         <v>317</v>
       </c>
       <c r="J23">
-        <v>255208.969208</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>255208.96920799999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2144,10 +2175,10 @@
         <v>318</v>
       </c>
       <c r="J24">
-        <v>86936203.29125148</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>86936203.291251481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2170,10 +2201,10 @@
         <v>371</v>
       </c>
       <c r="J25">
-        <v>4789014.03756</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>4789014.0375600001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2196,7 +2227,7 @@
         <v>163254.62437129</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2216,10 +2247,10 @@
         <v>372</v>
       </c>
       <c r="J27">
-        <v>1152609.9603904</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>1152609.9603903999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2239,10 +2270,10 @@
         <v>321</v>
       </c>
       <c r="J28">
-        <v>10572188.5661376</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>10572188.566137601</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2262,10 +2293,10 @@
         <v>306</v>
       </c>
       <c r="J29">
-        <v>1510729.369309124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>1510729.3693091241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2285,10 +2316,10 @@
         <v>313</v>
       </c>
       <c r="J30">
-        <v>681889.9964301857</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>681889.99643018574</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2308,10 +2339,10 @@
         <v>321</v>
       </c>
       <c r="J31">
-        <v>26104648.81795129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>26104648.817951292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2337,10 +2368,10 @@
         <v>321</v>
       </c>
       <c r="J32">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2363,7 +2394,7 @@
         <v>4354811.166996506</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2386,10 +2417,10 @@
         <v>373</v>
       </c>
       <c r="J34">
-        <v>3064668.693174671</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>3064668.6931746709</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2409,10 +2440,10 @@
         <v>322</v>
       </c>
       <c r="J35">
-        <v>9992991.568656314</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>9992991.5686563142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2438,7 +2469,7 @@
         <v>16826817.56129609</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2461,10 +2492,10 @@
         <v>373</v>
       </c>
       <c r="J37">
-        <v>126962.7450922684</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>126962.74509226839</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2481,10 +2512,10 @@
         <v>323</v>
       </c>
       <c r="J38">
-        <v>771997.9267729169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>771997.92677291692</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2501,10 +2532,10 @@
         <v>324</v>
       </c>
       <c r="J39">
-        <v>2695956.210741678</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>2695956.2107416778</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2533,10 +2564,10 @@
         <v>375</v>
       </c>
       <c r="J40">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -2559,10 +2590,10 @@
         <v>373</v>
       </c>
       <c r="J41">
-        <v>22789723.43693621</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>22789723.436936211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2585,10 +2616,10 @@
         <v>376</v>
       </c>
       <c r="J42">
-        <v>5804864.894492002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>5804864.8944920022</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2620,7 +2651,7 @@
         <v>1760913.595839669</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2649,10 +2680,10 @@
         <v>368</v>
       </c>
       <c r="J44">
-        <v>559241.2641449785</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>559241.26414497849</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2669,10 +2700,10 @@
         <v>328</v>
       </c>
       <c r="J45">
-        <v>2821612.246080229</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>2821612.2460802291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -2689,10 +2720,10 @@
         <v>329</v>
       </c>
       <c r="J46">
-        <v>2460432.820685903</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>2460432.8206859031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2715,7 +2746,7 @@
         <v>3512631.992361845</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2735,7 +2766,7 @@
         <v>367462.345355</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -2761,10 +2792,10 @@
         <v>331</v>
       </c>
       <c r="J49">
-        <v>6838840.246701591</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>6838840.2467015907</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -2790,10 +2821,10 @@
         <v>332</v>
       </c>
       <c r="J50">
-        <v>2161806.090909503</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>2161806.0909095029</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -2813,7 +2844,7 @@
         <v>124954.6686331536</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -2836,10 +2867,10 @@
         <v>378</v>
       </c>
       <c r="J52">
-        <v>7405086.228542091</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>7405086.2285420913</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -2865,10 +2896,10 @@
         <v>332</v>
       </c>
       <c r="J53">
-        <v>1929968.176370687</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>1929968.1763706871</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2900,7 +2931,7 @@
         <v>15428020.65126922</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -2917,10 +2948,10 @@
         <v>334</v>
       </c>
       <c r="J55">
-        <v>515060.9564426438</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>515060.95644264377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -2946,10 +2977,10 @@
         <v>335</v>
       </c>
       <c r="J56">
-        <v>3963061.644481355</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>3963061.6444813549</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -2966,10 +2997,10 @@
         <v>336</v>
       </c>
       <c r="J57">
-        <v>788132.0847764658</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>788132.08477646578</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -2995,10 +3026,10 @@
         <v>332</v>
       </c>
       <c r="J58">
-        <v>110803.8657774448</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>110803.86577744479</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -3021,10 +3052,10 @@
         <v>380</v>
       </c>
       <c r="J59">
-        <v>3503071.061728495</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>3503071.0617284952</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -3044,10 +3075,10 @@
         <v>337</v>
       </c>
       <c r="J60">
-        <v>989146.0724139999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+        <v>989146.07241399994</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -3073,7 +3104,7 @@
         <v>1874190.45757726</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -3096,10 +3127,10 @@
         <v>382</v>
       </c>
       <c r="J62">
-        <v>6139378.49533</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>6139378.4953300003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -3125,10 +3156,10 @@
         <v>305</v>
       </c>
       <c r="J63">
-        <v>1141145.864636208</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>1141145.8646362079</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -3148,10 +3179,10 @@
         <v>325</v>
       </c>
       <c r="J64">
-        <v>240468.7055894923</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>240468.70558949231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -3171,7 +3202,7 @@
         <v>242518.965983</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -3194,10 +3225,10 @@
         <v>383</v>
       </c>
       <c r="J66">
-        <v>8409093.12659</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+        <v>8409093.1265900005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -3220,10 +3251,10 @@
         <v>384</v>
       </c>
       <c r="J67">
-        <v>10276967.10066929</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+        <v>10276967.100669291</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -3240,10 +3271,10 @@
         <v>340</v>
       </c>
       <c r="J68">
-        <v>386230.806039</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>386230.80603899999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>77</v>
       </c>
@@ -3266,10 +3297,10 @@
         <v>385</v>
       </c>
       <c r="J69">
-        <v>948677.9026767507</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>948677.90267675067</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -3292,10 +3323,10 @@
         <v>384</v>
       </c>
       <c r="J70">
-        <v>352884.5737495346</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>352884.57374953461</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -3321,10 +3352,10 @@
         <v>332</v>
       </c>
       <c r="J71">
-        <v>3063892.805082795</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>3063892.8050827952</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -3356,7 +3387,7 @@
         <v>1039802.195699128</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -3385,7 +3416,7 @@
         <v>21591249.4628</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -3414,10 +3445,10 @@
         <v>386</v>
       </c>
       <c r="J74">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -3440,10 +3471,10 @@
         <v>387</v>
       </c>
       <c r="J75">
-        <v>4202253.5386</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>4202253.5385999996</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -3469,10 +3500,10 @@
         <v>342</v>
       </c>
       <c r="J76">
-        <v>1788407.819274</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>1788407.8192739999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -3498,7 +3529,7 @@
         <v>1550354.452950391</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>86</v>
       </c>
@@ -3524,7 +3555,7 @@
         <v>7249147.17667</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -3553,10 +3584,10 @@
         <v>388</v>
       </c>
       <c r="J79">
-        <v>24972920.13211028</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>24972920.132110279</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>88</v>
       </c>
@@ -3576,10 +3607,10 @@
         <v>321</v>
       </c>
       <c r="J80">
-        <v>15702687.60491092</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>15702687.604910919</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -3602,10 +3633,10 @@
         <v>343</v>
       </c>
       <c r="J81">
-        <v>346083.4630491536</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+        <v>346083.46304915362</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>90</v>
       </c>
@@ -3631,10 +3662,10 @@
         <v>344</v>
       </c>
       <c r="J82">
-        <v>1250800.940065123</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+        <v>1250800.9400651229</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>91</v>
       </c>
@@ -3660,7 +3691,7 @@
         <v>280723.3006520429</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -3686,10 +3717,10 @@
         <v>345</v>
       </c>
       <c r="J84">
-        <v>6630997.329259999</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>6630997.3292599991</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -3718,7 +3749,7 @@
         <v>3714363.081590083</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -3735,10 +3766,10 @@
         <v>346</v>
       </c>
       <c r="J86">
-        <v>1267949.17795359</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>1267949.1779535899</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>95</v>
       </c>
@@ -3755,10 +3786,10 @@
         <v>347</v>
       </c>
       <c r="J87">
-        <v>848008.505874</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>848008.50587400002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>96</v>
       </c>
@@ -3778,7 +3809,7 @@
         <v>148601.7043568496</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -3801,10 +3832,10 @@
         <v>366</v>
       </c>
       <c r="J89">
-        <v>1445491.925339854</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+        <v>1445491.9253398541</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>98</v>
       </c>
@@ -3830,10 +3861,10 @@
         <v>344</v>
       </c>
       <c r="J90">
-        <v>741138.9596083837</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>741138.95960838371</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -3862,7 +3893,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>100</v>
       </c>
@@ -3879,10 +3910,10 @@
         <v>350</v>
       </c>
       <c r="J92">
-        <v>899806.3255054827</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>899806.32550548273</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>101</v>
       </c>
@@ -3905,10 +3936,10 @@
         <v>390</v>
       </c>
       <c r="J93">
-        <v>3436361.112865424</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
+        <v>3436361.1128654238</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>102</v>
       </c>
@@ -3931,10 +3962,10 @@
         <v>388</v>
       </c>
       <c r="J94">
-        <v>2323252.926769045</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>2323252.9267690452</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>103</v>
       </c>
@@ -3957,10 +3988,10 @@
         <v>391</v>
       </c>
       <c r="J95">
-        <v>2475749.772500532</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+        <v>2475749.7725005322</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -3977,10 +4008,10 @@
         <v>304</v>
       </c>
       <c r="J96">
-        <v>9487628.08633</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>9487628.0863300003</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -3997,10 +4028,10 @@
         <v>353</v>
       </c>
       <c r="J97">
-        <v>333307.1237192919</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+        <v>333307.12371929188</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>106</v>
       </c>
@@ -4023,10 +4054,10 @@
         <v>392</v>
       </c>
       <c r="J98">
-        <v>6202897.01714</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
+        <v>6202897.0171400001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -4052,7 +4083,7 @@
         <v>1341835.17078</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -4075,10 +4106,10 @@
         <v>394</v>
       </c>
       <c r="J100">
-        <v>1113516.59973</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>1113516.5997299999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>109</v>
       </c>
@@ -4098,10 +4129,10 @@
         <v>343</v>
       </c>
       <c r="J101">
-        <v>2689687.063009932</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+        <v>2689687.0630099322</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>110</v>
       </c>
@@ -4121,10 +4152,10 @@
         <v>354</v>
       </c>
       <c r="J102">
-        <v>1248584.67151726</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>1248584.6715172599</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>111</v>
       </c>
@@ -4147,10 +4178,10 @@
         <v>395</v>
       </c>
       <c r="J103">
-        <v>5574423.981285</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
+        <v>5574423.9812850002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>112</v>
       </c>
@@ -4173,10 +4204,10 @@
         <v>396</v>
       </c>
       <c r="J104">
-        <v>19028718.4515658</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
+        <v>19028718.451565798</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>113</v>
       </c>
@@ -4205,10 +4236,10 @@
         <v>397</v>
       </c>
       <c r="J105">
-        <v>2331098.7137657</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
+        <v>2331098.7137656999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -4225,10 +4256,10 @@
         <v>311</v>
       </c>
       <c r="J106">
-        <v>6417855.902150526</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
+        <v>6417855.9021505257</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>115</v>
       </c>
@@ -4251,7 +4282,7 @@
         <v>11904079.93924279</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>116</v>
       </c>
@@ -4277,10 +4308,10 @@
         <v>305</v>
       </c>
       <c r="J108">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>117</v>
       </c>
@@ -4300,7 +4331,7 @@
         <v>189687.8885015327</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>118</v>
       </c>
@@ -4320,10 +4351,10 @@
         <v>357</v>
       </c>
       <c r="J110">
-        <v>4412887.439581322</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
+        <v>4412887.4395813216</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>119</v>
       </c>
@@ -4340,10 +4371,10 @@
         <v>358</v>
       </c>
       <c r="J111">
-        <v>708761.4147057816</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
+        <v>708761.41470578162</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>120</v>
       </c>
@@ -4369,7 +4400,7 @@
         <v>1600590.119251437</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>121</v>
       </c>
@@ -4386,10 +4417,10 @@
         <v>357</v>
       </c>
       <c r="J113">
-        <v>4345046.953741541</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
+        <v>4345046.9537415411</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>122</v>
       </c>
@@ -4418,7 +4449,7 @@
         <v>10235647.18904726</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>123</v>
       </c>
@@ -4444,10 +4475,10 @@
         <v>357</v>
       </c>
       <c r="J115">
-        <v>1973892.455465505</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
+        <v>1973892.4554655049</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>124</v>
       </c>
@@ -4470,7 +4501,7 @@
         <v>5293594.021862885</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>125</v>
       </c>
@@ -4493,7 +4524,7 @@
         <v>3418676.16080696</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>128</v>
       </c>
@@ -4513,10 +4544,10 @@
         <v>375</v>
       </c>
       <c r="J118">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>131</v>
       </c>
@@ -4536,10 +4567,10 @@
         <v>379</v>
       </c>
       <c r="J119">
-        <v>16569166.51590542</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
+        <v>16569166.515905419</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>133</v>
       </c>
@@ -4559,10 +4590,10 @@
         <v>388</v>
       </c>
       <c r="J120">
-        <v>28687283.21370036</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
+        <v>28687283.213700362</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>132</v>
       </c>
@@ -4582,10 +4613,10 @@
         <v>386</v>
       </c>
       <c r="J121">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>138</v>
       </c>
@@ -4602,10 +4633,10 @@
         <v>305</v>
       </c>
       <c r="J122">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>139</v>
       </c>
@@ -4622,10 +4653,10 @@
         <v>357</v>
       </c>
       <c r="J123">
-        <v>12209539.64451277</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>12209539.644512771</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>134</v>
       </c>
@@ -4645,10 +4676,10 @@
         <v>397</v>
       </c>
       <c r="J124">
-        <v>2677182.176814854</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
+        <v>2677182.1768148541</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>127</v>
       </c>
@@ -4665,10 +4696,10 @@
         <v>321</v>
       </c>
       <c r="J125">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>137</v>
       </c>
@@ -4688,7 +4719,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>135</v>
       </c>
@@ -4705,10 +4736,10 @@
         <v>344</v>
       </c>
       <c r="J127">
-        <v>1991939.899673507</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
+        <v>1991939.8996735071</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>126</v>
       </c>
@@ -4728,10 +4759,10 @@
         <v>398</v>
       </c>
       <c r="J128">
-        <v>3104130.852515586</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10">
+        <v>3104130.8525155862</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>136</v>
       </c>
@@ -4748,10 +4779,10 @@
         <v>345</v>
       </c>
       <c r="J129">
-        <v>6630997.329259999</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10">
+        <v>6630997.3292599991</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>130</v>
       </c>
@@ -4771,10 +4802,10 @@
         <v>368</v>
       </c>
       <c r="J130">
-        <v>33380023.30956676</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10">
+        <v>33380023.309566759</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>129</v>
       </c>
@@ -4794,10 +4825,11 @@
         <v>377</v>
       </c>
       <c r="J131">
-        <v>11427963.85751439</v>
+        <v>11427963.857514391</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/land_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_df.xlsx
@@ -1,29 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_6C41C2EF917B0B309F2C4CA6DDE83F0D797871F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D573C790-D562-4DAB-AB28-2BBDA67A6334}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="401">
   <si>
     <t>main_id</t>
   </si>
@@ -442,6 +433,9 @@
     <t>GRP-14bfbb82</t>
   </si>
   <si>
+    <t>GRP-91aaa60b</t>
+  </si>
+  <si>
     <t>GRP-21eee27d</t>
   </si>
   <si>
@@ -827,6 +821,9 @@
   </si>
   <si>
     <t>Seabee Gold Operation</t>
+  </si>
+  <si>
+    <t>Cigar Lake + McClean Lake</t>
   </si>
   <si>
     <t>Key Lake + McArthur River</t>
@@ -1225,8 +1222,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1289,21 +1286,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1341,7 +1330,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1375,7 +1364,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1410,10 +1398,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1586,23 +1573,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J131"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="45.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="220.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J132"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1634,332 +1609,332 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J2">
-        <v>1499689.8654100001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1499689.86541</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J3">
         <v>1396088.878773147</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J4">
-        <v>7967834.6375599997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7967834.63756</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J5">
-        <v>416736.86034155951</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>416736.8603415595</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J6">
-        <v>13233210.388599999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>13233210.3886</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="I7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="J7">
         <v>22527998.6785</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G8" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I8" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J8">
-        <v>11531646.543500001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>11531646.5435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J9">
-        <v>7682504.7611060319</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7682504.761106032</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="I10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J10">
         <v>4950459.91493</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J11">
-        <v>199723.49810779991</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>199723.4981077999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F12" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H12" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J12">
-        <v>63924259.804899998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+        <v>63924259.8049</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F13" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H13" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J13">
-        <v>5776459.4296462554</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>5776459.429646255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H14" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J14">
         <v>1931027.417599746</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H15" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I15" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J15">
         <v>12606786.4826</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1967,71 +1942,71 @@
         <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D16" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E16" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G16" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H16" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J16">
         <v>330003.3338055482</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H17" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J17">
-        <v>5670439.7954879999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>5670439.795488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G18" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H18" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J18">
-        <v>1058100.0927489479</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1058100.092748948</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2039,31 +2014,31 @@
         <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I19" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J19">
         <v>363438.296974</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2071,278 +2046,278 @@
         <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D20" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E20" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F20" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G20" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H20" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="I20" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J20">
-        <v>2410689.2217360381</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2410689.221736038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G21" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H21" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J21">
-        <v>7481998.4830510933</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7481998.483051093</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H22" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J22">
         <v>772974.2536339435</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E23" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H23" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J23">
-        <v>255208.96920799999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>255208.969208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F24" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H24" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J24">
-        <v>86936203.291251481</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+        <v>86936203.29125148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F25" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H25" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I25" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="J25">
-        <v>4789014.0375600001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+        <v>4789014.03756</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E26" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F26" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H26" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J26">
         <v>163254.62437129</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E27" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F27" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I27" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J27">
-        <v>1152609.9603903999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1152609.9603904</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E28" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F28" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H28" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J28">
-        <v>10572188.566137601</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>10572188.5661376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E29" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F29" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G29" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H29" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J29">
-        <v>1510729.3693091241</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1510729.369309124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E30" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F30" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G30" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H30" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J30">
-        <v>681889.99643018574</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>681889.9964301857</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E31" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F31" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H31" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J31">
-        <v>26104648.817951292</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+        <v>26104648.81795129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2350,192 +2325,192 @@
         <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E32" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F32" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G32" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H32" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J32">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
       <c r="C33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F33" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G33" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H33" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J33">
         <v>4354811.166996506</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E34" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F34" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G34" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H34" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I34" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J34">
-        <v>3064668.6931746709</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3064668.693174671</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F35" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G35" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H35" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J35">
-        <v>9992991.5686563142</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+        <v>9992991.568656314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F36" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G36" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H36" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I36" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J36">
         <v>16826817.56129609</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
       <c r="C37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E37" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F37" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G37" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H37" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J37">
-        <v>126962.74509226839</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
+        <v>126962.7450922684</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H38" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J38">
-        <v>771997.92677291692</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
+        <v>771997.9267729169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>47</v>
       </c>
       <c r="C39" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E39" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F39" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J39">
-        <v>2695956.2107416778</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2695956.210741678</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2543,83 +2518,83 @@
         <v>128</v>
       </c>
       <c r="C40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D40" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E40" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F40" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G40" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H40" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I40" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J40">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>49</v>
       </c>
       <c r="C41" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E41" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F41" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G41" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H41" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I41" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="J41">
-        <v>22789723.436936211</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
+        <v>22789723.43693621</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E42" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F42" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G42" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H42" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I42" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J42">
-        <v>5804864.8944920022</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+        <v>5804864.894492002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2627,31 +2602,31 @@
         <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D43" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E43" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F43" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G43" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H43" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="I43" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J43">
         <v>1760913.595839669</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2659,114 +2634,114 @@
         <v>130</v>
       </c>
       <c r="C44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D44" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E44" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F44" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G44" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H44" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I44" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J44">
-        <v>559241.26414497849</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+        <v>559241.2641449785</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
         <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F45" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H45" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J45">
-        <v>2821612.2460802291</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2821612.246080229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
         <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F46" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H46" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J46">
-        <v>2460432.8206859031</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2460432.820685903</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
         <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F47" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G47" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H47" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J47">
         <v>3512631.992361845</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
         <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F48" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H48" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J48">
         <v>367462.345355</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -2774,28 +2749,28 @@
         <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E49" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F49" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G49" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="H49" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J49">
-        <v>6838840.2467015907</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+        <v>6838840.246701591</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -2803,74 +2778,74 @@
         <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E50" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F50" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G50" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H50" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J50">
-        <v>2161806.0909095029</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2161806.090909503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
         <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F51" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H51" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J51">
         <v>124954.6686331536</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
         <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E52" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F52" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G52" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H52" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I52" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J52">
-        <v>7405086.2285420913</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7405086.228542091</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -2878,28 +2853,28 @@
         <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D53" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E53" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F53" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G53" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H53" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J53">
-        <v>1929968.1763706871</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1929968.176370687</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2907,51 +2882,51 @@
         <v>131</v>
       </c>
       <c r="C54" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D54" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E54" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F54" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G54" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H54" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I54" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J54">
         <v>15428020.65126922</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10">
       <c r="A55" t="s">
         <v>63</v>
       </c>
       <c r="C55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E55" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F55" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H55" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J55">
-        <v>515060.95644264377</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>515060.9564426438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -2959,48 +2934,48 @@
         <v>130</v>
       </c>
       <c r="C56" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D56" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E56" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F56" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G56" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H56" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J56">
-        <v>3963061.6444813549</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3963061.644481355</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>65</v>
       </c>
       <c r="C57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E57" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F57" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H57" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J57">
-        <v>788132.08477646578</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+        <v>788132.0847764658</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -3008,129 +2983,129 @@
         <v>130</v>
       </c>
       <c r="C58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D58" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E58" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F58" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G58" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H58" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J58">
-        <v>110803.86577744479</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+        <v>110803.8657774448</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" t="s">
         <v>67</v>
       </c>
       <c r="C59" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E59" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F59" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G59" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H59" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I59" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J59">
-        <v>3503071.0617284952</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3503071.061728495</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60" t="s">
         <v>68</v>
       </c>
       <c r="C60" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E60" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F60" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G60" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H60" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J60">
-        <v>989146.07241399994</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
+        <v>989146.0724139999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
         <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E61" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G61" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H61" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I61" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J61">
         <v>1874190.45757726</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
         <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E62" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F62" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G62" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I62" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J62">
-        <v>6139378.4953300003</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+        <v>6139378.49533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -3138,195 +3113,195 @@
         <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D63" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E63" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F63" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G63" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H63" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J63">
-        <v>1141145.8646362079</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1141145.864636208</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" t="s">
         <v>72</v>
       </c>
       <c r="C64" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E64" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F64" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G64" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H64" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J64">
-        <v>240468.70558949231</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+        <v>240468.7055894923</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" t="s">
         <v>73</v>
       </c>
       <c r="C65" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E65" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F65" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H65" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J65">
         <v>242518.965983</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
         <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E66" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F66" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G66" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H66" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I66" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J66">
-        <v>8409093.1265900005</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+        <v>8409093.12659</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
         <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E67" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F67" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G67" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H67" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I67" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J67">
-        <v>10276967.100669291</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
+        <v>10276967.10066929</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" t="s">
         <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E68" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F68" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H68" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J68">
-        <v>386230.80603899999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
+        <v>386230.806039</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" t="s">
         <v>77</v>
       </c>
       <c r="C69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E69" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F69" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G69" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H69" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I69" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J69">
-        <v>948677.90267675067</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
+        <v>948677.9026767507</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
         <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E70" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F70" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G70" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H70" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I70" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J70">
-        <v>352884.57374953461</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+        <v>352884.5737495346</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -3334,28 +3309,28 @@
         <v>130</v>
       </c>
       <c r="C71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E71" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F71" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H71" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J71">
-        <v>3063892.8050827952</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3063892.805082795</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -3363,31 +3338,31 @@
         <v>129</v>
       </c>
       <c r="C72" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D72" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E72" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F72" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G72" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H72" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I72" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J72">
         <v>1039802.195699128</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -3395,28 +3370,28 @@
         <v>130</v>
       </c>
       <c r="C73" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D73" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E73" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F73" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G73" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H73" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J73">
         <v>21591249.4628</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -3424,57 +3399,57 @@
         <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D74" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E74" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F74" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G74" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H74" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I74" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J74">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
         <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E75" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F75" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G75" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H75" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="I75" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J75">
-        <v>4202253.5385999996</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+        <v>4202253.5386</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -3482,80 +3457,80 @@
         <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D76" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E76" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F76" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G76" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H76" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J76">
-        <v>1788407.8192739999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1788407.819274</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
         <v>85</v>
       </c>
       <c r="C77" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E77" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F77" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G77" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H77" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I77" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J77">
         <v>1550354.452950391</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
         <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E78" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F78" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G78" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H78" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I78" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J78">
         <v>7249147.17667</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -3563,54 +3538,54 @@
         <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D79" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E79" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F79" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G79" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H79" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I79" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J79">
-        <v>24972920.132110279</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+        <v>24972920.13211028</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
         <v>88</v>
       </c>
       <c r="C80" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E80" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F80" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G80" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H80" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J80">
-        <v>15702687.604910919</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+        <v>15702687.60491092</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -3618,25 +3593,25 @@
         <v>134</v>
       </c>
       <c r="C81" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D81" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E81" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F81" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J81">
-        <v>346083.46304915362</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+        <v>346083.4630491536</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
         <v>90</v>
       </c>
@@ -3644,54 +3619,54 @@
         <v>135</v>
       </c>
       <c r="C82" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D82" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E82" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F82" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G82" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J82">
-        <v>1250800.9400651229</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1250800.940065123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
         <v>91</v>
       </c>
       <c r="C83" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E83" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F83" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G83" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H83" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="I83" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J83">
         <v>280723.3006520429</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -3699,28 +3674,28 @@
         <v>136</v>
       </c>
       <c r="C84" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D84" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E84" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F84" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G84" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H84" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J84">
-        <v>6630997.3292599991</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+        <v>6630997.329259999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -3728,114 +3703,114 @@
         <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E85" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F85" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G85" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H85" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J85">
         <v>3714363.081590083</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10">
       <c r="A86" t="s">
         <v>94</v>
       </c>
       <c r="C86" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E86" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F86" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H86" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J86">
-        <v>1267949.1779535899</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1267949.17795359</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" t="s">
         <v>95</v>
       </c>
       <c r="C87" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E87" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F87" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H87" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J87">
-        <v>848008.50587400002</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+        <v>848008.505874</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" t="s">
         <v>96</v>
       </c>
       <c r="C88" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F88" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H88" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J88">
         <v>148601.7043568496</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10">
       <c r="A89" t="s">
         <v>97</v>
       </c>
       <c r="C89" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E89" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G89" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H89" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I89" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J89">
-        <v>1445491.9253398541</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1445491.925339854</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
         <v>98</v>
       </c>
@@ -3843,28 +3818,28 @@
         <v>135</v>
       </c>
       <c r="C90" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E90" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F90" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G90" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H90" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J90">
-        <v>741138.95960838371</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+        <v>741138.9596083837</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -3872,342 +3847,342 @@
         <v>137</v>
       </c>
       <c r="C91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E91" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F91" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G91" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H91" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J91">
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10">
       <c r="A92" t="s">
         <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E92" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F92" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H92" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J92">
-        <v>899806.32550548273</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
+        <v>899806.3255054827</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
         <v>101</v>
       </c>
       <c r="C93" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E93" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F93" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G93" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H93" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I93" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="J93">
-        <v>3436361.1128654238</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
+        <v>3436361.112865424</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
         <v>102</v>
       </c>
       <c r="C94" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G94" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H94" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="I94" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J94">
-        <v>2323252.9267690452</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2323252.926769045</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" t="s">
         <v>103</v>
       </c>
       <c r="C95" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E95" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F95" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G95" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H95" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I95" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J95">
-        <v>2475749.7725005322</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2475749.772500532</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" t="s">
         <v>104</v>
       </c>
       <c r="C96" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E96" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F96" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H96" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J96">
-        <v>9487628.0863300003</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
+        <v>9487628.08633</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
         <v>105</v>
       </c>
       <c r="C97" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E97" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F97" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H97" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J97">
-        <v>333307.12371929188</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
+        <v>333307.1237192919</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" t="s">
         <v>106</v>
       </c>
       <c r="C98" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F98" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H98" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I98" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J98">
-        <v>6202897.0171400001</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
+        <v>6202897.01714</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" t="s">
         <v>107</v>
       </c>
       <c r="C99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E99" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F99" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G99" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H99" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I99" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J99">
         <v>1341835.17078</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10">
       <c r="A100" t="s">
         <v>108</v>
       </c>
       <c r="C100" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E100" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F100" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G100" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H100" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I100" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J100">
-        <v>1113516.5997299999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1113516.59973</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" t="s">
         <v>109</v>
       </c>
       <c r="C101" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E101" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F101" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G101" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H101" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J101">
-        <v>2689687.0630099322</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2689687.063009932</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" t="s">
         <v>110</v>
       </c>
       <c r="C102" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E102" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F102" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G102" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H102" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J102">
-        <v>1248584.6715172599</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1248584.67151726</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" t="s">
         <v>111</v>
       </c>
       <c r="C103" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E103" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F103" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G103" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H103" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I103" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J103">
-        <v>5574423.9812850002</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
+        <v>5574423.981285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
       <c r="A104" t="s">
         <v>112</v>
       </c>
       <c r="C104" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E104" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F104" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G104" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H104" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="I104" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="J104">
-        <v>19028718.451565798</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
+        <v>19028718.4515658</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105" t="s">
         <v>113</v>
       </c>
@@ -4215,74 +4190,74 @@
         <v>134</v>
       </c>
       <c r="C105" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D105" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E105" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F105" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G105" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H105" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="I105" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J105">
-        <v>2331098.7137656999</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2331098.7137657</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
       <c r="A106" t="s">
         <v>114</v>
       </c>
       <c r="C106" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E106" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F106" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H106" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J106">
-        <v>6417855.9021505257</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
+        <v>6417855.902150526</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107" t="s">
         <v>115</v>
       </c>
       <c r="C107" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E107" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F107" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G107" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H107" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J107">
         <v>11904079.93924279</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10">
       <c r="A108" t="s">
         <v>116</v>
       </c>
@@ -4290,546 +4265,580 @@
         <v>138</v>
       </c>
       <c r="C108" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D108" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E108" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F108" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G108" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H108" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J108">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
       <c r="A109" t="s">
         <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E109" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F109" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H109" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J109">
         <v>189687.8885015327</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10">
       <c r="A110" t="s">
         <v>118</v>
       </c>
+      <c r="B110" t="s">
+        <v>139</v>
+      </c>
       <c r="C110" t="s">
-        <v>247</v>
+        <v>248</v>
+      </c>
+      <c r="D110" t="s">
+        <v>269</v>
       </c>
       <c r="E110" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F110" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G110" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H110" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J110">
-        <v>4412887.4395813216</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
+        <v>4412887.439581322</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
       <c r="A111" t="s">
         <v>119</v>
       </c>
       <c r="C111" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E111" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F111" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H111" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J111">
-        <v>708761.41470578162</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
+        <v>708761.4147057816</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
       <c r="A112" t="s">
         <v>120</v>
       </c>
+      <c r="B112" t="s">
+        <v>139</v>
+      </c>
       <c r="C112" t="s">
-        <v>249</v>
+        <v>250</v>
+      </c>
+      <c r="D112" t="s">
+        <v>269</v>
       </c>
       <c r="E112" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F112" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G112" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H112" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I112" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J112">
         <v>1600590.119251437</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10">
       <c r="A113" t="s">
         <v>121</v>
       </c>
       <c r="C113" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E113" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F113" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H113" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J113">
-        <v>4345046.9537415411</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
+        <v>4345046.953741541</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
         <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C114" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D114" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E114" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F114" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G114" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H114" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J114">
         <v>10235647.18904726</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
         <v>123</v>
       </c>
       <c r="B115" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C115" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D115" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E115" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F115" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G115" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H115" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J115">
-        <v>1973892.4554655049</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1973892.455465505</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
       <c r="A116" t="s">
         <v>124</v>
       </c>
       <c r="C116" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E116" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F116" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G116" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H116" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J116">
         <v>5293594.021862885</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
         <v>125</v>
       </c>
       <c r="C117" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E117" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F117" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G117" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H117" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J117">
         <v>3418676.16080696</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10">
       <c r="B118" t="s">
         <v>128</v>
       </c>
       <c r="E118" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F118" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G118" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H118" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I118" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J118">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="B119" t="s">
         <v>131</v>
       </c>
       <c r="E119" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F119" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G119" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H119" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I119" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J119">
-        <v>16569166.515905419</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+        <v>16569166.51590542</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
       <c r="B120" t="s">
         <v>133</v>
       </c>
       <c r="E120" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F120" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G120" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H120" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I120" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="J120">
-        <v>28687283.213700362</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+        <v>28687283.21370036</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="B121" t="s">
         <v>132</v>
       </c>
       <c r="E121" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F121" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G121" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H121" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I121" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="J121">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="B122" t="s">
         <v>138</v>
       </c>
       <c r="E122" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F122" t="s">
+        <v>282</v>
+      </c>
+      <c r="G122" t="s">
+        <v>289</v>
+      </c>
+      <c r="H122" t="s">
+        <v>307</v>
+      </c>
+      <c r="J122">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
+      <c r="B123" t="s">
+        <v>140</v>
+      </c>
+      <c r="E123" t="s">
         <v>280</v>
       </c>
-      <c r="G122" t="s">
-        <v>287</v>
-      </c>
-      <c r="H122" t="s">
-        <v>305</v>
-      </c>
-      <c r="J122">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="B123" t="s">
-        <v>139</v>
-      </c>
-      <c r="E123" t="s">
-        <v>278</v>
-      </c>
       <c r="F123" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G123" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H123" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J123">
-        <v>12209539.644512771</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+        <v>12209539.64451277</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="B124" t="s">
         <v>134</v>
       </c>
       <c r="E124" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F124" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G124" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H124" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="I124" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J124">
-        <v>2677182.1768148541</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+        <v>2677182.176814854</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
       <c r="B125" t="s">
         <v>127</v>
       </c>
       <c r="E125" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F125" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G125" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H125" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J125">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
       <c r="B126" t="s">
         <v>137</v>
       </c>
       <c r="E126" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F126" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G126" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="H126" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J126">
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:10">
       <c r="B127" t="s">
         <v>135</v>
       </c>
       <c r="E127" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F127" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G127" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H127" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J127">
-        <v>1991939.8996735071</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+        <v>1991939.899673507</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
       <c r="B128" t="s">
+        <v>139</v>
+      </c>
+      <c r="E128" t="s">
+        <v>280</v>
+      </c>
+      <c r="F128" t="s">
+        <v>282</v>
+      </c>
+      <c r="G128" t="s">
+        <v>301</v>
+      </c>
+      <c r="H128" t="s">
+        <v>359</v>
+      </c>
+      <c r="I128" t="s">
+        <v>368</v>
+      </c>
+      <c r="J128">
+        <v>6013477.558832759</v>
+      </c>
+    </row>
+    <row r="129" spans="2:10">
+      <c r="B129" t="s">
         <v>126</v>
       </c>
-      <c r="E128" t="s">
-        <v>270</v>
-      </c>
-      <c r="F128" t="s">
-        <v>280</v>
-      </c>
-      <c r="G128" t="s">
-        <v>299</v>
-      </c>
-      <c r="H128" t="s">
-        <v>315</v>
-      </c>
-      <c r="I128" t="s">
-        <v>398</v>
-      </c>
-      <c r="J128">
-        <v>3104130.8525155862</v>
-      </c>
-    </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B129" t="s">
+      <c r="E129" t="s">
+        <v>272</v>
+      </c>
+      <c r="F129" t="s">
+        <v>282</v>
+      </c>
+      <c r="G129" t="s">
+        <v>301</v>
+      </c>
+      <c r="H129" t="s">
+        <v>317</v>
+      </c>
+      <c r="I129" t="s">
+        <v>400</v>
+      </c>
+      <c r="J129">
+        <v>3104130.852515586</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10">
+      <c r="B130" t="s">
         <v>136</v>
       </c>
-      <c r="E129" t="s">
-        <v>277</v>
-      </c>
-      <c r="F129" t="s">
-        <v>282</v>
-      </c>
-      <c r="G129" t="s">
-        <v>296</v>
-      </c>
-      <c r="H129" t="s">
-        <v>345</v>
-      </c>
-      <c r="J129">
-        <v>6630997.3292599991</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B130" t="s">
+      <c r="E130" t="s">
+        <v>279</v>
+      </c>
+      <c r="F130" t="s">
+        <v>284</v>
+      </c>
+      <c r="G130" t="s">
+        <v>298</v>
+      </c>
+      <c r="H130" t="s">
+        <v>347</v>
+      </c>
+      <c r="J130">
+        <v>6630997.329259999</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10">
+      <c r="B131" t="s">
         <v>130</v>
       </c>
-      <c r="E130" t="s">
-        <v>276</v>
-      </c>
-      <c r="F130" t="s">
-        <v>280</v>
-      </c>
-      <c r="G130" t="s">
-        <v>300</v>
-      </c>
-      <c r="H130" t="s">
-        <v>361</v>
-      </c>
-      <c r="I130" t="s">
-        <v>368</v>
-      </c>
-      <c r="J130">
-        <v>33380023.309566759</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B131" t="s">
+      <c r="E131" t="s">
+        <v>278</v>
+      </c>
+      <c r="F131" t="s">
+        <v>282</v>
+      </c>
+      <c r="G131" t="s">
+        <v>302</v>
+      </c>
+      <c r="H131" t="s">
+        <v>363</v>
+      </c>
+      <c r="I131" t="s">
+        <v>370</v>
+      </c>
+      <c r="J131">
+        <v>33380023.30956676</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10">
+      <c r="B132" t="s">
         <v>129</v>
       </c>
-      <c r="E131" t="s">
-        <v>276</v>
-      </c>
-      <c r="F131" t="s">
-        <v>280</v>
-      </c>
-      <c r="G131" t="s">
-        <v>301</v>
-      </c>
-      <c r="H131" t="s">
-        <v>362</v>
-      </c>
-      <c r="I131" t="s">
-        <v>377</v>
-      </c>
-      <c r="J131">
-        <v>11427963.857514391</v>
+      <c r="E132" t="s">
+        <v>278</v>
+      </c>
+      <c r="F132" t="s">
+        <v>282</v>
+      </c>
+      <c r="G132" t="s">
+        <v>303</v>
+      </c>
+      <c r="H132" t="s">
+        <v>364</v>
+      </c>
+      <c r="I132" t="s">
+        <v>379</v>
+      </c>
+      <c r="J132">
+        <v>11427963.85751439</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/land_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_df.xlsx
@@ -1,15 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_07A142F131A30F3E4B2C4CF0ED6F305B78788327" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EE47C13-B33E-453F-93BC-D9675AA93C39}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1222,8 +1231,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1286,13 +1295,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1330,7 +1347,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1364,6 +1381,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1398,9 +1416,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1573,11 +1592,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J132"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="230.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1609,251 +1640,230 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H2" t="s">
-        <v>304</v>
-      </c>
-      <c r="I2" t="s">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="J2">
-        <v>1499689.86541</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>772974.2536339435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F3" t="s">
         <v>283</v>
       </c>
       <c r="H3" t="s">
-        <v>305</v>
+        <v>349</v>
       </c>
       <c r="J3">
-        <v>1396088.878773147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>848008.50587400002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>143</v>
+        <v>244</v>
       </c>
       <c r="E4" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H4" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="J4">
-        <v>7967834.63756</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>6417855.9021505257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
         <v>271</v>
       </c>
       <c r="F5" t="s">
-        <v>282</v>
-      </c>
-      <c r="G5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H5" t="s">
+        <v>305</v>
+      </c>
+      <c r="J5">
+        <v>1396088.878773147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H6" t="s">
+        <v>355</v>
+      </c>
+      <c r="J6">
+        <v>333307.12371929188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" t="s">
+        <v>279</v>
+      </c>
+      <c r="F7" t="s">
+        <v>282</v>
+      </c>
+      <c r="G7" t="s">
         <v>287</v>
       </c>
-      <c r="H5" t="s">
-        <v>307</v>
-      </c>
-      <c r="J5">
-        <v>416736.8603415595</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E6" t="s">
-        <v>271</v>
-      </c>
-      <c r="F6" t="s">
-        <v>282</v>
-      </c>
-      <c r="G6" t="s">
-        <v>286</v>
-      </c>
-      <c r="H6" t="s">
-        <v>308</v>
-      </c>
-      <c r="I6" t="s">
-        <v>366</v>
-      </c>
-      <c r="J6">
-        <v>13233210.3886</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" t="s">
-        <v>271</v>
-      </c>
-      <c r="F7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G7" t="s">
-        <v>286</v>
-      </c>
       <c r="H7" t="s">
-        <v>309</v>
-      </c>
-      <c r="I7" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="J7">
-        <v>22527998.6785</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>15702687.604910919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F8" t="s">
-        <v>282</v>
-      </c>
-      <c r="G8" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H8" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="I8" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="J8">
-        <v>11531646.5435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>1152609.9603903999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>148</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F9" t="s">
         <v>283</v>
       </c>
       <c r="H9" t="s">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="J9">
-        <v>7682504.761106032</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>148601.7043568496</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>110</v>
       </c>
       <c r="C10" t="s">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H10" t="s">
-        <v>306</v>
-      </c>
-      <c r="I10" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="J10">
-        <v>4950459.91493</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>1248584.6715172599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>150</v>
+        <v>242</v>
       </c>
       <c r="E11" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F11" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G11" t="s">
+        <v>286</v>
       </c>
       <c r="H11" t="s">
-        <v>311</v>
+        <v>327</v>
+      </c>
+      <c r="I11" t="s">
+        <v>398</v>
       </c>
       <c r="J11">
-        <v>199723.4981077999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>19028718.451565798</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="E12" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F12" t="s">
         <v>282</v>
@@ -1862,589 +1872,646 @@
         <v>286</v>
       </c>
       <c r="H12" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="J12">
-        <v>63924259.8049</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>26104648.817951292</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="C13" t="s">
-        <v>152</v>
+        <v>236</v>
       </c>
       <c r="E13" t="s">
+        <v>279</v>
+      </c>
+      <c r="F13" t="s">
+        <v>282</v>
+      </c>
+      <c r="G13" t="s">
+        <v>291</v>
+      </c>
+      <c r="H13" t="s">
+        <v>327</v>
+      </c>
+      <c r="I13" t="s">
+        <v>394</v>
+      </c>
+      <c r="J13">
+        <v>6202897.0171400001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C14" t="s">
+        <v>250</v>
+      </c>
+      <c r="D14" t="s">
+        <v>269</v>
+      </c>
+      <c r="E14" t="s">
+        <v>280</v>
+      </c>
+      <c r="F14" t="s">
+        <v>282</v>
+      </c>
+      <c r="G14" t="s">
+        <v>285</v>
+      </c>
+      <c r="H14" t="s">
+        <v>359</v>
+      </c>
+      <c r="I14" t="s">
+        <v>368</v>
+      </c>
+      <c r="J14">
+        <v>1600590.119251437</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" t="s">
+        <v>260</v>
+      </c>
+      <c r="E15" t="s">
+        <v>278</v>
+      </c>
+      <c r="F15" t="s">
+        <v>282</v>
+      </c>
+      <c r="G15" t="s">
+        <v>289</v>
+      </c>
+      <c r="H15" t="s">
+        <v>334</v>
+      </c>
+      <c r="J15">
+        <v>3063892.8050827952</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" t="s">
+        <v>260</v>
+      </c>
+      <c r="E16" t="s">
+        <v>278</v>
+      </c>
+      <c r="F16" t="s">
+        <v>282</v>
+      </c>
+      <c r="G16" t="s">
+        <v>285</v>
+      </c>
+      <c r="H16" t="s">
+        <v>334</v>
+      </c>
+      <c r="J16">
+        <v>110803.86577744479</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" t="s">
+        <v>220</v>
+      </c>
+      <c r="D17" t="s">
+        <v>265</v>
+      </c>
+      <c r="E17" t="s">
+        <v>279</v>
+      </c>
+      <c r="F17" t="s">
+        <v>284</v>
+      </c>
+      <c r="G17" t="s">
+        <v>297</v>
+      </c>
+      <c r="H17" t="s">
+        <v>346</v>
+      </c>
+      <c r="J17">
+        <v>1250800.9400651229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D18" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" t="s">
+        <v>279</v>
+      </c>
+      <c r="F18" t="s">
+        <v>284</v>
+      </c>
+      <c r="G18" t="s">
+        <v>297</v>
+      </c>
+      <c r="H18" t="s">
+        <v>346</v>
+      </c>
+      <c r="J18">
+        <v>741138.95960838371</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>195</v>
+      </c>
+      <c r="D19" t="s">
+        <v>260</v>
+      </c>
+      <c r="E19" t="s">
+        <v>278</v>
+      </c>
+      <c r="F19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G19" t="s">
+        <v>296</v>
+      </c>
+      <c r="H19" t="s">
+        <v>337</v>
+      </c>
+      <c r="J19">
+        <v>3963061.6444813549</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D20" t="s">
+        <v>260</v>
+      </c>
+      <c r="E20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F20" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" t="s">
+        <v>285</v>
+      </c>
+      <c r="H20" t="s">
+        <v>334</v>
+      </c>
+      <c r="J20">
+        <v>21591249.4628</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>145</v>
+      </c>
+      <c r="E21" t="s">
         <v>271</v>
       </c>
-      <c r="F13" t="s">
-        <v>283</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="F21" t="s">
+        <v>282</v>
+      </c>
+      <c r="G21" t="s">
+        <v>286</v>
+      </c>
+      <c r="H21" t="s">
         <v>308</v>
       </c>
-      <c r="J13">
-        <v>5776459.429646255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" t="s">
-        <v>271</v>
-      </c>
-      <c r="F14" t="s">
-        <v>283</v>
-      </c>
-      <c r="H14" t="s">
-        <v>313</v>
-      </c>
-      <c r="J14">
-        <v>1931027.417599746</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" t="s">
-        <v>154</v>
-      </c>
-      <c r="E15" t="s">
-        <v>271</v>
-      </c>
-      <c r="F15" t="s">
-        <v>282</v>
-      </c>
-      <c r="G15" t="s">
-        <v>286</v>
-      </c>
-      <c r="H15" t="s">
-        <v>308</v>
-      </c>
-      <c r="I15" t="s">
-        <v>370</v>
-      </c>
-      <c r="J15">
-        <v>12606786.4826</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" t="s">
-        <v>155</v>
-      </c>
-      <c r="D16" t="s">
-        <v>256</v>
-      </c>
-      <c r="E16" t="s">
-        <v>272</v>
-      </c>
-      <c r="F16" t="s">
-        <v>282</v>
-      </c>
-      <c r="G16" t="s">
-        <v>289</v>
-      </c>
-      <c r="H16" t="s">
-        <v>314</v>
-      </c>
-      <c r="J16">
-        <v>330003.3338055482</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C17" t="s">
-        <v>156</v>
-      </c>
-      <c r="E17" t="s">
-        <v>272</v>
-      </c>
-      <c r="F17" t="s">
-        <v>283</v>
-      </c>
-      <c r="H17" t="s">
-        <v>315</v>
-      </c>
-      <c r="J17">
-        <v>5670439.795488</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" t="s">
-        <v>157</v>
-      </c>
-      <c r="E18" t="s">
-        <v>272</v>
-      </c>
-      <c r="F18" t="s">
-        <v>282</v>
-      </c>
-      <c r="G18" t="s">
-        <v>290</v>
-      </c>
-      <c r="H18" t="s">
-        <v>316</v>
-      </c>
-      <c r="J18">
-        <v>1058100.092748948</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D19" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" t="s">
-        <v>272</v>
-      </c>
-      <c r="F19" t="s">
-        <v>282</v>
-      </c>
-      <c r="G19" t="s">
-        <v>285</v>
-      </c>
-      <c r="H19" t="s">
-        <v>317</v>
-      </c>
-      <c r="I19" t="s">
-        <v>371</v>
-      </c>
-      <c r="J19">
-        <v>363438.296974</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C20" t="s">
-        <v>159</v>
-      </c>
-      <c r="D20" t="s">
-        <v>256</v>
-      </c>
-      <c r="E20" t="s">
-        <v>272</v>
-      </c>
-      <c r="F20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G20" t="s">
-        <v>289</v>
-      </c>
-      <c r="H20" t="s">
-        <v>313</v>
-      </c>
-      <c r="I20" t="s">
-        <v>372</v>
-      </c>
-      <c r="J20">
-        <v>2410689.221736038</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C21" t="s">
-        <v>160</v>
-      </c>
-      <c r="E21" t="s">
-        <v>272</v>
-      </c>
-      <c r="F21" t="s">
-        <v>282</v>
-      </c>
-      <c r="G21" t="s">
-        <v>291</v>
-      </c>
-      <c r="H21" t="s">
-        <v>318</v>
+      <c r="I21" t="s">
+        <v>366</v>
       </c>
       <c r="J21">
-        <v>7481998.483051093</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>13233210.388599999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C22" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="E22" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F22" t="s">
         <v>283</v>
       </c>
       <c r="H22" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="J22">
-        <v>772974.2536339435</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>124954.6686331536</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="E23" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F23" t="s">
         <v>283</v>
       </c>
       <c r="H23" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="J23">
-        <v>255208.969208</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>386230.80603899999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>32</v>
+        <v>61</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
       </c>
       <c r="C24" t="s">
-        <v>163</v>
+        <v>192</v>
+      </c>
+      <c r="D24" t="s">
+        <v>260</v>
       </c>
       <c r="E24" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F24" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G24" t="s">
+        <v>285</v>
       </c>
       <c r="H24" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="J24">
-        <v>86936203.29125148</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>1929968.1763706871</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="E25" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F25" t="s">
         <v>282</v>
       </c>
       <c r="G25" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H25" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="I25" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="J25">
-        <v>4789014.03756</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>10276967.100669291</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E26" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F26" t="s">
         <v>282</v>
       </c>
       <c r="G26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="H26" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J26">
-        <v>163254.62437129</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>9992991.5686563142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>127</v>
       </c>
       <c r="C27" t="s">
-        <v>166</v>
+        <v>171</v>
+      </c>
+      <c r="D27" t="s">
+        <v>257</v>
       </c>
       <c r="E27" t="s">
         <v>274</v>
       </c>
       <c r="F27" t="s">
+        <v>282</v>
+      </c>
+      <c r="G27" t="s">
+        <v>287</v>
+      </c>
+      <c r="H27" t="s">
+        <v>323</v>
+      </c>
+      <c r="J27">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" t="s">
+        <v>209</v>
+      </c>
+      <c r="E28" t="s">
+        <v>278</v>
+      </c>
+      <c r="F28" t="s">
+        <v>282</v>
+      </c>
+      <c r="G28" t="s">
+        <v>288</v>
+      </c>
+      <c r="H28" t="s">
+        <v>307</v>
+      </c>
+      <c r="I28" t="s">
+        <v>386</v>
+      </c>
+      <c r="J28">
+        <v>352884.57374953461</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29" t="s">
+        <v>175</v>
+      </c>
+      <c r="E29" t="s">
+        <v>276</v>
+      </c>
+      <c r="F29" t="s">
+        <v>282</v>
+      </c>
+      <c r="G29" t="s">
+        <v>293</v>
+      </c>
+      <c r="H29" t="s">
+        <v>324</v>
+      </c>
+      <c r="I29" t="s">
+        <v>376</v>
+      </c>
+      <c r="J29">
+        <v>16826817.56129609</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" t="s">
+        <v>227</v>
+      </c>
+      <c r="E30" t="s">
+        <v>279</v>
+      </c>
+      <c r="F30" t="s">
+        <v>282</v>
+      </c>
+      <c r="G30" t="s">
+        <v>288</v>
+      </c>
+      <c r="H30" t="s">
+        <v>307</v>
+      </c>
+      <c r="I30" t="s">
+        <v>368</v>
+      </c>
+      <c r="J30">
+        <v>1445491.9253398541</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" t="s">
+        <v>271</v>
+      </c>
+      <c r="F31" t="s">
+        <v>282</v>
+      </c>
+      <c r="G31" t="s">
+        <v>287</v>
+      </c>
+      <c r="H31" t="s">
+        <v>307</v>
+      </c>
+      <c r="J31">
+        <v>416736.86034155951</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" t="s">
+        <v>279</v>
+      </c>
+      <c r="F32" t="s">
+        <v>284</v>
+      </c>
+      <c r="H32" t="s">
+        <v>348</v>
+      </c>
+      <c r="J32">
+        <v>1267949.1779535899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" t="s">
+        <v>271</v>
+      </c>
+      <c r="F33" t="s">
         <v>283</v>
       </c>
-      <c r="H27" t="s">
-        <v>322</v>
-      </c>
-      <c r="I27" t="s">
-        <v>374</v>
-      </c>
-      <c r="J27">
-        <v>1152609.9603904</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" t="s">
-        <v>167</v>
-      </c>
-      <c r="E28" t="s">
-        <v>274</v>
-      </c>
-      <c r="F28" t="s">
-        <v>282</v>
-      </c>
-      <c r="G28" t="s">
-        <v>286</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="H33" t="s">
+        <v>311</v>
+      </c>
+      <c r="J33">
+        <v>199723.49810779991</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" t="s">
+        <v>223</v>
+      </c>
+      <c r="D34" t="s">
+        <v>263</v>
+      </c>
+      <c r="E34" t="s">
+        <v>279</v>
+      </c>
+      <c r="F34" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" t="s">
+        <v>287</v>
+      </c>
+      <c r="H34" t="s">
         <v>323</v>
       </c>
-      <c r="J28">
-        <v>10572188.5661376</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" t="s">
-        <v>168</v>
-      </c>
-      <c r="E29" t="s">
-        <v>274</v>
-      </c>
-      <c r="F29" t="s">
-        <v>282</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="J34">
+        <v>3714363.081590083</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" t="s">
+        <v>191</v>
+      </c>
+      <c r="E35" t="s">
+        <v>278</v>
+      </c>
+      <c r="F35" t="s">
+        <v>282</v>
+      </c>
+      <c r="G35" t="s">
+        <v>291</v>
+      </c>
+      <c r="H35" t="s">
+        <v>307</v>
+      </c>
+      <c r="I35" t="s">
+        <v>380</v>
+      </c>
+      <c r="J35">
+        <v>7405086.2285420913</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
+        <v>182</v>
+      </c>
+      <c r="D36" t="s">
+        <v>259</v>
+      </c>
+      <c r="E36" t="s">
+        <v>278</v>
+      </c>
+      <c r="F36" t="s">
+        <v>282</v>
+      </c>
+      <c r="G36" t="s">
         <v>285</v>
       </c>
-      <c r="H29" t="s">
-        <v>308</v>
-      </c>
-      <c r="J29">
-        <v>1510729.369309124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C30" t="s">
-        <v>169</v>
-      </c>
-      <c r="E30" t="s">
-        <v>274</v>
-      </c>
-      <c r="F30" t="s">
-        <v>284</v>
-      </c>
-      <c r="G30" t="s">
-        <v>292</v>
-      </c>
-      <c r="H30" t="s">
-        <v>315</v>
-      </c>
-      <c r="J30">
-        <v>681889.9964301857</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E31" t="s">
-        <v>274</v>
-      </c>
-      <c r="F31" t="s">
-        <v>282</v>
-      </c>
-      <c r="G31" t="s">
-        <v>286</v>
-      </c>
-      <c r="H31" t="s">
-        <v>323</v>
-      </c>
-      <c r="J31">
-        <v>26104648.81795129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" t="s">
-        <v>171</v>
-      </c>
-      <c r="D32" t="s">
-        <v>257</v>
-      </c>
-      <c r="E32" t="s">
-        <v>274</v>
-      </c>
-      <c r="F32" t="s">
-        <v>282</v>
-      </c>
-      <c r="G32" t="s">
-        <v>287</v>
-      </c>
-      <c r="H32" t="s">
-        <v>323</v>
-      </c>
-      <c r="J32">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" t="s">
-        <v>172</v>
-      </c>
-      <c r="E33" t="s">
-        <v>274</v>
-      </c>
-      <c r="F33" t="s">
-        <v>282</v>
-      </c>
-      <c r="G33" t="s">
-        <v>286</v>
-      </c>
-      <c r="H33" t="s">
-        <v>307</v>
-      </c>
-      <c r="J33">
-        <v>4354811.166996506</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" t="s">
-        <v>173</v>
-      </c>
-      <c r="E34" t="s">
-        <v>275</v>
-      </c>
-      <c r="F34" t="s">
-        <v>282</v>
-      </c>
-      <c r="G34" t="s">
-        <v>286</v>
-      </c>
-      <c r="H34" t="s">
-        <v>307</v>
-      </c>
-      <c r="I34" t="s">
-        <v>375</v>
-      </c>
-      <c r="J34">
-        <v>3064668.693174671</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" t="s">
-        <v>174</v>
-      </c>
-      <c r="E35" t="s">
-        <v>276</v>
-      </c>
-      <c r="F35" t="s">
-        <v>282</v>
-      </c>
-      <c r="G35" t="s">
-        <v>293</v>
-      </c>
-      <c r="H35" t="s">
-        <v>324</v>
-      </c>
-      <c r="J35">
-        <v>9992991.568656314</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" t="s">
-        <v>44</v>
-      </c>
-      <c r="C36" t="s">
-        <v>175</v>
-      </c>
-      <c r="E36" t="s">
-        <v>276</v>
-      </c>
-      <c r="F36" t="s">
-        <v>282</v>
-      </c>
-      <c r="G36" t="s">
-        <v>293</v>
-      </c>
       <c r="H36" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I36" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="J36">
-        <v>16826817.56129609</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
+        <v>1760913.595839669</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2467,113 +2534,116 @@
         <v>375</v>
       </c>
       <c r="J37">
-        <v>126962.7450922684</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>126962.74509226839</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>130</v>
       </c>
       <c r="C38" t="s">
-        <v>177</v>
+        <v>189</v>
+      </c>
+      <c r="D38" t="s">
+        <v>260</v>
       </c>
       <c r="E38" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F38" t="s">
+        <v>282</v>
+      </c>
+      <c r="G38" t="s">
+        <v>285</v>
+      </c>
+      <c r="H38" t="s">
+        <v>334</v>
+      </c>
+      <c r="J38">
+        <v>2161806.0909095029</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" t="s">
+        <v>271</v>
+      </c>
+      <c r="F39" t="s">
+        <v>282</v>
+      </c>
+      <c r="G39" t="s">
+        <v>286</v>
+      </c>
+      <c r="H39" t="s">
+        <v>309</v>
+      </c>
+      <c r="I39" t="s">
+        <v>367</v>
+      </c>
+      <c r="J39">
+        <v>22527998.6785</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" t="s">
+        <v>271</v>
+      </c>
+      <c r="F40" t="s">
         <v>283</v>
       </c>
-      <c r="H38" t="s">
-        <v>325</v>
-      </c>
-      <c r="J38">
-        <v>771997.9267729169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39" t="s">
-        <v>178</v>
-      </c>
-      <c r="E39" t="s">
-        <v>276</v>
-      </c>
-      <c r="F39" t="s">
-        <v>283</v>
-      </c>
-      <c r="H39" t="s">
-        <v>326</v>
-      </c>
-      <c r="J39">
-        <v>2695956.210741678</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" t="s">
-        <v>179</v>
-      </c>
-      <c r="D40" t="s">
-        <v>258</v>
-      </c>
-      <c r="E40" t="s">
-        <v>277</v>
-      </c>
-      <c r="F40" t="s">
-        <v>282</v>
-      </c>
-      <c r="G40" t="s">
-        <v>289</v>
-      </c>
       <c r="H40" t="s">
-        <v>307</v>
-      </c>
-      <c r="I40" t="s">
-        <v>377</v>
+        <v>313</v>
       </c>
       <c r="J40">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>1931027.417599746</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>107</v>
       </c>
       <c r="C41" t="s">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="E41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F41" t="s">
         <v>282</v>
       </c>
       <c r="G41" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H41" t="s">
         <v>327</v>
       </c>
       <c r="I41" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="J41">
-        <v>22789723.43693621</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>1341835.17078</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E42" t="s">
         <v>278</v>
@@ -2582,62 +2652,53 @@
         <v>282</v>
       </c>
       <c r="G42" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H42" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="I42" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="J42">
-        <v>5804864.894492002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>3503071.0617284952</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="C43" t="s">
-        <v>182</v>
-      </c>
-      <c r="D43" t="s">
-        <v>259</v>
+        <v>151</v>
       </c>
       <c r="E43" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F43" t="s">
         <v>282</v>
       </c>
       <c r="G43" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H43" t="s">
-        <v>328</v>
-      </c>
-      <c r="I43" t="s">
-        <v>379</v>
+        <v>312</v>
       </c>
       <c r="J43">
-        <v>1760913.595839669</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
+        <v>63924259.804899998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E44" t="s">
         <v>278</v>
@@ -2646,64 +2707,76 @@
         <v>282</v>
       </c>
       <c r="G44" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H44" t="s">
-        <v>329</v>
-      </c>
-      <c r="I44" t="s">
-        <v>370</v>
+        <v>307</v>
       </c>
       <c r="J44">
-        <v>559241.2641449785</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>1141145.8646362079</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>92</v>
+      </c>
+      <c r="B45" t="s">
+        <v>136</v>
       </c>
       <c r="C45" t="s">
-        <v>184</v>
+        <v>222</v>
+      </c>
+      <c r="D45" t="s">
+        <v>266</v>
       </c>
       <c r="E45" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F45" t="s">
-        <v>283</v>
+        <v>284</v>
+      </c>
+      <c r="G45" t="s">
+        <v>298</v>
       </c>
       <c r="H45" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="J45">
-        <v>2821612.246080229</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>6630997.3292599991</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
+        <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F46" t="s">
         <v>283</v>
       </c>
       <c r="H46" t="s">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="J46">
-        <v>2460432.820685903</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>4345046.9537415411</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>55</v>
+        <v>62</v>
+      </c>
+      <c r="B47" t="s">
+        <v>131</v>
       </c>
       <c r="C47" t="s">
-        <v>186</v>
+        <v>193</v>
+      </c>
+      <c r="D47" t="s">
+        <v>261</v>
       </c>
       <c r="E47" t="s">
         <v>278</v>
@@ -2712,151 +2785,148 @@
         <v>282</v>
       </c>
       <c r="G47" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H47" t="s">
         <v>307</v>
       </c>
+      <c r="I47" t="s">
+        <v>381</v>
+      </c>
       <c r="J47">
-        <v>3512631.992361845</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
+        <v>15428020.65126922</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="E48" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F48" t="s">
         <v>283</v>
       </c>
       <c r="H48" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="J48">
-        <v>367462.345355</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
+        <v>5776459.4296462554</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>188</v>
-      </c>
-      <c r="D49" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E49" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F49" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G49" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="H49" t="s">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="J49">
-        <v>6838840.246701591</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>5293594.021862885</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>122</v>
       </c>
       <c r="B50" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C50" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="D50" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="E50" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F50" t="s">
         <v>282</v>
       </c>
       <c r="G50" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H50" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="J50">
-        <v>2161806.090909503</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>10235647.18904726</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="E51" t="s">
         <v>278</v>
       </c>
       <c r="F51" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G51" t="s">
+        <v>288</v>
       </c>
       <c r="H51" t="s">
-        <v>335</v>
+        <v>343</v>
+      </c>
+      <c r="I51" t="s">
+        <v>389</v>
       </c>
       <c r="J51">
-        <v>124954.6686331536</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
+        <v>4202253.5385999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="E52" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F52" t="s">
         <v>282</v>
       </c>
       <c r="G52" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H52" t="s">
         <v>307</v>
       </c>
       <c r="I52" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="J52">
-        <v>7405086.228542091</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>3436361.1128654238</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="C53" t="s">
-        <v>192</v>
-      </c>
-      <c r="D53" t="s">
-        <v>260</v>
+        <v>205</v>
       </c>
       <c r="E53" t="s">
         <v>278</v>
@@ -2865,200 +2935,206 @@
         <v>282</v>
       </c>
       <c r="G53" t="s">
+        <v>291</v>
+      </c>
+      <c r="H53" t="s">
+        <v>341</v>
+      </c>
+      <c r="I53" t="s">
+        <v>385</v>
+      </c>
+      <c r="J53">
+        <v>8409093.1265900005</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>113</v>
+      </c>
+      <c r="B54" t="s">
+        <v>134</v>
+      </c>
+      <c r="C54" t="s">
+        <v>243</v>
+      </c>
+      <c r="D54" t="s">
+        <v>264</v>
+      </c>
+      <c r="E54" t="s">
+        <v>279</v>
+      </c>
+      <c r="F54" t="s">
+        <v>282</v>
+      </c>
+      <c r="G54" t="s">
+        <v>287</v>
+      </c>
+      <c r="H54" t="s">
+        <v>358</v>
+      </c>
+      <c r="I54" t="s">
+        <v>399</v>
+      </c>
+      <c r="J54">
+        <v>2331098.7137656999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
+        <v>126</v>
+      </c>
+      <c r="C55" t="s">
+        <v>158</v>
+      </c>
+      <c r="D55" t="s">
+        <v>256</v>
+      </c>
+      <c r="E55" t="s">
+        <v>272</v>
+      </c>
+      <c r="F55" t="s">
+        <v>282</v>
+      </c>
+      <c r="G55" t="s">
         <v>285</v>
       </c>
-      <c r="H53" t="s">
-        <v>334</v>
-      </c>
-      <c r="J53">
-        <v>1929968.176370687</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
-      <c r="A54" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" t="s">
-        <v>131</v>
-      </c>
-      <c r="C54" t="s">
-        <v>193</v>
-      </c>
-      <c r="D54" t="s">
-        <v>261</v>
-      </c>
-      <c r="E54" t="s">
-        <v>278</v>
-      </c>
-      <c r="F54" t="s">
-        <v>282</v>
-      </c>
-      <c r="G54" t="s">
-        <v>285</v>
-      </c>
-      <c r="H54" t="s">
+      <c r="H55" t="s">
+        <v>317</v>
+      </c>
+      <c r="I55" t="s">
+        <v>371</v>
+      </c>
+      <c r="J55">
+        <v>363438.296974</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>115</v>
+      </c>
+      <c r="C56" t="s">
+        <v>245</v>
+      </c>
+      <c r="E56" t="s">
+        <v>279</v>
+      </c>
+      <c r="F56" t="s">
+        <v>282</v>
+      </c>
+      <c r="G56" t="s">
+        <v>288</v>
+      </c>
+      <c r="H56" t="s">
         <v>307</v>
       </c>
-      <c r="I54" t="s">
-        <v>381</v>
-      </c>
-      <c r="J54">
-        <v>15428020.65126922</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10">
-      <c r="A55" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" t="s">
-        <v>194</v>
-      </c>
-      <c r="E55" t="s">
-        <v>278</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="J56">
+        <v>11904079.93924279</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" t="s">
+        <v>241</v>
+      </c>
+      <c r="E57" t="s">
+        <v>279</v>
+      </c>
+      <c r="F57" t="s">
+        <v>282</v>
+      </c>
+      <c r="G57" t="s">
+        <v>288</v>
+      </c>
+      <c r="H57" t="s">
+        <v>357</v>
+      </c>
+      <c r="I57" t="s">
+        <v>397</v>
+      </c>
+      <c r="J57">
+        <v>5574423.9812850002</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>89</v>
+      </c>
+      <c r="B58" t="s">
+        <v>134</v>
+      </c>
+      <c r="C58" t="s">
+        <v>219</v>
+      </c>
+      <c r="D58" t="s">
+        <v>264</v>
+      </c>
+      <c r="E58" t="s">
+        <v>279</v>
+      </c>
+      <c r="F58" t="s">
         <v>283</v>
       </c>
-      <c r="H55" t="s">
-        <v>336</v>
-      </c>
-      <c r="J55">
-        <v>515060.9564426438</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="A56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" t="s">
-        <v>130</v>
-      </c>
-      <c r="C56" t="s">
-        <v>195</v>
-      </c>
-      <c r="D56" t="s">
-        <v>260</v>
-      </c>
-      <c r="E56" t="s">
-        <v>278</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="H58" t="s">
+        <v>345</v>
+      </c>
+      <c r="J58">
+        <v>346083.46304915362</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>38</v>
+      </c>
+      <c r="C59" t="s">
+        <v>169</v>
+      </c>
+      <c r="E59" t="s">
+        <v>274</v>
+      </c>
+      <c r="F59" t="s">
         <v>284</v>
       </c>
-      <c r="G56" t="s">
-        <v>296</v>
-      </c>
-      <c r="H56" t="s">
-        <v>337</v>
-      </c>
-      <c r="J56">
-        <v>3963061.644481355</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
-      <c r="A57" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" t="s">
-        <v>196</v>
-      </c>
-      <c r="E57" t="s">
-        <v>278</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="G59" t="s">
+        <v>292</v>
+      </c>
+      <c r="H59" t="s">
+        <v>315</v>
+      </c>
+      <c r="J59">
+        <v>681889.99643018574</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" t="s">
+        <v>272</v>
+      </c>
+      <c r="F60" t="s">
         <v>283</v>
       </c>
-      <c r="H57" t="s">
-        <v>338</v>
-      </c>
-      <c r="J57">
-        <v>788132.0847764658</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
-      <c r="A58" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" t="s">
-        <v>130</v>
-      </c>
-      <c r="C58" t="s">
-        <v>197</v>
-      </c>
-      <c r="D58" t="s">
-        <v>260</v>
-      </c>
-      <c r="E58" t="s">
-        <v>278</v>
-      </c>
-      <c r="F58" t="s">
-        <v>282</v>
-      </c>
-      <c r="G58" t="s">
-        <v>285</v>
-      </c>
-      <c r="H58" t="s">
-        <v>334</v>
-      </c>
-      <c r="J58">
-        <v>110803.8657774448</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
-      <c r="A59" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" t="s">
-        <v>198</v>
-      </c>
-      <c r="E59" t="s">
-        <v>278</v>
-      </c>
-      <c r="F59" t="s">
-        <v>282</v>
-      </c>
-      <c r="G59" t="s">
-        <v>291</v>
-      </c>
-      <c r="H59" t="s">
-        <v>307</v>
-      </c>
-      <c r="I59" t="s">
-        <v>382</v>
-      </c>
-      <c r="J59">
-        <v>3503071.061728495</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
-      <c r="A60" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" t="s">
-        <v>199</v>
-      </c>
-      <c r="E60" t="s">
-        <v>278</v>
-      </c>
-      <c r="F60" t="s">
-        <v>282</v>
-      </c>
-      <c r="G60" t="s">
-        <v>285</v>
-      </c>
       <c r="H60" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="J60">
-        <v>989146.0724139999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+        <v>5670439.7954879999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E61" t="s">
         <v>278</v>
@@ -3070,21 +3146,21 @@
         <v>288</v>
       </c>
       <c r="H61" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="I61" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="J61">
-        <v>1874190.45757726</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10">
+        <v>5804864.8944920022</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E62" t="s">
         <v>278</v>
@@ -3093,96 +3169,99 @@
         <v>282</v>
       </c>
       <c r="G62" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H62" t="s">
         <v>327</v>
       </c>
-      <c r="I62" t="s">
-        <v>384</v>
-      </c>
       <c r="J62">
-        <v>6139378.49533</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>240468.70558949231</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="C63" t="s">
-        <v>202</v>
-      </c>
-      <c r="D63" t="s">
-        <v>261</v>
+        <v>196</v>
       </c>
       <c r="E63" t="s">
         <v>278</v>
       </c>
       <c r="F63" t="s">
-        <v>282</v>
-      </c>
-      <c r="G63" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H63" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="J63">
-        <v>1141145.864636208</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>788132.08477646578</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>123</v>
+      </c>
+      <c r="B64" t="s">
+        <v>140</v>
       </c>
       <c r="C64" t="s">
-        <v>203</v>
+        <v>253</v>
+      </c>
+      <c r="D64" t="s">
+        <v>270</v>
       </c>
       <c r="E64" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F64" t="s">
         <v>282</v>
       </c>
       <c r="G64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H64" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="J64">
-        <v>240468.7055894923</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>1973892.4554655049</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>118</v>
+      </c>
+      <c r="B65" t="s">
+        <v>139</v>
       </c>
       <c r="C65" t="s">
-        <v>204</v>
+        <v>248</v>
+      </c>
+      <c r="D65" t="s">
+        <v>269</v>
       </c>
       <c r="E65" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F65" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G65" t="s">
+        <v>289</v>
       </c>
       <c r="H65" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="J65">
-        <v>242518.965983</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10">
+        <v>4412887.4395813216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="E66" t="s">
         <v>278</v>
@@ -3191,128 +3270,119 @@
         <v>282</v>
       </c>
       <c r="G66" t="s">
+        <v>285</v>
+      </c>
+      <c r="H66" t="s">
+        <v>339</v>
+      </c>
+      <c r="J66">
+        <v>989146.07241399994</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>119</v>
+      </c>
+      <c r="C67" t="s">
+        <v>249</v>
+      </c>
+      <c r="E67" t="s">
+        <v>280</v>
+      </c>
+      <c r="F67" t="s">
+        <v>283</v>
+      </c>
+      <c r="H67" t="s">
+        <v>360</v>
+      </c>
+      <c r="J67">
+        <v>708761.41470578162</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>48</v>
+      </c>
+      <c r="B68" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" t="s">
+        <v>179</v>
+      </c>
+      <c r="D68" t="s">
+        <v>258</v>
+      </c>
+      <c r="E68" t="s">
+        <v>277</v>
+      </c>
+      <c r="F68" t="s">
+        <v>282</v>
+      </c>
+      <c r="G68" t="s">
+        <v>289</v>
+      </c>
+      <c r="H68" t="s">
+        <v>307</v>
+      </c>
+      <c r="I68" t="s">
+        <v>377</v>
+      </c>
+      <c r="J68">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" t="s">
+        <v>168</v>
+      </c>
+      <c r="E69" t="s">
+        <v>274</v>
+      </c>
+      <c r="F69" t="s">
+        <v>282</v>
+      </c>
+      <c r="G69" t="s">
+        <v>285</v>
+      </c>
+      <c r="H69" t="s">
+        <v>308</v>
+      </c>
+      <c r="J69">
+        <v>1510729.3693091241</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>125</v>
+      </c>
+      <c r="C70" t="s">
+        <v>255</v>
+      </c>
+      <c r="E70" t="s">
+        <v>281</v>
+      </c>
+      <c r="F70" t="s">
+        <v>282</v>
+      </c>
+      <c r="G70" t="s">
         <v>291</v>
       </c>
-      <c r="H66" t="s">
-        <v>341</v>
-      </c>
-      <c r="I66" t="s">
-        <v>385</v>
-      </c>
-      <c r="J66">
-        <v>8409093.12659</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
-      <c r="A67" t="s">
-        <v>75</v>
-      </c>
-      <c r="C67" t="s">
-        <v>206</v>
-      </c>
-      <c r="E67" t="s">
-        <v>278</v>
-      </c>
-      <c r="F67" t="s">
-        <v>282</v>
-      </c>
-      <c r="G67" t="s">
-        <v>286</v>
-      </c>
-      <c r="H67" t="s">
-        <v>307</v>
-      </c>
-      <c r="I67" t="s">
-        <v>386</v>
-      </c>
-      <c r="J67">
-        <v>10276967.10066929</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
-      <c r="A68" t="s">
-        <v>76</v>
-      </c>
-      <c r="C68" t="s">
-        <v>207</v>
-      </c>
-      <c r="E68" t="s">
-        <v>278</v>
-      </c>
-      <c r="F68" t="s">
-        <v>283</v>
-      </c>
-      <c r="H68" t="s">
-        <v>342</v>
-      </c>
-      <c r="J68">
-        <v>386230.806039</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
-      <c r="A69" t="s">
+      <c r="H70" t="s">
+        <v>308</v>
+      </c>
+      <c r="J70">
+        <v>3418676.16080696</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>77</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C71" t="s">
         <v>208</v>
-      </c>
-      <c r="E69" t="s">
-        <v>278</v>
-      </c>
-      <c r="F69" t="s">
-        <v>282</v>
-      </c>
-      <c r="G69" t="s">
-        <v>287</v>
-      </c>
-      <c r="H69" t="s">
-        <v>307</v>
-      </c>
-      <c r="I69" t="s">
-        <v>387</v>
-      </c>
-      <c r="J69">
-        <v>948677.9026767507</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
-      <c r="A70" t="s">
-        <v>78</v>
-      </c>
-      <c r="C70" t="s">
-        <v>209</v>
-      </c>
-      <c r="E70" t="s">
-        <v>278</v>
-      </c>
-      <c r="F70" t="s">
-        <v>282</v>
-      </c>
-      <c r="G70" t="s">
-        <v>288</v>
-      </c>
-      <c r="H70" t="s">
-        <v>307</v>
-      </c>
-      <c r="I70" t="s">
-        <v>386</v>
-      </c>
-      <c r="J70">
-        <v>352884.5737495346</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="A71" t="s">
-        <v>79</v>
-      </c>
-      <c r="B71" t="s">
-        <v>130</v>
-      </c>
-      <c r="C71" t="s">
-        <v>210</v>
-      </c>
-      <c r="D71" t="s">
-        <v>260</v>
       </c>
       <c r="E71" t="s">
         <v>278</v>
@@ -3321,164 +3391,146 @@
         <v>282</v>
       </c>
       <c r="G71" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H71" t="s">
-        <v>334</v>
+        <v>307</v>
+      </c>
+      <c r="I71" t="s">
+        <v>387</v>
       </c>
       <c r="J71">
-        <v>3063892.805082795</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>948677.90267675067</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C72" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D72" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E72" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F72" t="s">
         <v>282</v>
       </c>
       <c r="G72" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="H72" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="I72" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="J72">
-        <v>1039802.195699128</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
+        <v>24972920.132110279</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="C73" t="s">
-        <v>195</v>
-      </c>
-      <c r="D73" t="s">
-        <v>260</v>
+        <v>173</v>
       </c>
       <c r="E73" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F73" t="s">
         <v>282</v>
       </c>
       <c r="G73" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H73" t="s">
-        <v>334</v>
+        <v>307</v>
+      </c>
+      <c r="I73" t="s">
+        <v>375</v>
       </c>
       <c r="J73">
-        <v>21591249.4628</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10">
+        <v>3064668.6931746709</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" t="s">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>212</v>
-      </c>
-      <c r="D74" t="s">
-        <v>262</v>
+        <v>154</v>
       </c>
       <c r="E74" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F74" t="s">
         <v>282</v>
       </c>
       <c r="G74" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H74" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I74" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="J74">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>12606786.4826</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>83</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>213</v>
+        <v>143</v>
       </c>
       <c r="E75" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="F75" t="s">
         <v>282</v>
       </c>
       <c r="G75" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H75" t="s">
-        <v>343</v>
-      </c>
-      <c r="I75" t="s">
-        <v>389</v>
+        <v>306</v>
       </c>
       <c r="J75">
-        <v>4202253.5386</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>7967834.6375599997</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="C76" t="s">
-        <v>214</v>
-      </c>
-      <c r="D76" t="s">
-        <v>259</v>
+        <v>162</v>
       </c>
       <c r="E76" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F76" t="s">
-        <v>282</v>
-      </c>
-      <c r="G76" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H76" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="J76">
-        <v>1788407.819274</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>255208.96920799999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -3504,148 +3556,151 @@
         <v>1550354.452950391</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="C78" t="s">
-        <v>216</v>
+        <v>141</v>
       </c>
       <c r="E78" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F78" t="s">
         <v>282</v>
       </c>
       <c r="G78" t="s">
+        <v>285</v>
+      </c>
+      <c r="H78" t="s">
+        <v>304</v>
+      </c>
+      <c r="I78" t="s">
+        <v>365</v>
+      </c>
+      <c r="J78">
+        <v>1499689.8654100001</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" t="s">
+        <v>149</v>
+      </c>
+      <c r="E79" t="s">
+        <v>271</v>
+      </c>
+      <c r="F79" t="s">
+        <v>282</v>
+      </c>
+      <c r="G79" t="s">
         <v>288</v>
       </c>
-      <c r="H78" t="s">
-        <v>327</v>
-      </c>
-      <c r="I78" t="s">
-        <v>370</v>
-      </c>
-      <c r="J78">
-        <v>7249147.17667</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10">
-      <c r="A79" t="s">
-        <v>87</v>
-      </c>
-      <c r="B79" t="s">
-        <v>133</v>
-      </c>
-      <c r="C79" t="s">
-        <v>217</v>
-      </c>
-      <c r="D79" t="s">
-        <v>263</v>
-      </c>
-      <c r="E79" t="s">
-        <v>279</v>
-      </c>
-      <c r="F79" t="s">
-        <v>282</v>
-      </c>
-      <c r="G79" t="s">
-        <v>286</v>
-      </c>
       <c r="H79" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="I79" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="J79">
-        <v>24972920.13211028</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>4950459.91493</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>88</v>
+        <v>28</v>
+      </c>
+      <c r="B80" t="s">
+        <v>126</v>
       </c>
       <c r="C80" t="s">
-        <v>218</v>
+        <v>159</v>
+      </c>
+      <c r="D80" t="s">
+        <v>256</v>
       </c>
       <c r="E80" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="F80" t="s">
         <v>282</v>
       </c>
       <c r="G80" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H80" t="s">
-        <v>323</v>
+        <v>313</v>
+      </c>
+      <c r="I80" t="s">
+        <v>372</v>
       </c>
       <c r="J80">
-        <v>15702687.60491092</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>2410689.2217360381</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B81" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C81" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D81" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E81" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F81" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G81" t="s">
+        <v>285</v>
       </c>
       <c r="H81" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J81">
-        <v>346083.4630491536</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+        <v>1788407.8192739999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>90</v>
-      </c>
-      <c r="B82" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="C82" t="s">
-        <v>220</v>
-      </c>
-      <c r="D82" t="s">
-        <v>265</v>
+        <v>232</v>
       </c>
       <c r="E82" t="s">
         <v>279</v>
       </c>
       <c r="F82" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G82" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="H82" t="s">
-        <v>346</v>
+        <v>353</v>
+      </c>
+      <c r="I82" t="s">
+        <v>390</v>
       </c>
       <c r="J82">
-        <v>1250800.940065123</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+        <v>2323252.9267690452</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C83" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E83" t="s">
         <v>279</v>
@@ -3654,249 +3709,225 @@
         <v>282</v>
       </c>
       <c r="G83" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="H83" t="s">
-        <v>324</v>
-      </c>
-      <c r="I83" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="J83">
-        <v>280723.3006520429</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10">
+        <v>2689687.0630099322</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" t="s">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="C84" t="s">
-        <v>222</v>
-      </c>
-      <c r="D84" t="s">
-        <v>266</v>
+        <v>165</v>
       </c>
       <c r="E84" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F84" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G84" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="H84" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="J84">
-        <v>6630997.329259999</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>163254.62437129</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" t="s">
-        <v>133</v>
+        <v>53</v>
       </c>
       <c r="C85" t="s">
-        <v>223</v>
-      </c>
-      <c r="D85" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="E85" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F85" t="s">
-        <v>282</v>
-      </c>
-      <c r="G85" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="H85" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="J85">
-        <v>3714363.081590083</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10">
+        <v>2821612.2460802291</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>224</v>
+        <v>148</v>
       </c>
       <c r="E86" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F86" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H86" t="s">
-        <v>348</v>
+        <v>310</v>
       </c>
       <c r="J86">
-        <v>1267949.17795359</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>7682504.7611060319</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="C87" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
       <c r="E87" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F87" t="s">
         <v>283</v>
       </c>
       <c r="H87" t="s">
-        <v>349</v>
+        <v>326</v>
       </c>
       <c r="J87">
-        <v>848008.505874</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>2695956.2107416778</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="C88" t="s">
-        <v>226</v>
+        <v>172</v>
       </c>
       <c r="E88" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F88" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G88" t="s">
+        <v>286</v>
       </c>
       <c r="H88" t="s">
-        <v>350</v>
+        <v>307</v>
       </c>
       <c r="J88">
-        <v>148601.7043568496</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10">
+        <v>4354811.166996506</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="E89" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F89" t="s">
         <v>282</v>
       </c>
       <c r="G89" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H89" t="s">
         <v>307</v>
       </c>
-      <c r="I89" t="s">
-        <v>368</v>
-      </c>
       <c r="J89">
-        <v>1445491.925339854</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+        <v>3512631.992361845</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>98</v>
-      </c>
-      <c r="B90" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="C90" t="s">
-        <v>228</v>
-      </c>
-      <c r="D90" t="s">
-        <v>265</v>
+        <v>177</v>
       </c>
       <c r="E90" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F90" t="s">
-        <v>284</v>
-      </c>
-      <c r="G90" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="H90" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="J90">
-        <v>741138.9596083837</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>771997.92677291692</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>99</v>
-      </c>
-      <c r="B91" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="C91" t="s">
-        <v>229</v>
-      </c>
-      <c r="D91" t="s">
-        <v>267</v>
+        <v>233</v>
       </c>
       <c r="E91" t="s">
         <v>279</v>
       </c>
       <c r="F91" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G91" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H91" t="s">
-        <v>351</v>
+        <v>354</v>
+      </c>
+      <c r="I91" t="s">
+        <v>393</v>
       </c>
       <c r="J91">
-        <v>1113481.921945367</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10">
+        <v>2475749.7725005322</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="C92" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="E92" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F92" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G92" t="s">
+        <v>291</v>
       </c>
       <c r="H92" t="s">
-        <v>352</v>
+        <v>327</v>
+      </c>
+      <c r="I92" t="s">
+        <v>375</v>
       </c>
       <c r="J92">
-        <v>899806.3255054827</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>22789723.436936211</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>101</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>231</v>
+        <v>147</v>
       </c>
       <c r="E93" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F93" t="s">
         <v>282</v>
@@ -3905,24 +3936,24 @@
         <v>286</v>
       </c>
       <c r="H93" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="I93" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="J93">
-        <v>3436361.112865424</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
+        <v>11531646.543500001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="C94" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="E94" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F94" t="s">
         <v>282</v>
@@ -3931,21 +3962,21 @@
         <v>288</v>
       </c>
       <c r="H94" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="I94" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="J94">
-        <v>2323252.926769045</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>6139378.4953300003</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C95" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="E95" t="s">
         <v>279</v>
@@ -3954,111 +3985,111 @@
         <v>282</v>
       </c>
       <c r="G95" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H95" t="s">
-        <v>354</v>
+        <v>324</v>
       </c>
       <c r="I95" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J95">
-        <v>2475749.772500532</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+        <v>280723.3006520429</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="C96" t="s">
-        <v>234</v>
+        <v>167</v>
       </c>
       <c r="E96" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F96" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G96" t="s">
+        <v>286</v>
       </c>
       <c r="H96" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="J96">
-        <v>9487628.08633</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>10572188.566137601</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
       <c r="C97" t="s">
-        <v>235</v>
+        <v>163</v>
       </c>
       <c r="E97" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F97" t="s">
         <v>283</v>
       </c>
       <c r="H97" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="J97">
-        <v>333307.1237192919</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+        <v>86936203.291251481</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>106</v>
+        <v>116</v>
+      </c>
+      <c r="B98" t="s">
+        <v>138</v>
       </c>
       <c r="C98" t="s">
-        <v>236</v>
+        <v>246</v>
+      </c>
+      <c r="D98" t="s">
+        <v>268</v>
       </c>
       <c r="E98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F98" t="s">
         <v>282</v>
       </c>
       <c r="G98" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H98" t="s">
-        <v>327</v>
-      </c>
-      <c r="I98" t="s">
-        <v>394</v>
+        <v>307</v>
       </c>
       <c r="J98">
-        <v>6202897.01714</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C99" t="s">
-        <v>237</v>
+        <v>194</v>
       </c>
       <c r="E99" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F99" t="s">
-        <v>282</v>
-      </c>
-      <c r="G99" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H99" t="s">
-        <v>327</v>
-      </c>
-      <c r="I99" t="s">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="J99">
-        <v>1341835.17078</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10">
+        <v>515060.95644264377</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -4081,437 +4112,437 @@
         <v>396</v>
       </c>
       <c r="J100">
-        <v>1113516.59973</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>1113516.5997299999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>109</v>
+        <v>24</v>
+      </c>
+      <c r="B101" t="s">
+        <v>126</v>
       </c>
       <c r="C101" t="s">
-        <v>239</v>
+        <v>155</v>
+      </c>
+      <c r="D101" t="s">
+        <v>256</v>
       </c>
       <c r="E101" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="F101" t="s">
         <v>282</v>
       </c>
       <c r="G101" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="H101" t="s">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="J101">
-        <v>2689687.063009932</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+        <v>330003.3338055482</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>110</v>
+        <v>80</v>
+      </c>
+      <c r="B102" t="s">
+        <v>129</v>
       </c>
       <c r="C102" t="s">
-        <v>240</v>
+        <v>211</v>
+      </c>
+      <c r="D102" t="s">
+        <v>259</v>
       </c>
       <c r="E102" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F102" t="s">
+        <v>282</v>
+      </c>
+      <c r="G102" t="s">
+        <v>289</v>
+      </c>
+      <c r="H102" t="s">
+        <v>334</v>
+      </c>
+      <c r="I102" t="s">
+        <v>379</v>
+      </c>
+      <c r="J102">
+        <v>1039802.195699128</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" t="s">
+        <v>129</v>
+      </c>
+      <c r="C103" t="s">
+        <v>188</v>
+      </c>
+      <c r="D103" t="s">
+        <v>259</v>
+      </c>
+      <c r="E103" t="s">
+        <v>278</v>
+      </c>
+      <c r="F103" t="s">
         <v>284</v>
       </c>
-      <c r="G102" t="s">
-        <v>292</v>
-      </c>
-      <c r="H102" t="s">
-        <v>356</v>
-      </c>
-      <c r="J102">
-        <v>1248584.67151726</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
-      <c r="A103" t="s">
-        <v>111</v>
-      </c>
-      <c r="C103" t="s">
-        <v>241</v>
-      </c>
-      <c r="E103" t="s">
-        <v>279</v>
-      </c>
-      <c r="F103" t="s">
-        <v>282</v>
-      </c>
       <c r="G103" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H103" t="s">
-        <v>357</v>
-      </c>
-      <c r="I103" t="s">
-        <v>397</v>
+        <v>333</v>
       </c>
       <c r="J103">
-        <v>5574423.981285</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
+        <v>6838840.2467015907</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C104" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="E104" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F104" t="s">
-        <v>282</v>
-      </c>
-      <c r="G104" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H104" t="s">
-        <v>327</v>
-      </c>
-      <c r="I104" t="s">
-        <v>398</v>
+        <v>332</v>
       </c>
       <c r="J104">
-        <v>19028718.4515658</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
+        <v>367462.345355</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>113</v>
-      </c>
-      <c r="B105" t="s">
-        <v>134</v>
+        <v>26</v>
       </c>
       <c r="C105" t="s">
-        <v>243</v>
-      </c>
-      <c r="D105" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
       <c r="E105" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="F105" t="s">
         <v>282</v>
       </c>
       <c r="G105" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H105" t="s">
-        <v>358</v>
-      </c>
-      <c r="I105" t="s">
-        <v>399</v>
+        <v>316</v>
       </c>
       <c r="J105">
-        <v>2331098.7137657</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
+        <v>1058100.0927489479</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="C106" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="E106" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F106" t="s">
         <v>283</v>
       </c>
       <c r="H106" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="J106">
-        <v>6417855.902150526</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
+        <v>2460432.8206859031</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="C107" t="s">
-        <v>245</v>
+        <v>160</v>
       </c>
       <c r="E107" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="F107" t="s">
         <v>282</v>
       </c>
       <c r="G107" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H107" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="J107">
-        <v>11904079.93924279</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10">
+        <v>7481998.4830510933</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="B108" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C108" t="s">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="D108" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="E108" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F108" t="s">
         <v>282</v>
       </c>
       <c r="G108" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H108" t="s">
         <v>307</v>
       </c>
+      <c r="I108" t="s">
+        <v>388</v>
+      </c>
       <c r="J108">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>52</v>
+      </c>
+      <c r="B109" t="s">
+        <v>130</v>
+      </c>
+      <c r="C109" t="s">
+        <v>183</v>
+      </c>
+      <c r="D109" t="s">
+        <v>260</v>
+      </c>
+      <c r="E109" t="s">
+        <v>278</v>
+      </c>
+      <c r="F109" t="s">
+        <v>282</v>
+      </c>
+      <c r="G109" t="s">
+        <v>285</v>
+      </c>
+      <c r="H109" t="s">
+        <v>329</v>
+      </c>
+      <c r="I109" t="s">
+        <v>370</v>
+      </c>
+      <c r="J109">
+        <v>559241.26414497849</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>104</v>
+      </c>
+      <c r="C110" t="s">
+        <v>234</v>
+      </c>
+      <c r="E110" t="s">
+        <v>279</v>
+      </c>
+      <c r="F110" t="s">
+        <v>283</v>
+      </c>
+      <c r="H110" t="s">
+        <v>306</v>
+      </c>
+      <c r="J110">
+        <v>9487628.0863300003</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>99</v>
+      </c>
+      <c r="B111" t="s">
+        <v>137</v>
+      </c>
+      <c r="C111" t="s">
+        <v>229</v>
+      </c>
+      <c r="D111" t="s">
+        <v>267</v>
+      </c>
+      <c r="E111" t="s">
+        <v>279</v>
+      </c>
+      <c r="F111" t="s">
+        <v>284</v>
+      </c>
+      <c r="G111" t="s">
+        <v>292</v>
+      </c>
+      <c r="H111" t="s">
+        <v>351</v>
+      </c>
+      <c r="J111">
+        <v>1113481.921945367</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>73</v>
+      </c>
+      <c r="C112" t="s">
+        <v>204</v>
+      </c>
+      <c r="E112" t="s">
+        <v>278</v>
+      </c>
+      <c r="F112" t="s">
+        <v>283</v>
+      </c>
+      <c r="H112" t="s">
+        <v>340</v>
+      </c>
+      <c r="J112">
+        <v>242518.965983</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>33</v>
+      </c>
+      <c r="C113" t="s">
+        <v>164</v>
+      </c>
+      <c r="E113" t="s">
+        <v>274</v>
+      </c>
+      <c r="F113" t="s">
+        <v>282</v>
+      </c>
+      <c r="G113" t="s">
+        <v>291</v>
+      </c>
+      <c r="H113" t="s">
+        <v>315</v>
+      </c>
+      <c r="I113" t="s">
+        <v>373</v>
+      </c>
+      <c r="J113">
+        <v>4789014.0375600001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>117</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C114" t="s">
         <v>247</v>
-      </c>
-      <c r="E109" t="s">
-        <v>280</v>
-      </c>
-      <c r="F109" t="s">
-        <v>283</v>
-      </c>
-      <c r="H109" t="s">
-        <v>359</v>
-      </c>
-      <c r="J109">
-        <v>189687.8885015327</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10">
-      <c r="A110" t="s">
-        <v>118</v>
-      </c>
-      <c r="B110" t="s">
-        <v>139</v>
-      </c>
-      <c r="C110" t="s">
-        <v>248</v>
-      </c>
-      <c r="D110" t="s">
-        <v>269</v>
-      </c>
-      <c r="E110" t="s">
-        <v>280</v>
-      </c>
-      <c r="F110" t="s">
-        <v>282</v>
-      </c>
-      <c r="G110" t="s">
-        <v>289</v>
-      </c>
-      <c r="H110" t="s">
-        <v>359</v>
-      </c>
-      <c r="J110">
-        <v>4412887.439581322</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
-      <c r="A111" t="s">
-        <v>119</v>
-      </c>
-      <c r="C111" t="s">
-        <v>249</v>
-      </c>
-      <c r="E111" t="s">
-        <v>280</v>
-      </c>
-      <c r="F111" t="s">
-        <v>283</v>
-      </c>
-      <c r="H111" t="s">
-        <v>360</v>
-      </c>
-      <c r="J111">
-        <v>708761.4147057816</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" t="s">
-        <v>120</v>
-      </c>
-      <c r="B112" t="s">
-        <v>139</v>
-      </c>
-      <c r="C112" t="s">
-        <v>250</v>
-      </c>
-      <c r="D112" t="s">
-        <v>269</v>
-      </c>
-      <c r="E112" t="s">
-        <v>280</v>
-      </c>
-      <c r="F112" t="s">
-        <v>282</v>
-      </c>
-      <c r="G112" t="s">
-        <v>285</v>
-      </c>
-      <c r="H112" t="s">
-        <v>359</v>
-      </c>
-      <c r="I112" t="s">
-        <v>368</v>
-      </c>
-      <c r="J112">
-        <v>1600590.119251437</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10">
-      <c r="A113" t="s">
-        <v>121</v>
-      </c>
-      <c r="C113" t="s">
-        <v>251</v>
-      </c>
-      <c r="E113" t="s">
-        <v>280</v>
-      </c>
-      <c r="F113" t="s">
-        <v>283</v>
-      </c>
-      <c r="H113" t="s">
-        <v>359</v>
-      </c>
-      <c r="J113">
-        <v>4345046.953741541</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
-      <c r="A114" t="s">
-        <v>122</v>
-      </c>
-      <c r="B114" t="s">
-        <v>140</v>
-      </c>
-      <c r="C114" t="s">
-        <v>252</v>
-      </c>
-      <c r="D114" t="s">
-        <v>270</v>
       </c>
       <c r="E114" t="s">
         <v>280</v>
       </c>
       <c r="F114" t="s">
-        <v>282</v>
-      </c>
-      <c r="G114" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="H114" t="s">
         <v>359</v>
       </c>
       <c r="J114">
-        <v>10235647.18904726</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10">
+        <v>189687.8885015327</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>123</v>
-      </c>
-      <c r="B115" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="C115" t="s">
-        <v>253</v>
-      </c>
-      <c r="D115" t="s">
-        <v>270</v>
+        <v>216</v>
       </c>
       <c r="E115" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F115" t="s">
         <v>282</v>
       </c>
       <c r="G115" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H115" t="s">
-        <v>359</v>
+        <v>327</v>
+      </c>
+      <c r="I115" t="s">
+        <v>370</v>
       </c>
       <c r="J115">
-        <v>1973892.455465505</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
+        <v>7249147.17667</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C116" t="s">
-        <v>254</v>
+        <v>230</v>
       </c>
       <c r="E116" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F116" t="s">
-        <v>282</v>
-      </c>
-      <c r="G116" t="s">
+        <v>283</v>
+      </c>
+      <c r="H116" t="s">
+        <v>352</v>
+      </c>
+      <c r="J116">
+        <v>899806.32550548273</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>69</v>
+      </c>
+      <c r="C117" t="s">
+        <v>200</v>
+      </c>
+      <c r="E117" t="s">
+        <v>278</v>
+      </c>
+      <c r="F117" t="s">
+        <v>282</v>
+      </c>
+      <c r="G117" t="s">
         <v>288</v>
       </c>
-      <c r="H116" t="s">
-        <v>361</v>
-      </c>
-      <c r="J116">
-        <v>5293594.021862885</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10">
-      <c r="A117" t="s">
-        <v>125</v>
-      </c>
-      <c r="C117" t="s">
-        <v>255</v>
-      </c>
-      <c r="E117" t="s">
-        <v>281</v>
-      </c>
-      <c r="F117" t="s">
-        <v>282</v>
-      </c>
-      <c r="G117" t="s">
-        <v>291</v>
-      </c>
       <c r="H117" t="s">
-        <v>308</v>
+        <v>307</v>
+      </c>
+      <c r="I117" t="s">
+        <v>383</v>
       </c>
       <c r="J117">
-        <v>3418676.16080696</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10">
+        <v>1874190.45757726</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
         <v>128</v>
       </c>
@@ -4531,10 +4562,10 @@
         <v>377</v>
       </c>
       <c r="J118">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
         <v>131</v>
       </c>
@@ -4554,10 +4585,10 @@
         <v>381</v>
       </c>
       <c r="J119">
-        <v>16569166.51590542</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
+        <v>16569166.515905419</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
         <v>133</v>
       </c>
@@ -4577,10 +4608,10 @@
         <v>390</v>
       </c>
       <c r="J120">
-        <v>28687283.21370036</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
+        <v>28687283.213700362</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
         <v>132</v>
       </c>
@@ -4600,10 +4631,10 @@
         <v>388</v>
       </c>
       <c r="J121">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
         <v>138</v>
       </c>
@@ -4620,10 +4651,10 @@
         <v>307</v>
       </c>
       <c r="J122">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
         <v>140</v>
       </c>
@@ -4640,10 +4671,10 @@
         <v>359</v>
       </c>
       <c r="J123">
-        <v>12209539.64451277</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>12209539.644512771</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>134</v>
       </c>
@@ -4663,10 +4694,10 @@
         <v>399</v>
       </c>
       <c r="J124">
-        <v>2677182.176814854</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
+        <v>2677182.1768148541</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
         <v>127</v>
       </c>
@@ -4683,10 +4714,10 @@
         <v>323</v>
       </c>
       <c r="J125">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
         <v>137</v>
       </c>
@@ -4706,7 +4737,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>135</v>
       </c>
@@ -4723,10 +4754,10 @@
         <v>346</v>
       </c>
       <c r="J127">
-        <v>1991939.899673507</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
+        <v>1991939.8996735071</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
         <v>139</v>
       </c>
@@ -4749,7 +4780,7 @@
         <v>6013477.558832759</v>
       </c>
     </row>
-    <row r="129" spans="2:10">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
         <v>126</v>
       </c>
@@ -4769,10 +4800,10 @@
         <v>400</v>
       </c>
       <c r="J129">
-        <v>3104130.852515586</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10">
+        <v>3104130.8525155862</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
         <v>136</v>
       </c>
@@ -4789,10 +4820,10 @@
         <v>347</v>
       </c>
       <c r="J130">
-        <v>6630997.329259999</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10">
+        <v>6630997.3292599991</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
         <v>130</v>
       </c>
@@ -4812,10 +4843,10 @@
         <v>370</v>
       </c>
       <c r="J131">
-        <v>33380023.30956676</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10">
+        <v>33380023.309566759</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
         <v>129</v>
       </c>
@@ -4835,10 +4866,15 @@
         <v>379</v>
       </c>
       <c r="J132">
-        <v>11427963.85751439</v>
+        <v>11427963.857514391</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J132">
+      <sortCondition ref="C1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/land_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_df.xlsx
@@ -1,24 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_07A142F131A30F3E4B2C4CF0ED6F305B78788327" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EE47C13-B33E-453F-93BC-D9675AA93C39}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$1</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1231,8 +1222,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1295,21 +1286,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1347,7 +1330,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1381,7 +1364,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1416,10 +1398,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1592,23 +1573,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J132"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="230.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1640,230 +1609,251 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F2" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G2" t="s">
+        <v>285</v>
       </c>
       <c r="H2" t="s">
-        <v>317</v>
+        <v>304</v>
+      </c>
+      <c r="I2" t="s">
+        <v>365</v>
       </c>
       <c r="J2">
-        <v>772974.2536339435</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1499689.86541</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F3" t="s">
         <v>283</v>
       </c>
       <c r="H3" t="s">
-        <v>349</v>
+        <v>305</v>
       </c>
       <c r="J3">
-        <v>848008.50587400002</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1396088.878773147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>114</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>244</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F4" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G4" t="s">
+        <v>286</v>
       </c>
       <c r="H4" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="J4">
-        <v>6417855.9021505257</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7967834.63756</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
         <v>271</v>
       </c>
       <c r="F5" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G5" t="s">
+        <v>287</v>
       </c>
       <c r="H5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J5">
-        <v>1396088.878773147</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>416736.8603415595</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F6" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G6" t="s">
+        <v>286</v>
       </c>
       <c r="H6" t="s">
-        <v>355</v>
+        <v>308</v>
+      </c>
+      <c r="I6" t="s">
+        <v>366</v>
       </c>
       <c r="J6">
-        <v>333307.12371929188</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>13233210.3886</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F7" t="s">
         <v>282</v>
       </c>
       <c r="G7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H7" t="s">
-        <v>323</v>
+        <v>309</v>
+      </c>
+      <c r="I7" t="s">
+        <v>367</v>
       </c>
       <c r="J7">
-        <v>15702687.604910919</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>22527998.6785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F8" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G8" t="s">
+        <v>286</v>
       </c>
       <c r="H8" t="s">
-        <v>322</v>
+        <v>306</v>
       </c>
       <c r="I8" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="J8">
-        <v>1152609.9603903999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>11531646.5435</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>226</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F9" t="s">
         <v>283</v>
       </c>
       <c r="H9" t="s">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="J9">
-        <v>148601.7043568496</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7682504.761106032</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>240</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H10" t="s">
-        <v>356</v>
+        <v>306</v>
+      </c>
+      <c r="I10" t="s">
+        <v>369</v>
       </c>
       <c r="J10">
-        <v>1248584.6715172599</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4950459.91493</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>242</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F11" t="s">
-        <v>282</v>
-      </c>
-      <c r="G11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H11" t="s">
-        <v>327</v>
-      </c>
-      <c r="I11" t="s">
-        <v>398</v>
+        <v>311</v>
       </c>
       <c r="J11">
-        <v>19028718.451565798</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>199723.4981077999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F12" t="s">
         <v>282</v>
@@ -1872,646 +1862,589 @@
         <v>286</v>
       </c>
       <c r="H12" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="J12">
-        <v>26104648.817951292</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>63924259.8049</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>236</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="F13" t="s">
-        <v>282</v>
-      </c>
-      <c r="G13" t="s">
+        <v>283</v>
+      </c>
+      <c r="H13" t="s">
+        <v>308</v>
+      </c>
+      <c r="J13">
+        <v>5776459.429646255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" t="s">
+        <v>271</v>
+      </c>
+      <c r="F14" t="s">
+        <v>283</v>
+      </c>
+      <c r="H14" t="s">
+        <v>313</v>
+      </c>
+      <c r="J14">
+        <v>1931027.417599746</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>154</v>
+      </c>
+      <c r="E15" t="s">
+        <v>271</v>
+      </c>
+      <c r="F15" t="s">
+        <v>282</v>
+      </c>
+      <c r="G15" t="s">
+        <v>286</v>
+      </c>
+      <c r="H15" t="s">
+        <v>308</v>
+      </c>
+      <c r="I15" t="s">
+        <v>370</v>
+      </c>
+      <c r="J15">
+        <v>12606786.4826</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" t="s">
+        <v>282</v>
+      </c>
+      <c r="G16" t="s">
+        <v>289</v>
+      </c>
+      <c r="H16" t="s">
+        <v>314</v>
+      </c>
+      <c r="J16">
+        <v>330003.3338055482</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" t="s">
+        <v>272</v>
+      </c>
+      <c r="F17" t="s">
+        <v>283</v>
+      </c>
+      <c r="H17" t="s">
+        <v>315</v>
+      </c>
+      <c r="J17">
+        <v>5670439.795488</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" t="s">
+        <v>157</v>
+      </c>
+      <c r="E18" t="s">
+        <v>272</v>
+      </c>
+      <c r="F18" t="s">
+        <v>282</v>
+      </c>
+      <c r="G18" t="s">
+        <v>290</v>
+      </c>
+      <c r="H18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J18">
+        <v>1058100.092748948</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D19" t="s">
+        <v>256</v>
+      </c>
+      <c r="E19" t="s">
+        <v>272</v>
+      </c>
+      <c r="F19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G19" t="s">
+        <v>285</v>
+      </c>
+      <c r="H19" t="s">
+        <v>317</v>
+      </c>
+      <c r="I19" t="s">
+        <v>371</v>
+      </c>
+      <c r="J19">
+        <v>363438.296974</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>126</v>
+      </c>
+      <c r="C20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E20" t="s">
+        <v>272</v>
+      </c>
+      <c r="F20" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" t="s">
+        <v>289</v>
+      </c>
+      <c r="H20" t="s">
+        <v>313</v>
+      </c>
+      <c r="I20" t="s">
+        <v>372</v>
+      </c>
+      <c r="J20">
+        <v>2410689.221736038</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" t="s">
+        <v>272</v>
+      </c>
+      <c r="F21" t="s">
+        <v>282</v>
+      </c>
+      <c r="G21" t="s">
         <v>291</v>
       </c>
-      <c r="H13" t="s">
-        <v>327</v>
-      </c>
-      <c r="I13" t="s">
-        <v>394</v>
-      </c>
-      <c r="J13">
-        <v>6202897.0171400001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" t="s">
-        <v>250</v>
-      </c>
-      <c r="D14" t="s">
-        <v>269</v>
-      </c>
-      <c r="E14" t="s">
-        <v>280</v>
-      </c>
-      <c r="F14" t="s">
-        <v>282</v>
-      </c>
-      <c r="G14" t="s">
-        <v>285</v>
-      </c>
-      <c r="H14" t="s">
-        <v>359</v>
-      </c>
-      <c r="I14" t="s">
-        <v>368</v>
-      </c>
-      <c r="J14">
-        <v>1600590.119251437</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
-        <v>130</v>
-      </c>
-      <c r="C15" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" t="s">
-        <v>260</v>
-      </c>
-      <c r="E15" t="s">
-        <v>278</v>
-      </c>
-      <c r="F15" t="s">
-        <v>282</v>
-      </c>
-      <c r="G15" t="s">
-        <v>289</v>
-      </c>
-      <c r="H15" t="s">
-        <v>334</v>
-      </c>
-      <c r="J15">
-        <v>3063892.8050827952</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>66</v>
-      </c>
-      <c r="B16" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" t="s">
-        <v>197</v>
-      </c>
-      <c r="D16" t="s">
-        <v>260</v>
-      </c>
-      <c r="E16" t="s">
-        <v>278</v>
-      </c>
-      <c r="F16" t="s">
-        <v>282</v>
-      </c>
-      <c r="G16" t="s">
-        <v>285</v>
-      </c>
-      <c r="H16" t="s">
-        <v>334</v>
-      </c>
-      <c r="J16">
-        <v>110803.86577744479</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" t="s">
-        <v>220</v>
-      </c>
-      <c r="D17" t="s">
-        <v>265</v>
-      </c>
-      <c r="E17" t="s">
-        <v>279</v>
-      </c>
-      <c r="F17" t="s">
-        <v>284</v>
-      </c>
-      <c r="G17" t="s">
-        <v>297</v>
-      </c>
-      <c r="H17" t="s">
-        <v>346</v>
-      </c>
-      <c r="J17">
-        <v>1250800.9400651229</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" t="s">
-        <v>228</v>
-      </c>
-      <c r="D18" t="s">
-        <v>265</v>
-      </c>
-      <c r="E18" t="s">
-        <v>279</v>
-      </c>
-      <c r="F18" t="s">
-        <v>284</v>
-      </c>
-      <c r="G18" t="s">
-        <v>297</v>
-      </c>
-      <c r="H18" t="s">
-        <v>346</v>
-      </c>
-      <c r="J18">
-        <v>741138.95960838371</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>64</v>
-      </c>
-      <c r="B19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" t="s">
-        <v>195</v>
-      </c>
-      <c r="D19" t="s">
-        <v>260</v>
-      </c>
-      <c r="E19" t="s">
-        <v>278</v>
-      </c>
-      <c r="F19" t="s">
-        <v>284</v>
-      </c>
-      <c r="G19" t="s">
-        <v>296</v>
-      </c>
-      <c r="H19" t="s">
-        <v>337</v>
-      </c>
-      <c r="J19">
-        <v>3963061.6444813549</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D20" t="s">
-        <v>260</v>
-      </c>
-      <c r="E20" t="s">
-        <v>278</v>
-      </c>
-      <c r="F20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G20" t="s">
-        <v>285</v>
-      </c>
-      <c r="H20" t="s">
-        <v>334</v>
-      </c>
-      <c r="J20">
-        <v>21591249.4628</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" t="s">
-        <v>145</v>
-      </c>
-      <c r="E21" t="s">
-        <v>271</v>
-      </c>
-      <c r="F21" t="s">
-        <v>282</v>
-      </c>
-      <c r="G21" t="s">
-        <v>286</v>
-      </c>
       <c r="H21" t="s">
-        <v>308</v>
-      </c>
-      <c r="I21" t="s">
-        <v>366</v>
+        <v>318</v>
       </c>
       <c r="J21">
-        <v>13233210.388599999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7481998.483051093</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F22" t="s">
         <v>283</v>
       </c>
       <c r="H22" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="J22">
-        <v>124954.6686331536</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>772974.2536339435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C23" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="E23" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F23" t="s">
         <v>283</v>
       </c>
       <c r="H23" t="s">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="J23">
-        <v>386230.80603899999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>255208.969208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>192</v>
-      </c>
-      <c r="D24" t="s">
-        <v>260</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F24" t="s">
-        <v>282</v>
-      </c>
-      <c r="G24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H24" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="J24">
-        <v>1929968.1763706871</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>86936203.29125148</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="E25" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="F25" t="s">
         <v>282</v>
       </c>
       <c r="G25" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H25" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="I25" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="J25">
-        <v>10276967.100669291</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4789014.03756</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="E26" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F26" t="s">
         <v>282</v>
       </c>
       <c r="G26" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="H26" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J26">
-        <v>9992991.5686563142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>163254.62437129</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>171</v>
-      </c>
-      <c r="D27" t="s">
-        <v>257</v>
+        <v>166</v>
       </c>
       <c r="E27" t="s">
         <v>274</v>
       </c>
       <c r="F27" t="s">
-        <v>282</v>
-      </c>
-      <c r="G27" t="s">
+        <v>283</v>
+      </c>
+      <c r="H27" t="s">
+        <v>322</v>
+      </c>
+      <c r="I27" t="s">
+        <v>374</v>
+      </c>
+      <c r="J27">
+        <v>1152609.9603904</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" t="s">
+        <v>274</v>
+      </c>
+      <c r="F28" t="s">
+        <v>282</v>
+      </c>
+      <c r="G28" t="s">
+        <v>286</v>
+      </c>
+      <c r="H28" t="s">
+        <v>323</v>
+      </c>
+      <c r="J28">
+        <v>10572188.5661376</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" t="s">
+        <v>168</v>
+      </c>
+      <c r="E29" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" t="s">
+        <v>282</v>
+      </c>
+      <c r="G29" t="s">
+        <v>285</v>
+      </c>
+      <c r="H29" t="s">
+        <v>308</v>
+      </c>
+      <c r="J29">
+        <v>1510729.369309124</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>274</v>
+      </c>
+      <c r="F30" t="s">
+        <v>284</v>
+      </c>
+      <c r="G30" t="s">
+        <v>292</v>
+      </c>
+      <c r="H30" t="s">
+        <v>315</v>
+      </c>
+      <c r="J30">
+        <v>681889.9964301857</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" t="s">
+        <v>170</v>
+      </c>
+      <c r="E31" t="s">
+        <v>274</v>
+      </c>
+      <c r="F31" t="s">
+        <v>282</v>
+      </c>
+      <c r="G31" t="s">
+        <v>286</v>
+      </c>
+      <c r="H31" t="s">
+        <v>323</v>
+      </c>
+      <c r="J31">
+        <v>26104648.81795129</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s">
+        <v>127</v>
+      </c>
+      <c r="C32" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" t="s">
+        <v>257</v>
+      </c>
+      <c r="E32" t="s">
+        <v>274</v>
+      </c>
+      <c r="F32" t="s">
+        <v>282</v>
+      </c>
+      <c r="G32" t="s">
         <v>287</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H32" t="s">
         <v>323</v>
       </c>
-      <c r="J27">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" t="s">
-        <v>209</v>
-      </c>
-      <c r="E28" t="s">
-        <v>278</v>
-      </c>
-      <c r="F28" t="s">
-        <v>282</v>
-      </c>
-      <c r="G28" t="s">
-        <v>288</v>
-      </c>
-      <c r="H28" t="s">
+      <c r="J32">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" t="s">
+        <v>172</v>
+      </c>
+      <c r="E33" t="s">
+        <v>274</v>
+      </c>
+      <c r="F33" t="s">
+        <v>282</v>
+      </c>
+      <c r="G33" t="s">
+        <v>286</v>
+      </c>
+      <c r="H33" t="s">
         <v>307</v>
       </c>
-      <c r="I28" t="s">
-        <v>386</v>
-      </c>
-      <c r="J28">
-        <v>352884.57374953461</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="J33">
+        <v>4354811.166996506</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>275</v>
+      </c>
+      <c r="F34" t="s">
+        <v>282</v>
+      </c>
+      <c r="G34" t="s">
+        <v>286</v>
+      </c>
+      <c r="H34" t="s">
+        <v>307</v>
+      </c>
+      <c r="I34" t="s">
+        <v>375</v>
+      </c>
+      <c r="J34">
+        <v>3064668.693174671</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" t="s">
+        <v>276</v>
+      </c>
+      <c r="F35" t="s">
+        <v>282</v>
+      </c>
+      <c r="G35" t="s">
+        <v>293</v>
+      </c>
+      <c r="H35" t="s">
+        <v>324</v>
+      </c>
+      <c r="J35">
+        <v>9992991.568656314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" t="s">
         <v>44</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C36" t="s">
         <v>175</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E36" t="s">
         <v>276</v>
       </c>
-      <c r="F29" t="s">
-        <v>282</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="F36" t="s">
+        <v>282</v>
+      </c>
+      <c r="G36" t="s">
         <v>293</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H36" t="s">
         <v>324</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I36" t="s">
         <v>376</v>
       </c>
-      <c r="J29">
+      <c r="J36">
         <v>16826817.56129609</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" t="s">
-        <v>227</v>
-      </c>
-      <c r="E30" t="s">
-        <v>279</v>
-      </c>
-      <c r="F30" t="s">
-        <v>282</v>
-      </c>
-      <c r="G30" t="s">
-        <v>288</v>
-      </c>
-      <c r="H30" t="s">
-        <v>307</v>
-      </c>
-      <c r="I30" t="s">
-        <v>368</v>
-      </c>
-      <c r="J30">
-        <v>1445491.9253398541</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
-        <v>144</v>
-      </c>
-      <c r="E31" t="s">
-        <v>271</v>
-      </c>
-      <c r="F31" t="s">
-        <v>282</v>
-      </c>
-      <c r="G31" t="s">
-        <v>287</v>
-      </c>
-      <c r="H31" t="s">
-        <v>307</v>
-      </c>
-      <c r="J31">
-        <v>416736.86034155951</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>224</v>
-      </c>
-      <c r="E32" t="s">
-        <v>279</v>
-      </c>
-      <c r="F32" t="s">
-        <v>284</v>
-      </c>
-      <c r="H32" t="s">
-        <v>348</v>
-      </c>
-      <c r="J32">
-        <v>1267949.1779535899</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" t="s">
-        <v>271</v>
-      </c>
-      <c r="F33" t="s">
-        <v>283</v>
-      </c>
-      <c r="H33" t="s">
-        <v>311</v>
-      </c>
-      <c r="J33">
-        <v>199723.49810779991</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>93</v>
-      </c>
-      <c r="B34" t="s">
-        <v>133</v>
-      </c>
-      <c r="C34" t="s">
-        <v>223</v>
-      </c>
-      <c r="D34" t="s">
-        <v>263</v>
-      </c>
-      <c r="E34" t="s">
-        <v>279</v>
-      </c>
-      <c r="F34" t="s">
-        <v>282</v>
-      </c>
-      <c r="G34" t="s">
-        <v>287</v>
-      </c>
-      <c r="H34" t="s">
-        <v>323</v>
-      </c>
-      <c r="J34">
-        <v>3714363.081590083</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" t="s">
-        <v>191</v>
-      </c>
-      <c r="E35" t="s">
-        <v>278</v>
-      </c>
-      <c r="F35" t="s">
-        <v>282</v>
-      </c>
-      <c r="G35" t="s">
-        <v>291</v>
-      </c>
-      <c r="H35" t="s">
-        <v>307</v>
-      </c>
-      <c r="I35" t="s">
-        <v>380</v>
-      </c>
-      <c r="J35">
-        <v>7405086.2285420913</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" t="s">
-        <v>129</v>
-      </c>
-      <c r="C36" t="s">
-        <v>182</v>
-      </c>
-      <c r="D36" t="s">
-        <v>259</v>
-      </c>
-      <c r="E36" t="s">
-        <v>278</v>
-      </c>
-      <c r="F36" t="s">
-        <v>282</v>
-      </c>
-      <c r="G36" t="s">
-        <v>285</v>
-      </c>
-      <c r="H36" t="s">
-        <v>328</v>
-      </c>
-      <c r="I36" t="s">
-        <v>379</v>
-      </c>
-      <c r="J36">
-        <v>1760913.595839669</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2534,116 +2467,113 @@
         <v>375</v>
       </c>
       <c r="J37">
-        <v>126962.74509226839</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+        <v>126962.7450922684</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>58</v>
-      </c>
-      <c r="B38" t="s">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
-      </c>
-      <c r="D38" t="s">
-        <v>260</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
+        <v>276</v>
+      </c>
+      <c r="F38" t="s">
+        <v>283</v>
+      </c>
+      <c r="H38" t="s">
+        <v>325</v>
+      </c>
+      <c r="J38">
+        <v>771997.9267729169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" t="s">
+        <v>178</v>
+      </c>
+      <c r="E39" t="s">
+        <v>276</v>
+      </c>
+      <c r="F39" t="s">
+        <v>283</v>
+      </c>
+      <c r="H39" t="s">
+        <v>326</v>
+      </c>
+      <c r="J39">
+        <v>2695956.210741678</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" t="s">
+        <v>258</v>
+      </c>
+      <c r="E40" t="s">
+        <v>277</v>
+      </c>
+      <c r="F40" t="s">
+        <v>282</v>
+      </c>
+      <c r="G40" t="s">
+        <v>289</v>
+      </c>
+      <c r="H40" t="s">
+        <v>307</v>
+      </c>
+      <c r="I40" t="s">
+        <v>377</v>
+      </c>
+      <c r="J40">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" t="s">
         <v>278</v>
       </c>
-      <c r="F38" t="s">
-        <v>282</v>
-      </c>
-      <c r="G38" t="s">
-        <v>285</v>
-      </c>
-      <c r="H38" t="s">
-        <v>334</v>
-      </c>
-      <c r="J38">
-        <v>2161806.0909095029</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" t="s">
-        <v>146</v>
-      </c>
-      <c r="E39" t="s">
-        <v>271</v>
-      </c>
-      <c r="F39" t="s">
-        <v>282</v>
-      </c>
-      <c r="G39" t="s">
-        <v>286</v>
-      </c>
-      <c r="H39" t="s">
-        <v>309</v>
-      </c>
-      <c r="I39" t="s">
-        <v>367</v>
-      </c>
-      <c r="J39">
-        <v>22527998.6785</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>22</v>
-      </c>
-      <c r="C40" t="s">
-        <v>153</v>
-      </c>
-      <c r="E40" t="s">
-        <v>271</v>
-      </c>
-      <c r="F40" t="s">
-        <v>283</v>
-      </c>
-      <c r="H40" t="s">
-        <v>313</v>
-      </c>
-      <c r="J40">
-        <v>1931027.417599746</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>107</v>
-      </c>
-      <c r="C41" t="s">
-        <v>237</v>
-      </c>
-      <c r="E41" t="s">
-        <v>279</v>
-      </c>
       <c r="F41" t="s">
         <v>282</v>
       </c>
       <c r="G41" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H41" t="s">
         <v>327</v>
       </c>
       <c r="I41" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="J41">
-        <v>1341835.17078</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+        <v>22789723.43693621</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="E42" t="s">
         <v>278</v>
@@ -2652,53 +2582,62 @@
         <v>282</v>
       </c>
       <c r="G42" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H42" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="I42" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J42">
-        <v>3503071.0617284952</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5804864.894492002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>51</v>
+      </c>
+      <c r="B43" t="s">
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>151</v>
+        <v>182</v>
+      </c>
+      <c r="D43" t="s">
+        <v>259</v>
       </c>
       <c r="E43" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F43" t="s">
         <v>282</v>
       </c>
       <c r="G43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H43" t="s">
-        <v>312</v>
+        <v>328</v>
+      </c>
+      <c r="I43" t="s">
+        <v>379</v>
       </c>
       <c r="J43">
-        <v>63924259.804899998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1760913.595839669</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C44" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="D44" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E44" t="s">
         <v>278</v>
@@ -2707,76 +2646,64 @@
         <v>282</v>
       </c>
       <c r="G44" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H44" t="s">
-        <v>307</v>
+        <v>329</v>
+      </c>
+      <c r="I44" t="s">
+        <v>370</v>
       </c>
       <c r="J44">
-        <v>1141145.8646362079</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+        <v>559241.2641449785</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="C45" t="s">
-        <v>222</v>
-      </c>
-      <c r="D45" t="s">
-        <v>266</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F45" t="s">
-        <v>284</v>
-      </c>
-      <c r="G45" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="H45" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="J45">
-        <v>6630997.3292599991</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2821612.246080229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>121</v>
+        <v>54</v>
       </c>
       <c r="C46" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F46" t="s">
         <v>283</v>
       </c>
       <c r="H46" t="s">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="J46">
-        <v>4345046.9537415411</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2460432.820685903</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" t="s">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>193</v>
-      </c>
-      <c r="D47" t="s">
-        <v>261</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
         <v>278</v>
@@ -2785,148 +2712,151 @@
         <v>282</v>
       </c>
       <c r="G47" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H47" t="s">
         <v>307</v>
       </c>
-      <c r="I47" t="s">
-        <v>381</v>
-      </c>
       <c r="J47">
-        <v>15428020.65126922</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3512631.992361845</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C48" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F48" t="s">
         <v>283</v>
       </c>
       <c r="H48" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="J48">
-        <v>5776459.4296462554</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>367462.345355</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>57</v>
+      </c>
+      <c r="B49" t="s">
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>254</v>
+        <v>188</v>
+      </c>
+      <c r="D49" t="s">
+        <v>259</v>
       </c>
       <c r="E49" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F49" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G49" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="H49" t="s">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="J49">
-        <v>5293594.021862885</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6838840.246701591</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="D50" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="E50" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F50" t="s">
         <v>282</v>
       </c>
       <c r="G50" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="H50" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="J50">
-        <v>10235647.18904726</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2161806.090909503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C51" t="s">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="E51" t="s">
         <v>278</v>
       </c>
       <c r="F51" t="s">
-        <v>282</v>
-      </c>
-      <c r="G51" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="H51" t="s">
-        <v>343</v>
-      </c>
-      <c r="I51" t="s">
-        <v>389</v>
+        <v>335</v>
       </c>
       <c r="J51">
-        <v>4202253.5385999996</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>124954.6686331536</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>101</v>
+        <v>60</v>
       </c>
       <c r="C52" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="E52" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F52" t="s">
         <v>282</v>
       </c>
       <c r="G52" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="H52" t="s">
         <v>307</v>
       </c>
       <c r="I52" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="J52">
-        <v>3436361.1128654238</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7405086.228542091</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>61</v>
+      </c>
+      <c r="B53" t="s">
+        <v>130</v>
       </c>
       <c r="C53" t="s">
-        <v>205</v>
+        <v>192</v>
+      </c>
+      <c r="D53" t="s">
+        <v>260</v>
       </c>
       <c r="E53" t="s">
         <v>278</v>
@@ -2935,206 +2865,200 @@
         <v>282</v>
       </c>
       <c r="G53" t="s">
+        <v>285</v>
+      </c>
+      <c r="H53" t="s">
+        <v>334</v>
+      </c>
+      <c r="J53">
+        <v>1929968.176370687</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" t="s">
+        <v>193</v>
+      </c>
+      <c r="D54" t="s">
+        <v>261</v>
+      </c>
+      <c r="E54" t="s">
+        <v>278</v>
+      </c>
+      <c r="F54" t="s">
+        <v>282</v>
+      </c>
+      <c r="G54" t="s">
+        <v>285</v>
+      </c>
+      <c r="H54" t="s">
+        <v>307</v>
+      </c>
+      <c r="I54" t="s">
+        <v>381</v>
+      </c>
+      <c r="J54">
+        <v>15428020.65126922</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" t="s">
+        <v>278</v>
+      </c>
+      <c r="F55" t="s">
+        <v>283</v>
+      </c>
+      <c r="H55" t="s">
+        <v>336</v>
+      </c>
+      <c r="J55">
+        <v>515060.9564426438</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" t="s">
+        <v>260</v>
+      </c>
+      <c r="E56" t="s">
+        <v>278</v>
+      </c>
+      <c r="F56" t="s">
+        <v>284</v>
+      </c>
+      <c r="G56" t="s">
+        <v>296</v>
+      </c>
+      <c r="H56" t="s">
+        <v>337</v>
+      </c>
+      <c r="J56">
+        <v>3963061.644481355</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" t="s">
+        <v>196</v>
+      </c>
+      <c r="E57" t="s">
+        <v>278</v>
+      </c>
+      <c r="F57" t="s">
+        <v>283</v>
+      </c>
+      <c r="H57" t="s">
+        <v>338</v>
+      </c>
+      <c r="J57">
+        <v>788132.0847764658</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" t="s">
+        <v>197</v>
+      </c>
+      <c r="D58" t="s">
+        <v>260</v>
+      </c>
+      <c r="E58" t="s">
+        <v>278</v>
+      </c>
+      <c r="F58" t="s">
+        <v>282</v>
+      </c>
+      <c r="G58" t="s">
+        <v>285</v>
+      </c>
+      <c r="H58" t="s">
+        <v>334</v>
+      </c>
+      <c r="J58">
+        <v>110803.8657774448</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" t="s">
+        <v>198</v>
+      </c>
+      <c r="E59" t="s">
+        <v>278</v>
+      </c>
+      <c r="F59" t="s">
+        <v>282</v>
+      </c>
+      <c r="G59" t="s">
         <v>291</v>
       </c>
-      <c r="H53" t="s">
-        <v>341</v>
-      </c>
-      <c r="I53" t="s">
-        <v>385</v>
-      </c>
-      <c r="J53">
-        <v>8409093.1265900005</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>113</v>
-      </c>
-      <c r="B54" t="s">
-        <v>134</v>
-      </c>
-      <c r="C54" t="s">
-        <v>243</v>
-      </c>
-      <c r="D54" t="s">
-        <v>264</v>
-      </c>
-      <c r="E54" t="s">
-        <v>279</v>
-      </c>
-      <c r="F54" t="s">
-        <v>282</v>
-      </c>
-      <c r="G54" t="s">
-        <v>287</v>
-      </c>
-      <c r="H54" t="s">
-        <v>358</v>
-      </c>
-      <c r="I54" t="s">
-        <v>399</v>
-      </c>
-      <c r="J54">
-        <v>2331098.7137656999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" t="s">
-        <v>126</v>
-      </c>
-      <c r="C55" t="s">
-        <v>158</v>
-      </c>
-      <c r="D55" t="s">
-        <v>256</v>
-      </c>
-      <c r="E55" t="s">
-        <v>272</v>
-      </c>
-      <c r="F55" t="s">
-        <v>282</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="H59" t="s">
+        <v>307</v>
+      </c>
+      <c r="I59" t="s">
+        <v>382</v>
+      </c>
+      <c r="J59">
+        <v>3503071.061728495</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" t="s">
+        <v>199</v>
+      </c>
+      <c r="E60" t="s">
+        <v>278</v>
+      </c>
+      <c r="F60" t="s">
+        <v>282</v>
+      </c>
+      <c r="G60" t="s">
         <v>285</v>
       </c>
-      <c r="H55" t="s">
-        <v>317</v>
-      </c>
-      <c r="I55" t="s">
-        <v>371</v>
-      </c>
-      <c r="J55">
-        <v>363438.296974</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" t="s">
-        <v>245</v>
-      </c>
-      <c r="E56" t="s">
-        <v>279</v>
-      </c>
-      <c r="F56" t="s">
-        <v>282</v>
-      </c>
-      <c r="G56" t="s">
-        <v>288</v>
-      </c>
-      <c r="H56" t="s">
-        <v>307</v>
-      </c>
-      <c r="J56">
-        <v>11904079.93924279</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>111</v>
-      </c>
-      <c r="C57" t="s">
-        <v>241</v>
-      </c>
-      <c r="E57" t="s">
-        <v>279</v>
-      </c>
-      <c r="F57" t="s">
-        <v>282</v>
-      </c>
-      <c r="G57" t="s">
-        <v>288</v>
-      </c>
-      <c r="H57" t="s">
-        <v>357</v>
-      </c>
-      <c r="I57" t="s">
-        <v>397</v>
-      </c>
-      <c r="J57">
-        <v>5574423.9812850002</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>89</v>
-      </c>
-      <c r="B58" t="s">
-        <v>134</v>
-      </c>
-      <c r="C58" t="s">
-        <v>219</v>
-      </c>
-      <c r="D58" t="s">
-        <v>264</v>
-      </c>
-      <c r="E58" t="s">
-        <v>279</v>
-      </c>
-      <c r="F58" t="s">
-        <v>283</v>
-      </c>
-      <c r="H58" t="s">
-        <v>345</v>
-      </c>
-      <c r="J58">
-        <v>346083.46304915362</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>38</v>
-      </c>
-      <c r="C59" t="s">
-        <v>169</v>
-      </c>
-      <c r="E59" t="s">
-        <v>274</v>
-      </c>
-      <c r="F59" t="s">
-        <v>284</v>
-      </c>
-      <c r="G59" t="s">
-        <v>292</v>
-      </c>
-      <c r="H59" t="s">
-        <v>315</v>
-      </c>
-      <c r="J59">
-        <v>681889.99643018574</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>25</v>
-      </c>
-      <c r="C60" t="s">
-        <v>156</v>
-      </c>
-      <c r="E60" t="s">
-        <v>272</v>
-      </c>
-      <c r="F60" t="s">
-        <v>283</v>
-      </c>
       <c r="H60" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="J60">
-        <v>5670439.7954879999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+        <v>989146.0724139999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="E61" t="s">
         <v>278</v>
@@ -3146,21 +3070,21 @@
         <v>288</v>
       </c>
       <c r="H61" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="I61" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="J61">
-        <v>5804864.8944920022</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1874190.45757726</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C62" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E62" t="s">
         <v>278</v>
@@ -3169,99 +3093,96 @@
         <v>282</v>
       </c>
       <c r="G62" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H62" t="s">
         <v>327</v>
       </c>
+      <c r="I62" t="s">
+        <v>384</v>
+      </c>
       <c r="J62">
-        <v>240468.70558949231</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6139378.49533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" t="s">
-        <v>65</v>
+        <v>71</v>
+      </c>
+      <c r="B63" t="s">
+        <v>131</v>
       </c>
       <c r="C63" t="s">
-        <v>196</v>
+        <v>202</v>
+      </c>
+      <c r="D63" t="s">
+        <v>261</v>
       </c>
       <c r="E63" t="s">
         <v>278</v>
       </c>
       <c r="F63" t="s">
+        <v>282</v>
+      </c>
+      <c r="G63" t="s">
+        <v>287</v>
+      </c>
+      <c r="H63" t="s">
+        <v>307</v>
+      </c>
+      <c r="J63">
+        <v>1141145.864636208</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+      <c r="C64" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" t="s">
+        <v>278</v>
+      </c>
+      <c r="F64" t="s">
+        <v>282</v>
+      </c>
+      <c r="G64" t="s">
+        <v>286</v>
+      </c>
+      <c r="H64" t="s">
+        <v>327</v>
+      </c>
+      <c r="J64">
+        <v>240468.7055894923</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" t="s">
+        <v>73</v>
+      </c>
+      <c r="C65" t="s">
+        <v>204</v>
+      </c>
+      <c r="E65" t="s">
+        <v>278</v>
+      </c>
+      <c r="F65" t="s">
         <v>283</v>
       </c>
-      <c r="H63" t="s">
-        <v>338</v>
-      </c>
-      <c r="J63">
-        <v>788132.08477646578</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>123</v>
-      </c>
-      <c r="B64" t="s">
-        <v>140</v>
-      </c>
-      <c r="C64" t="s">
-        <v>253</v>
-      </c>
-      <c r="D64" t="s">
-        <v>270</v>
-      </c>
-      <c r="E64" t="s">
-        <v>280</v>
-      </c>
-      <c r="F64" t="s">
-        <v>282</v>
-      </c>
-      <c r="G64" t="s">
-        <v>285</v>
-      </c>
-      <c r="H64" t="s">
-        <v>359</v>
-      </c>
-      <c r="J64">
-        <v>1973892.4554655049</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>118</v>
-      </c>
-      <c r="B65" t="s">
-        <v>139</v>
-      </c>
-      <c r="C65" t="s">
-        <v>248</v>
-      </c>
-      <c r="D65" t="s">
-        <v>269</v>
-      </c>
-      <c r="E65" t="s">
-        <v>280</v>
-      </c>
-      <c r="F65" t="s">
-        <v>282</v>
-      </c>
-      <c r="G65" t="s">
-        <v>289</v>
-      </c>
       <c r="H65" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="J65">
-        <v>4412887.4395813216</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+        <v>242518.965983</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C66" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E66" t="s">
         <v>278</v>
@@ -3270,119 +3191,128 @@
         <v>282</v>
       </c>
       <c r="G66" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="H66" t="s">
-        <v>339</v>
+        <v>341</v>
+      </c>
+      <c r="I66" t="s">
+        <v>385</v>
       </c>
       <c r="J66">
-        <v>989146.07241399994</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+        <v>8409093.12659</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="C67" t="s">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="E67" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F67" t="s">
+        <v>282</v>
+      </c>
+      <c r="G67" t="s">
+        <v>286</v>
+      </c>
+      <c r="H67" t="s">
+        <v>307</v>
+      </c>
+      <c r="I67" t="s">
+        <v>386</v>
+      </c>
+      <c r="J67">
+        <v>10276967.10066929</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" t="s">
+        <v>76</v>
+      </c>
+      <c r="C68" t="s">
+        <v>207</v>
+      </c>
+      <c r="E68" t="s">
+        <v>278</v>
+      </c>
+      <c r="F68" t="s">
         <v>283</v>
       </c>
-      <c r="H67" t="s">
-        <v>360</v>
-      </c>
-      <c r="J67">
-        <v>708761.41470578162</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>48</v>
-      </c>
-      <c r="B68" t="s">
-        <v>128</v>
-      </c>
-      <c r="C68" t="s">
-        <v>179</v>
-      </c>
-      <c r="D68" t="s">
-        <v>258</v>
-      </c>
-      <c r="E68" t="s">
-        <v>277</v>
-      </c>
-      <c r="F68" t="s">
-        <v>282</v>
-      </c>
-      <c r="G68" t="s">
-        <v>289</v>
-      </c>
       <c r="H68" t="s">
+        <v>342</v>
+      </c>
+      <c r="J68">
+        <v>386230.806039</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" t="s">
+        <v>77</v>
+      </c>
+      <c r="C69" t="s">
+        <v>208</v>
+      </c>
+      <c r="E69" t="s">
+        <v>278</v>
+      </c>
+      <c r="F69" t="s">
+        <v>282</v>
+      </c>
+      <c r="G69" t="s">
+        <v>287</v>
+      </c>
+      <c r="H69" t="s">
         <v>307</v>
       </c>
-      <c r="I68" t="s">
-        <v>377</v>
-      </c>
-      <c r="J68">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>37</v>
-      </c>
-      <c r="C69" t="s">
-        <v>168</v>
-      </c>
-      <c r="E69" t="s">
-        <v>274</v>
-      </c>
-      <c r="F69" t="s">
-        <v>282</v>
-      </c>
-      <c r="G69" t="s">
-        <v>285</v>
-      </c>
-      <c r="H69" t="s">
-        <v>308</v>
+      <c r="I69" t="s">
+        <v>387</v>
       </c>
       <c r="J69">
-        <v>1510729.3693091241</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+        <v>948677.9026767507</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="C70" t="s">
-        <v>255</v>
+        <v>209</v>
       </c>
       <c r="E70" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F70" t="s">
         <v>282</v>
       </c>
       <c r="G70" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H70" t="s">
-        <v>308</v>
+        <v>307</v>
+      </c>
+      <c r="I70" t="s">
+        <v>386</v>
       </c>
       <c r="J70">
-        <v>3418676.16080696</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+        <v>352884.5737495346</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="B71" t="s">
+        <v>130</v>
       </c>
       <c r="C71" t="s">
-        <v>208</v>
+        <v>210</v>
+      </c>
+      <c r="D71" t="s">
+        <v>260</v>
       </c>
       <c r="E71" t="s">
         <v>278</v>
@@ -3391,146 +3321,164 @@
         <v>282</v>
       </c>
       <c r="G71" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H71" t="s">
+        <v>334</v>
+      </c>
+      <c r="J71">
+        <v>3063892.805082795</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" t="s">
+        <v>129</v>
+      </c>
+      <c r="C72" t="s">
+        <v>211</v>
+      </c>
+      <c r="D72" t="s">
+        <v>259</v>
+      </c>
+      <c r="E72" t="s">
+        <v>278</v>
+      </c>
+      <c r="F72" t="s">
+        <v>282</v>
+      </c>
+      <c r="G72" t="s">
+        <v>289</v>
+      </c>
+      <c r="H72" t="s">
+        <v>334</v>
+      </c>
+      <c r="I72" t="s">
+        <v>379</v>
+      </c>
+      <c r="J72">
+        <v>1039802.195699128</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" t="s">
+        <v>130</v>
+      </c>
+      <c r="C73" t="s">
+        <v>195</v>
+      </c>
+      <c r="D73" t="s">
+        <v>260</v>
+      </c>
+      <c r="E73" t="s">
+        <v>278</v>
+      </c>
+      <c r="F73" t="s">
+        <v>282</v>
+      </c>
+      <c r="G73" t="s">
+        <v>285</v>
+      </c>
+      <c r="H73" t="s">
+        <v>334</v>
+      </c>
+      <c r="J73">
+        <v>21591249.4628</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" t="s">
+        <v>212</v>
+      </c>
+      <c r="D74" t="s">
+        <v>262</v>
+      </c>
+      <c r="E74" t="s">
+        <v>278</v>
+      </c>
+      <c r="F74" t="s">
+        <v>282</v>
+      </c>
+      <c r="G74" t="s">
+        <v>285</v>
+      </c>
+      <c r="H74" t="s">
         <v>307</v>
       </c>
-      <c r="I71" t="s">
-        <v>387</v>
-      </c>
-      <c r="J71">
-        <v>948677.90267675067</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>87</v>
-      </c>
-      <c r="B72" t="s">
-        <v>133</v>
-      </c>
-      <c r="C72" t="s">
-        <v>217</v>
-      </c>
-      <c r="D72" t="s">
-        <v>263</v>
-      </c>
-      <c r="E72" t="s">
-        <v>279</v>
-      </c>
-      <c r="F72" t="s">
-        <v>282</v>
-      </c>
-      <c r="G72" t="s">
-        <v>286</v>
-      </c>
-      <c r="H72" t="s">
-        <v>323</v>
-      </c>
-      <c r="I72" t="s">
-        <v>390</v>
-      </c>
-      <c r="J72">
-        <v>24972920.132110279</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C73" t="s">
-        <v>173</v>
-      </c>
-      <c r="E73" t="s">
-        <v>275</v>
-      </c>
-      <c r="F73" t="s">
-        <v>282</v>
-      </c>
-      <c r="G73" t="s">
-        <v>286</v>
-      </c>
-      <c r="H73" t="s">
-        <v>307</v>
-      </c>
-      <c r="I73" t="s">
-        <v>375</v>
-      </c>
-      <c r="J73">
-        <v>3064668.6931746709</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" t="s">
-        <v>154</v>
-      </c>
-      <c r="E74" t="s">
-        <v>271</v>
-      </c>
-      <c r="F74" t="s">
-        <v>282</v>
-      </c>
-      <c r="G74" t="s">
-        <v>286</v>
-      </c>
-      <c r="H74" t="s">
-        <v>308</v>
-      </c>
       <c r="I74" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="J74">
-        <v>12606786.4826</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
       <c r="C75" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="E75" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="F75" t="s">
         <v>282</v>
       </c>
       <c r="G75" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H75" t="s">
-        <v>306</v>
+        <v>343</v>
+      </c>
+      <c r="I75" t="s">
+        <v>389</v>
       </c>
       <c r="J75">
-        <v>7967834.6375599997</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4202253.5386</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>84</v>
+      </c>
+      <c r="B76" t="s">
+        <v>129</v>
       </c>
       <c r="C76" t="s">
-        <v>162</v>
+        <v>214</v>
+      </c>
+      <c r="D76" t="s">
+        <v>259</v>
       </c>
       <c r="E76" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F76" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G76" t="s">
+        <v>285</v>
       </c>
       <c r="H76" t="s">
-        <v>319</v>
+        <v>344</v>
       </c>
       <c r="J76">
-        <v>255208.96920799999</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1788407.819274</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -3556,151 +3504,148 @@
         <v>1550354.452950391</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10">
       <c r="A78" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>216</v>
       </c>
       <c r="E78" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F78" t="s">
         <v>282</v>
       </c>
       <c r="G78" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="H78" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="I78" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="J78">
-        <v>1499689.8654100001</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7249147.17667</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" t="s">
-        <v>18</v>
+        <v>87</v>
+      </c>
+      <c r="B79" t="s">
+        <v>133</v>
       </c>
       <c r="C79" t="s">
-        <v>149</v>
+        <v>217</v>
+      </c>
+      <c r="D79" t="s">
+        <v>263</v>
       </c>
       <c r="E79" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F79" t="s">
         <v>282</v>
       </c>
       <c r="G79" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H79" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="I79" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="J79">
-        <v>4950459.91493</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>24972920.13211028</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" t="s">
-        <v>28</v>
-      </c>
-      <c r="B80" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="C80" t="s">
-        <v>159</v>
-      </c>
-      <c r="D80" t="s">
-        <v>256</v>
+        <v>218</v>
       </c>
       <c r="E80" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F80" t="s">
         <v>282</v>
       </c>
       <c r="G80" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H80" t="s">
-        <v>313</v>
-      </c>
-      <c r="I80" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="J80">
-        <v>2410689.2217360381</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+        <v>15702687.60491092</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B81" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C81" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D81" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="E81" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F81" t="s">
-        <v>282</v>
-      </c>
-      <c r="G81" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H81" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J81">
-        <v>1788407.8192739999</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+        <v>346083.4630491536</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>90</v>
+      </c>
+      <c r="B82" t="s">
+        <v>135</v>
       </c>
       <c r="C82" t="s">
-        <v>232</v>
+        <v>220</v>
+      </c>
+      <c r="D82" t="s">
+        <v>265</v>
       </c>
       <c r="E82" t="s">
         <v>279</v>
       </c>
       <c r="F82" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G82" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="H82" t="s">
-        <v>353</v>
-      </c>
-      <c r="I82" t="s">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="J82">
-        <v>2323252.9267690452</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1250800.940065123</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C83" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="E83" t="s">
         <v>279</v>
@@ -3709,225 +3654,249 @@
         <v>282</v>
       </c>
       <c r="G83" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="H83" t="s">
-        <v>345</v>
+        <v>324</v>
+      </c>
+      <c r="I83" t="s">
+        <v>391</v>
       </c>
       <c r="J83">
-        <v>2689687.0630099322</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+        <v>280723.3006520429</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>92</v>
+      </c>
+      <c r="B84" t="s">
+        <v>136</v>
       </c>
       <c r="C84" t="s">
-        <v>165</v>
+        <v>222</v>
+      </c>
+      <c r="D84" t="s">
+        <v>266</v>
       </c>
       <c r="E84" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F84" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G84" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="H84" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="J84">
-        <v>163254.62437129</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6630997.329259999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>93</v>
+      </c>
+      <c r="B85" t="s">
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>184</v>
+        <v>223</v>
+      </c>
+      <c r="D85" t="s">
+        <v>263</v>
       </c>
       <c r="E85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F85" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G85" t="s">
+        <v>287</v>
       </c>
       <c r="H85" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="J85">
-        <v>2821612.2460802291</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3714363.081590083</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="C86" t="s">
-        <v>148</v>
+        <v>224</v>
       </c>
       <c r="E86" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F86" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H86" t="s">
-        <v>310</v>
+        <v>348</v>
       </c>
       <c r="J86">
-        <v>7682504.7611060319</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1267949.17795359</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="C87" t="s">
-        <v>178</v>
+        <v>225</v>
       </c>
       <c r="E87" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F87" t="s">
         <v>283</v>
       </c>
       <c r="H87" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="J87">
-        <v>2695956.2107416778</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+        <v>848008.505874</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="C88" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="E88" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F88" t="s">
-        <v>282</v>
-      </c>
-      <c r="G88" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H88" t="s">
-        <v>307</v>
+        <v>350</v>
       </c>
       <c r="J88">
-        <v>4354811.166996506</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+        <v>148601.7043568496</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="C89" t="s">
-        <v>186</v>
+        <v>227</v>
       </c>
       <c r="E89" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F89" t="s">
         <v>282</v>
       </c>
       <c r="G89" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H89" t="s">
         <v>307</v>
       </c>
+      <c r="I89" t="s">
+        <v>368</v>
+      </c>
       <c r="J89">
-        <v>3512631.992361845</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1445491.925339854</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" t="s">
-        <v>46</v>
+        <v>98</v>
+      </c>
+      <c r="B90" t="s">
+        <v>135</v>
       </c>
       <c r="C90" t="s">
-        <v>177</v>
+        <v>228</v>
+      </c>
+      <c r="D90" t="s">
+        <v>265</v>
       </c>
       <c r="E90" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="F90" t="s">
-        <v>283</v>
+        <v>284</v>
+      </c>
+      <c r="G90" t="s">
+        <v>297</v>
       </c>
       <c r="H90" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="J90">
-        <v>771997.92677291692</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+        <v>741138.9596083837</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" t="s">
-        <v>103</v>
+        <v>99</v>
+      </c>
+      <c r="B91" t="s">
+        <v>137</v>
       </c>
       <c r="C91" t="s">
-        <v>233</v>
+        <v>229</v>
+      </c>
+      <c r="D91" t="s">
+        <v>267</v>
       </c>
       <c r="E91" t="s">
         <v>279</v>
       </c>
       <c r="F91" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G91" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H91" t="s">
-        <v>354</v>
-      </c>
-      <c r="I91" t="s">
-        <v>393</v>
+        <v>351</v>
       </c>
       <c r="J91">
-        <v>2475749.7725005322</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1113481.921945367</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="C92" t="s">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="E92" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F92" t="s">
-        <v>282</v>
-      </c>
-      <c r="G92" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="H92" t="s">
-        <v>327</v>
-      </c>
-      <c r="I92" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="J92">
-        <v>22789723.436936211</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+        <v>899806.3255054827</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" t="s">
-        <v>16</v>
+        <v>101</v>
       </c>
       <c r="C93" t="s">
-        <v>147</v>
+        <v>231</v>
       </c>
       <c r="E93" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F93" t="s">
         <v>282</v>
@@ -3936,24 +3905,24 @@
         <v>286</v>
       </c>
       <c r="H93" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I93" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="J93">
-        <v>11531646.543500001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3436361.112865424</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="C94" t="s">
-        <v>201</v>
+        <v>232</v>
       </c>
       <c r="E94" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F94" t="s">
         <v>282</v>
@@ -3962,21 +3931,21 @@
         <v>288</v>
       </c>
       <c r="H94" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="I94" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="J94">
-        <v>6139378.4953300003</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2323252.926769045</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="C95" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="E95" t="s">
         <v>279</v>
@@ -3985,111 +3954,111 @@
         <v>282</v>
       </c>
       <c r="G95" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H95" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="I95" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J95">
-        <v>280723.3006520429</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2475749.772500532</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="C96" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="E96" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F96" t="s">
-        <v>282</v>
-      </c>
-      <c r="G96" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H96" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="J96">
-        <v>10572188.566137601</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+        <v>9487628.08633</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>105</v>
       </c>
       <c r="C97" t="s">
-        <v>163</v>
+        <v>235</v>
       </c>
       <c r="E97" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F97" t="s">
         <v>283</v>
       </c>
       <c r="H97" t="s">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="J97">
-        <v>86936203.291251481</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>333307.1237192919</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" t="s">
-        <v>116</v>
-      </c>
-      <c r="B98" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C98" t="s">
-        <v>246</v>
-      </c>
-      <c r="D98" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="E98" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F98" t="s">
         <v>282</v>
       </c>
       <c r="G98" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H98" t="s">
-        <v>307</v>
+        <v>327</v>
+      </c>
+      <c r="I98" t="s">
+        <v>394</v>
       </c>
       <c r="J98">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6202897.01714</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C99" t="s">
-        <v>194</v>
+        <v>237</v>
       </c>
       <c r="E99" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F99" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G99" t="s">
+        <v>288</v>
       </c>
       <c r="H99" t="s">
-        <v>336</v>
+        <v>327</v>
+      </c>
+      <c r="I99" t="s">
+        <v>395</v>
       </c>
       <c r="J99">
-        <v>515060.95644264377</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1341835.17078</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -4112,437 +4081,437 @@
         <v>396</v>
       </c>
       <c r="J100">
-        <v>1113516.5997299999</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1113516.59973</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" t="s">
-        <v>24</v>
-      </c>
-      <c r="B101" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="C101" t="s">
-        <v>155</v>
-      </c>
-      <c r="D101" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="E101" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F101" t="s">
         <v>282</v>
       </c>
       <c r="G101" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="H101" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="J101">
-        <v>330003.3338055482</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2689687.063009932</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" t="s">
-        <v>80</v>
-      </c>
-      <c r="B102" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="C102" t="s">
-        <v>211</v>
-      </c>
-      <c r="D102" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="E102" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F102" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G102" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="H102" t="s">
-        <v>334</v>
-      </c>
-      <c r="I102" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="J102">
-        <v>1039802.195699128</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1248584.67151726</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" t="s">
-        <v>57</v>
-      </c>
-      <c r="B103" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="C103" t="s">
-        <v>188</v>
-      </c>
-      <c r="D103" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="E103" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F103" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G103" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="H103" t="s">
-        <v>333</v>
+        <v>357</v>
+      </c>
+      <c r="I103" t="s">
+        <v>397</v>
       </c>
       <c r="J103">
-        <v>6838840.2467015907</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5574423.981285</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
       <c r="A104" t="s">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="C104" t="s">
-        <v>187</v>
+        <v>242</v>
       </c>
       <c r="E104" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F104" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G104" t="s">
+        <v>286</v>
       </c>
       <c r="H104" t="s">
-        <v>332</v>
+        <v>327</v>
+      </c>
+      <c r="I104" t="s">
+        <v>398</v>
       </c>
       <c r="J104">
-        <v>367462.345355</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+        <v>19028718.4515658</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105" t="s">
-        <v>26</v>
+        <v>113</v>
+      </c>
+      <c r="B105" t="s">
+        <v>134</v>
       </c>
       <c r="C105" t="s">
-        <v>157</v>
+        <v>243</v>
+      </c>
+      <c r="D105" t="s">
+        <v>264</v>
       </c>
       <c r="E105" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F105" t="s">
         <v>282</v>
       </c>
       <c r="G105" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H105" t="s">
-        <v>316</v>
+        <v>358</v>
+      </c>
+      <c r="I105" t="s">
+        <v>399</v>
       </c>
       <c r="J105">
-        <v>1058100.0927489479</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2331098.7137657</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
       <c r="A106" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C106" t="s">
-        <v>185</v>
+        <v>244</v>
       </c>
       <c r="E106" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F106" t="s">
         <v>283</v>
       </c>
       <c r="H106" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="J106">
-        <v>2460432.8206859031</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>6417855.902150526</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107" t="s">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="C107" t="s">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="E107" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F107" t="s">
         <v>282</v>
       </c>
       <c r="G107" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H107" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="J107">
-        <v>7481998.4830510933</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+        <v>11904079.93924279</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10">
       <c r="A108" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B108" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C108" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="D108" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E108" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F108" t="s">
         <v>282</v>
       </c>
       <c r="G108" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H108" t="s">
         <v>307</v>
       </c>
-      <c r="I108" t="s">
-        <v>388</v>
-      </c>
       <c r="J108">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10">
       <c r="A109" t="s">
-        <v>52</v>
-      </c>
-      <c r="B109" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="C109" t="s">
-        <v>183</v>
-      </c>
-      <c r="D109" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="E109" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F109" t="s">
-        <v>282</v>
-      </c>
-      <c r="G109" t="s">
+        <v>283</v>
+      </c>
+      <c r="H109" t="s">
+        <v>359</v>
+      </c>
+      <c r="J109">
+        <v>189687.8885015327</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
+      <c r="A110" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" t="s">
+        <v>139</v>
+      </c>
+      <c r="C110" t="s">
+        <v>248</v>
+      </c>
+      <c r="D110" t="s">
+        <v>269</v>
+      </c>
+      <c r="E110" t="s">
+        <v>280</v>
+      </c>
+      <c r="F110" t="s">
+        <v>282</v>
+      </c>
+      <c r="G110" t="s">
+        <v>289</v>
+      </c>
+      <c r="H110" t="s">
+        <v>359</v>
+      </c>
+      <c r="J110">
+        <v>4412887.439581322</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10">
+      <c r="A111" t="s">
+        <v>119</v>
+      </c>
+      <c r="C111" t="s">
+        <v>249</v>
+      </c>
+      <c r="E111" t="s">
+        <v>280</v>
+      </c>
+      <c r="F111" t="s">
+        <v>283</v>
+      </c>
+      <c r="H111" t="s">
+        <v>360</v>
+      </c>
+      <c r="J111">
+        <v>708761.4147057816</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" t="s">
+        <v>139</v>
+      </c>
+      <c r="C112" t="s">
+        <v>250</v>
+      </c>
+      <c r="D112" t="s">
+        <v>269</v>
+      </c>
+      <c r="E112" t="s">
+        <v>280</v>
+      </c>
+      <c r="F112" t="s">
+        <v>282</v>
+      </c>
+      <c r="G112" t="s">
         <v>285</v>
       </c>
-      <c r="H109" t="s">
-        <v>329</v>
-      </c>
-      <c r="I109" t="s">
-        <v>370</v>
-      </c>
-      <c r="J109">
-        <v>559241.26414497849</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>104</v>
-      </c>
-      <c r="C110" t="s">
-        <v>234</v>
-      </c>
-      <c r="E110" t="s">
-        <v>279</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="H112" t="s">
+        <v>359</v>
+      </c>
+      <c r="I112" t="s">
+        <v>368</v>
+      </c>
+      <c r="J112">
+        <v>1600590.119251437</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10">
+      <c r="A113" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" t="s">
+        <v>251</v>
+      </c>
+      <c r="E113" t="s">
+        <v>280</v>
+      </c>
+      <c r="F113" t="s">
         <v>283</v>
       </c>
-      <c r="H110" t="s">
-        <v>306</v>
-      </c>
-      <c r="J110">
-        <v>9487628.0863300003</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>99</v>
-      </c>
-      <c r="B111" t="s">
-        <v>137</v>
-      </c>
-      <c r="C111" t="s">
-        <v>229</v>
-      </c>
-      <c r="D111" t="s">
-        <v>267</v>
-      </c>
-      <c r="E111" t="s">
-        <v>279</v>
-      </c>
-      <c r="F111" t="s">
-        <v>284</v>
-      </c>
-      <c r="G111" t="s">
-        <v>292</v>
-      </c>
-      <c r="H111" t="s">
-        <v>351</v>
-      </c>
-      <c r="J111">
-        <v>1113481.921945367</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>73</v>
-      </c>
-      <c r="C112" t="s">
-        <v>204</v>
-      </c>
-      <c r="E112" t="s">
-        <v>278</v>
-      </c>
-      <c r="F112" t="s">
-        <v>283</v>
-      </c>
-      <c r="H112" t="s">
-        <v>340</v>
-      </c>
-      <c r="J112">
-        <v>242518.965983</v>
-      </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>33</v>
-      </c>
-      <c r="C113" t="s">
-        <v>164</v>
-      </c>
-      <c r="E113" t="s">
-        <v>274</v>
-      </c>
-      <c r="F113" t="s">
-        <v>282</v>
-      </c>
-      <c r="G113" t="s">
-        <v>291</v>
-      </c>
       <c r="H113" t="s">
-        <v>315</v>
-      </c>
-      <c r="I113" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="J113">
-        <v>4789014.0375600001</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4345046.953741541</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>122</v>
+      </c>
+      <c r="B114" t="s">
+        <v>140</v>
       </c>
       <c r="C114" t="s">
-        <v>247</v>
+        <v>252</v>
+      </c>
+      <c r="D114" t="s">
+        <v>270</v>
       </c>
       <c r="E114" t="s">
         <v>280</v>
       </c>
       <c r="F114" t="s">
-        <v>283</v>
+        <v>282</v>
+      </c>
+      <c r="G114" t="s">
+        <v>289</v>
       </c>
       <c r="H114" t="s">
         <v>359</v>
       </c>
       <c r="J114">
-        <v>189687.8885015327</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10235647.18904726</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10">
       <c r="A115" t="s">
-        <v>86</v>
+        <v>123</v>
+      </c>
+      <c r="B115" t="s">
+        <v>140</v>
       </c>
       <c r="C115" t="s">
-        <v>216</v>
+        <v>253</v>
+      </c>
+      <c r="D115" t="s">
+        <v>270</v>
       </c>
       <c r="E115" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F115" t="s">
         <v>282</v>
       </c>
       <c r="G115" t="s">
+        <v>285</v>
+      </c>
+      <c r="H115" t="s">
+        <v>359</v>
+      </c>
+      <c r="J115">
+        <v>1973892.455465505</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10">
+      <c r="A116" t="s">
+        <v>124</v>
+      </c>
+      <c r="C116" t="s">
+        <v>254</v>
+      </c>
+      <c r="E116" t="s">
+        <v>281</v>
+      </c>
+      <c r="F116" t="s">
+        <v>282</v>
+      </c>
+      <c r="G116" t="s">
         <v>288</v>
       </c>
-      <c r="H115" t="s">
-        <v>327</v>
-      </c>
-      <c r="I115" t="s">
-        <v>370</v>
-      </c>
-      <c r="J115">
-        <v>7249147.17667</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>100</v>
-      </c>
-      <c r="C116" t="s">
-        <v>230</v>
-      </c>
-      <c r="E116" t="s">
-        <v>279</v>
-      </c>
-      <c r="F116" t="s">
-        <v>283</v>
-      </c>
       <c r="H116" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="J116">
-        <v>899806.32550548273</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+        <v>5293594.021862885</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="C117" t="s">
-        <v>200</v>
+        <v>255</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F117" t="s">
         <v>282</v>
       </c>
       <c r="G117" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H117" t="s">
-        <v>307</v>
-      </c>
-      <c r="I117" t="s">
-        <v>383</v>
+        <v>308</v>
       </c>
       <c r="J117">
-        <v>1874190.45757726</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+        <v>3418676.16080696</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10">
       <c r="B118" t="s">
         <v>128</v>
       </c>
@@ -4562,10 +4531,10 @@
         <v>377</v>
       </c>
       <c r="J118">
-        <v>7644288.8516325541</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+        <v>7644288.851632554</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="B119" t="s">
         <v>131</v>
       </c>
@@ -4585,10 +4554,10 @@
         <v>381</v>
       </c>
       <c r="J119">
-        <v>16569166.515905419</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+        <v>16569166.51590542</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10">
       <c r="B120" t="s">
         <v>133</v>
       </c>
@@ -4608,10 +4577,10 @@
         <v>390</v>
       </c>
       <c r="J120">
-        <v>28687283.213700362</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+        <v>28687283.21370036</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10">
       <c r="B121" t="s">
         <v>132</v>
       </c>
@@ -4631,10 +4600,10 @@
         <v>388</v>
       </c>
       <c r="J121">
-        <v>1464485.5013698239</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1464485.501369824</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="B122" t="s">
         <v>138</v>
       </c>
@@ -4651,10 +4620,10 @@
         <v>307</v>
       </c>
       <c r="J122">
-        <v>517003.99124031531</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+        <v>517003.9912403153</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
       <c r="B123" t="s">
         <v>140</v>
       </c>
@@ -4671,10 +4640,10 @@
         <v>359</v>
       </c>
       <c r="J123">
-        <v>12209539.644512771</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+        <v>12209539.64451277</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="B124" t="s">
         <v>134</v>
       </c>
@@ -4694,10 +4663,10 @@
         <v>399</v>
       </c>
       <c r="J124">
-        <v>2677182.1768148541</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+        <v>2677182.176814854</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10">
       <c r="B125" t="s">
         <v>127</v>
       </c>
@@ -4714,10 +4683,10 @@
         <v>323</v>
       </c>
       <c r="J125">
-        <v>10340795.840703109</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+        <v>10340795.84070311</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
       <c r="B126" t="s">
         <v>137</v>
       </c>
@@ -4737,7 +4706,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10">
       <c r="B127" t="s">
         <v>135</v>
       </c>
@@ -4754,10 +4723,10 @@
         <v>346</v>
       </c>
       <c r="J127">
-        <v>1991939.8996735071</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+        <v>1991939.899673507</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10">
       <c r="B128" t="s">
         <v>139</v>
       </c>
@@ -4780,7 +4749,7 @@
         <v>6013477.558832759</v>
       </c>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:10">
       <c r="B129" t="s">
         <v>126</v>
       </c>
@@ -4800,10 +4769,10 @@
         <v>400</v>
       </c>
       <c r="J129">
-        <v>3104130.8525155862</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
+        <v>3104130.852515586</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10">
       <c r="B130" t="s">
         <v>136</v>
       </c>
@@ -4820,10 +4789,10 @@
         <v>347</v>
       </c>
       <c r="J130">
-        <v>6630997.3292599991</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
+        <v>6630997.329259999</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10">
       <c r="B131" t="s">
         <v>130</v>
       </c>
@@ -4843,10 +4812,10 @@
         <v>370</v>
       </c>
       <c r="J131">
-        <v>33380023.309566759</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
+        <v>33380023.30956676</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10">
       <c r="B132" t="s">
         <v>129</v>
       </c>
@@ -4866,15 +4835,10 @@
         <v>379</v>
       </c>
       <c r="J132">
-        <v>11427963.857514391</v>
+        <v>11427963.85751439</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J132">
-      <sortCondition ref="C1"/>
-    </sortState>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/MetalliCan/pre_cleaned_data/land_df.xlsx
+++ b/data/MetalliCan/pre_cleaned_data/land_df.xlsx
@@ -1,15 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/pre_cleaned_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_07A142F131A30F3E4B2C4CE9ED6824D578788327" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E7E4B9-A0FA-4DB7-8B83-AFBA39118E0E}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$132</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1222,8 +1244,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1286,13 +1308,25 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1330,7 +1364,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1364,6 +1398,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1398,9 +1433,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1573,11 +1609,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J132"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="211" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1609,7 +1658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1632,10 +1681,10 @@
         <v>365</v>
       </c>
       <c r="J2">
-        <v>1499689.86541</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>1499689.8654100001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1655,7 +1704,7 @@
         <v>1396088.878773147</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1675,10 +1724,10 @@
         <v>306</v>
       </c>
       <c r="J4">
-        <v>7967834.63756</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>7967834.6375599997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1698,10 +1747,10 @@
         <v>307</v>
       </c>
       <c r="J5">
-        <v>416736.8603415595</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+        <v>416736.86034155951</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1724,10 +1773,10 @@
         <v>366</v>
       </c>
       <c r="J6">
-        <v>13233210.3886</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>13233210.388599999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1753,7 +1802,7 @@
         <v>22527998.6785</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1776,10 +1825,10 @@
         <v>368</v>
       </c>
       <c r="J8">
-        <v>11531646.5435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>11531646.543500001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1796,10 +1845,10 @@
         <v>310</v>
       </c>
       <c r="J9">
-        <v>7682504.761106032</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>7682504.7611060319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1825,7 +1874,7 @@
         <v>4950459.91493</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1842,10 +1891,10 @@
         <v>311</v>
       </c>
       <c r="J11">
-        <v>199723.4981077999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>199723.49810779991</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1865,10 +1914,10 @@
         <v>312</v>
       </c>
       <c r="J12">
-        <v>63924259.8049</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>63924259.804899998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1885,10 +1934,10 @@
         <v>308</v>
       </c>
       <c r="J13">
-        <v>5776459.429646255</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>5776459.4296462554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1908,7 +1957,7 @@
         <v>1931027.417599746</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1934,7 +1983,7 @@
         <v>12606786.4826</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1963,7 +2012,7 @@
         <v>330003.3338055482</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1980,10 +2029,10 @@
         <v>315</v>
       </c>
       <c r="J17">
-        <v>5670439.795488</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>5670439.7954879999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2003,10 +2052,10 @@
         <v>316</v>
       </c>
       <c r="J18">
-        <v>1058100.092748948</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>1058100.0927489479</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2038,7 +2087,7 @@
         <v>363438.296974</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2067,10 +2116,10 @@
         <v>372</v>
       </c>
       <c r="J20">
-        <v>2410689.221736038</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>2410689.2217360381</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -2090,10 +2139,10 @@
         <v>318</v>
       </c>
       <c r="J21">
-        <v>7481998.483051093</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>7481998.4830510933</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -2113,7 +2162,7 @@
         <v>772974.2536339435</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2130,10 +2179,10 @@
         <v>319</v>
       </c>
       <c r="J23">
-        <v>255208.969208</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>255208.96920799999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -2150,10 +2199,10 @@
         <v>320</v>
       </c>
       <c r="J24">
-        <v>86936203.29125148</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>86936203.291251481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -2176,10 +2225,10 @@
         <v>373</v>
       </c>
       <c r="J25">
-        <v>4789014.03756</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>4789014.0375600001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2202,7 +2251,7 @@
         <v>163254.62437129</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2222,10 +2271,10 @@
         <v>374</v>
       </c>
       <c r="J27">
-        <v>1152609.9603904</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>1152609.9603903999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2245,10 +2294,10 @@
         <v>323</v>
       </c>
       <c r="J28">
-        <v>10572188.5661376</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>10572188.566137601</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2268,10 +2317,10 @@
         <v>308</v>
       </c>
       <c r="J29">
-        <v>1510729.369309124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
+        <v>1510729.3693091241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2291,10 +2340,10 @@
         <v>315</v>
       </c>
       <c r="J30">
-        <v>681889.9964301857</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>681889.99643018574</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2314,10 +2363,10 @@
         <v>323</v>
       </c>
       <c r="J31">
-        <v>26104648.81795129</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>26104648.817951292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2343,10 +2392,10 @@
         <v>323</v>
       </c>
       <c r="J32">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2369,7 +2418,7 @@
         <v>4354811.166996506</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2392,10 +2441,10 @@
         <v>375</v>
       </c>
       <c r="J34">
-        <v>3064668.693174671</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>3064668.6931746709</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2415,10 +2464,10 @@
         <v>324</v>
       </c>
       <c r="J35">
-        <v>9992991.568656314</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>9992991.5686563142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2444,7 +2493,7 @@
         <v>16826817.56129609</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2467,10 +2516,10 @@
         <v>375</v>
       </c>
       <c r="J37">
-        <v>126962.7450922684</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
+        <v>126962.74509226839</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2487,10 +2536,10 @@
         <v>325</v>
       </c>
       <c r="J38">
-        <v>771997.9267729169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>771997.92677291692</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2507,10 +2556,10 @@
         <v>326</v>
       </c>
       <c r="J39">
-        <v>2695956.210741678</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>2695956.2107416778</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2539,10 +2588,10 @@
         <v>377</v>
       </c>
       <c r="J40">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -2565,10 +2614,10 @@
         <v>375</v>
       </c>
       <c r="J41">
-        <v>22789723.43693621</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
+        <v>22789723.436936211</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -2591,10 +2640,10 @@
         <v>378</v>
       </c>
       <c r="J42">
-        <v>5804864.894492002</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
+        <v>5804864.8944920022</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -2626,7 +2675,7 @@
         <v>1760913.595839669</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -2655,10 +2704,10 @@
         <v>370</v>
       </c>
       <c r="J44">
-        <v>559241.2641449785</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
+        <v>559241.26414497849</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -2675,10 +2724,10 @@
         <v>330</v>
       </c>
       <c r="J45">
-        <v>2821612.246080229</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
+        <v>2821612.2460802291</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -2695,10 +2744,10 @@
         <v>331</v>
       </c>
       <c r="J46">
-        <v>2460432.820685903</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
+        <v>2460432.8206859031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2721,7 +2770,7 @@
         <v>3512631.992361845</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -2741,7 +2790,7 @@
         <v>367462.345355</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -2767,10 +2816,10 @@
         <v>333</v>
       </c>
       <c r="J49">
-        <v>6838840.246701591</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
+        <v>6838840.2467015907</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -2796,10 +2845,10 @@
         <v>334</v>
       </c>
       <c r="J50">
-        <v>2161806.090909503</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
+        <v>2161806.0909095029</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -2819,7 +2868,7 @@
         <v>124954.6686331536</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -2842,10 +2891,10 @@
         <v>380</v>
       </c>
       <c r="J52">
-        <v>7405086.228542091</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10">
+        <v>7405086.2285420913</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>61</v>
       </c>
@@ -2871,10 +2920,10 @@
         <v>334</v>
       </c>
       <c r="J53">
-        <v>1929968.176370687</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10">
+        <v>1929968.1763706871</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -2906,7 +2955,7 @@
         <v>15428020.65126922</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -2923,10 +2972,10 @@
         <v>336</v>
       </c>
       <c r="J55">
-        <v>515060.9564426438</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
+        <v>515060.95644264377</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -2952,10 +3001,10 @@
         <v>337</v>
       </c>
       <c r="J56">
-        <v>3963061.644481355</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10">
+        <v>3963061.6444813549</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>65</v>
       </c>
@@ -2972,10 +3021,10 @@
         <v>338</v>
       </c>
       <c r="J57">
-        <v>788132.0847764658</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10">
+        <v>788132.08477646578</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>66</v>
       </c>
@@ -3001,10 +3050,10 @@
         <v>334</v>
       </c>
       <c r="J58">
-        <v>110803.8657774448</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10">
+        <v>110803.86577744479</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -3027,10 +3076,10 @@
         <v>382</v>
       </c>
       <c r="J59">
-        <v>3503071.061728495</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10">
+        <v>3503071.0617284952</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>68</v>
       </c>
@@ -3050,10 +3099,10 @@
         <v>339</v>
       </c>
       <c r="J60">
-        <v>989146.0724139999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10">
+        <v>989146.07241399994</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -3079,7 +3128,7 @@
         <v>1874190.45757726</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>70</v>
       </c>
@@ -3102,10 +3151,10 @@
         <v>384</v>
       </c>
       <c r="J62">
-        <v>6139378.49533</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10">
+        <v>6139378.4953300003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>71</v>
       </c>
@@ -3131,10 +3180,10 @@
         <v>307</v>
       </c>
       <c r="J63">
-        <v>1141145.864636208</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10">
+        <v>1141145.8646362079</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>72</v>
       </c>
@@ -3154,10 +3203,10 @@
         <v>327</v>
       </c>
       <c r="J64">
-        <v>240468.7055894923</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
+        <v>240468.70558949231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>73</v>
       </c>
@@ -3177,7 +3226,7 @@
         <v>242518.965983</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -3200,10 +3249,10 @@
         <v>385</v>
       </c>
       <c r="J66">
-        <v>8409093.12659</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10">
+        <v>8409093.1265900005</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>75</v>
       </c>
@@ -3226,10 +3275,10 @@
         <v>386</v>
       </c>
       <c r="J67">
-        <v>10276967.10066929</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10">
+        <v>10276967.100669291</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -3246,10 +3295,10 @@
         <v>342</v>
       </c>
       <c r="J68">
-        <v>386230.806039</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10">
+        <v>386230.80603899999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>77</v>
       </c>
@@ -3272,10 +3321,10 @@
         <v>387</v>
       </c>
       <c r="J69">
-        <v>948677.9026767507</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10">
+        <v>948677.90267675067</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>78</v>
       </c>
@@ -3298,10 +3347,10 @@
         <v>386</v>
       </c>
       <c r="J70">
-        <v>352884.5737495346</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
+        <v>352884.57374953461</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>79</v>
       </c>
@@ -3327,10 +3376,10 @@
         <v>334</v>
       </c>
       <c r="J71">
-        <v>3063892.805082795</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
+        <v>3063892.8050827952</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>80</v>
       </c>
@@ -3362,7 +3411,7 @@
         <v>1039802.195699128</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -3391,7 +3440,7 @@
         <v>21591249.4628</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -3420,10 +3469,10 @@
         <v>388</v>
       </c>
       <c r="J74">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>83</v>
       </c>
@@ -3446,10 +3495,10 @@
         <v>389</v>
       </c>
       <c r="J75">
-        <v>4202253.5386</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10">
+        <v>4202253.5385999996</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -3475,10 +3524,10 @@
         <v>344</v>
       </c>
       <c r="J76">
-        <v>1788407.819274</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10">
+        <v>1788407.8192739999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>85</v>
       </c>
@@ -3504,7 +3553,7 @@
         <v>1550354.452950391</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>86</v>
       </c>
@@ -3530,7 +3579,7 @@
         <v>7249147.17667</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -3559,10 +3608,10 @@
         <v>390</v>
       </c>
       <c r="J79">
-        <v>24972920.13211028</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10">
+        <v>24972920.132110279</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>88</v>
       </c>
@@ -3582,10 +3631,10 @@
         <v>323</v>
       </c>
       <c r="J80">
-        <v>15702687.60491092</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10">
+        <v>15702687.604910919</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>89</v>
       </c>
@@ -3608,10 +3657,10 @@
         <v>345</v>
       </c>
       <c r="J81">
-        <v>346083.4630491536</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10">
+        <v>346083.46304915362</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>90</v>
       </c>
@@ -3637,10 +3686,10 @@
         <v>346</v>
       </c>
       <c r="J82">
-        <v>1250800.940065123</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10">
+        <v>1250800.9400651229</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>91</v>
       </c>
@@ -3666,7 +3715,7 @@
         <v>280723.3006520429</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -3692,10 +3741,10 @@
         <v>347</v>
       </c>
       <c r="J84">
-        <v>6630997.329259999</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10">
+        <v>6630997.3292599991</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>93</v>
       </c>
@@ -3724,7 +3773,7 @@
         <v>3714363.081590083</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>94</v>
       </c>
@@ -3741,10 +3790,10 @@
         <v>348</v>
       </c>
       <c r="J86">
-        <v>1267949.17795359</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10">
+        <v>1267949.1779535899</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>95</v>
       </c>
@@ -3761,10 +3810,10 @@
         <v>349</v>
       </c>
       <c r="J87">
-        <v>848008.505874</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10">
+        <v>848008.50587400002</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>96</v>
       </c>
@@ -3784,7 +3833,7 @@
         <v>148601.7043568496</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>97</v>
       </c>
@@ -3807,10 +3856,10 @@
         <v>368</v>
       </c>
       <c r="J89">
-        <v>1445491.925339854</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10">
+        <v>1445491.9253398541</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>98</v>
       </c>
@@ -3836,10 +3885,10 @@
         <v>346</v>
       </c>
       <c r="J90">
-        <v>741138.9596083837</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10">
+        <v>741138.95960838371</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -3868,7 +3917,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>100</v>
       </c>
@@ -3885,10 +3934,10 @@
         <v>352</v>
       </c>
       <c r="J92">
-        <v>899806.3255054827</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10">
+        <v>899806.32550548273</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>101</v>
       </c>
@@ -3911,10 +3960,10 @@
         <v>392</v>
       </c>
       <c r="J93">
-        <v>3436361.112865424</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10">
+        <v>3436361.1128654238</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>102</v>
       </c>
@@ -3937,10 +3986,10 @@
         <v>390</v>
       </c>
       <c r="J94">
-        <v>2323252.926769045</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10">
+        <v>2323252.9267690452</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>103</v>
       </c>
@@ -3963,10 +4012,10 @@
         <v>393</v>
       </c>
       <c r="J95">
-        <v>2475749.772500532</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10">
+        <v>2475749.7725005322</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -3983,10 +4032,10 @@
         <v>306</v>
       </c>
       <c r="J96">
-        <v>9487628.08633</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10">
+        <v>9487628.0863300003</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>105</v>
       </c>
@@ -4003,10 +4052,10 @@
         <v>355</v>
       </c>
       <c r="J97">
-        <v>333307.1237192919</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10">
+        <v>333307.12371929188</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>106</v>
       </c>
@@ -4029,10 +4078,10 @@
         <v>394</v>
       </c>
       <c r="J98">
-        <v>6202897.01714</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10">
+        <v>6202897.0171400001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -4058,7 +4107,7 @@
         <v>1341835.17078</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>108</v>
       </c>
@@ -4081,10 +4130,10 @@
         <v>396</v>
       </c>
       <c r="J100">
-        <v>1113516.59973</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10">
+        <v>1113516.5997299999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>109</v>
       </c>
@@ -4104,10 +4153,10 @@
         <v>345</v>
       </c>
       <c r="J101">
-        <v>2689687.063009932</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10">
+        <v>2689687.0630099322</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>110</v>
       </c>
@@ -4127,10 +4176,10 @@
         <v>356</v>
       </c>
       <c r="J102">
-        <v>1248584.67151726</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10">
+        <v>1248584.6715172599</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>111</v>
       </c>
@@ -4153,10 +4202,10 @@
         <v>397</v>
       </c>
       <c r="J103">
-        <v>5574423.981285</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
+        <v>5574423.9812850002</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>112</v>
       </c>
@@ -4179,10 +4228,10 @@
         <v>398</v>
       </c>
       <c r="J104">
-        <v>19028718.4515658</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10">
+        <v>19028718.451565798</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>113</v>
       </c>
@@ -4211,10 +4260,10 @@
         <v>399</v>
       </c>
       <c r="J105">
-        <v>2331098.7137657</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10">
+        <v>2331098.7137656999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -4231,10 +4280,10 @@
         <v>313</v>
       </c>
       <c r="J106">
-        <v>6417855.902150526</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10">
+        <v>6417855.9021505257</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>115</v>
       </c>
@@ -4257,7 +4306,7 @@
         <v>11904079.93924279</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>116</v>
       </c>
@@ -4283,10 +4332,10 @@
         <v>307</v>
       </c>
       <c r="J108">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>117</v>
       </c>
@@ -4306,7 +4355,7 @@
         <v>189687.8885015327</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>118</v>
       </c>
@@ -4332,10 +4381,10 @@
         <v>359</v>
       </c>
       <c r="J110">
-        <v>4412887.439581322</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10">
+        <v>4412887.4395813216</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>119</v>
       </c>
@@ -4352,10 +4401,10 @@
         <v>360</v>
       </c>
       <c r="J111">
-        <v>708761.4147057816</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10">
+        <v>708761.41470578162</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>120</v>
       </c>
@@ -4387,7 +4436,7 @@
         <v>1600590.119251437</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>121</v>
       </c>
@@ -4404,10 +4453,10 @@
         <v>359</v>
       </c>
       <c r="J113">
-        <v>4345046.953741541</v>
-      </c>
-    </row>
-    <row r="114" spans="1:10">
+        <v>4345046.9537415411</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>122</v>
       </c>
@@ -4436,7 +4485,7 @@
         <v>10235647.18904726</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>123</v>
       </c>
@@ -4462,10 +4511,10 @@
         <v>359</v>
       </c>
       <c r="J115">
-        <v>1973892.455465505</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10">
+        <v>1973892.4554655049</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>124</v>
       </c>
@@ -4488,7 +4537,7 @@
         <v>5293594.021862885</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>125</v>
       </c>
@@ -4511,7 +4560,7 @@
         <v>3418676.16080696</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>128</v>
       </c>
@@ -4531,10 +4580,10 @@
         <v>377</v>
       </c>
       <c r="J118">
-        <v>7644288.851632554</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10">
+        <v>7644288.8516325541</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>131</v>
       </c>
@@ -4554,10 +4603,10 @@
         <v>381</v>
       </c>
       <c r="J119">
-        <v>16569166.51590542</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10">
+        <v>16569166.515905419</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>133</v>
       </c>
@@ -4577,10 +4626,10 @@
         <v>390</v>
       </c>
       <c r="J120">
-        <v>28687283.21370036</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10">
+        <v>28687283.213700362</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>132</v>
       </c>
@@ -4600,10 +4649,10 @@
         <v>388</v>
       </c>
       <c r="J121">
-        <v>1464485.501369824</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10">
+        <v>1464485.5013698239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>138</v>
       </c>
@@ -4620,10 +4669,10 @@
         <v>307</v>
       </c>
       <c r="J122">
-        <v>517003.9912403153</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10">
+        <v>517003.99124031531</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>140</v>
       </c>
@@ -4640,10 +4689,10 @@
         <v>359</v>
       </c>
       <c r="J123">
-        <v>12209539.64451277</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10">
+        <v>12209539.644512771</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>134</v>
       </c>
@@ -4663,10 +4712,10 @@
         <v>399</v>
       </c>
       <c r="J124">
-        <v>2677182.176814854</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10">
+        <v>2677182.1768148541</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>127</v>
       </c>
@@ -4683,10 +4732,10 @@
         <v>323</v>
       </c>
       <c r="J125">
-        <v>10340795.84070311</v>
-      </c>
-    </row>
-    <row r="126" spans="1:10">
+        <v>10340795.840703109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>137</v>
       </c>
@@ -4706,7 +4755,7 @@
         <v>1113481.921945367</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>135</v>
       </c>
@@ -4723,10 +4772,10 @@
         <v>346</v>
       </c>
       <c r="J127">
-        <v>1991939.899673507</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10">
+        <v>1991939.8996735071</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>139</v>
       </c>
@@ -4749,7 +4798,7 @@
         <v>6013477.558832759</v>
       </c>
     </row>
-    <row r="129" spans="2:10">
+    <row r="129" spans="2:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>126</v>
       </c>
@@ -4769,10 +4818,10 @@
         <v>400</v>
       </c>
       <c r="J129">
-        <v>3104130.852515586</v>
-      </c>
-    </row>
-    <row r="130" spans="2:10">
+        <v>3104130.8525155862</v>
+      </c>
+    </row>
+    <row r="130" spans="2:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>136</v>
       </c>
@@ -4789,10 +4838,10 @@
         <v>347</v>
       </c>
       <c r="J130">
-        <v>6630997.329259999</v>
-      </c>
-    </row>
-    <row r="131" spans="2:10">
+        <v>6630997.3292599991</v>
+      </c>
+    </row>
+    <row r="131" spans="2:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>130</v>
       </c>
@@ -4812,10 +4861,10 @@
         <v>370</v>
       </c>
       <c r="J131">
-        <v>33380023.30956676</v>
-      </c>
-    </row>
-    <row r="132" spans="2:10">
+        <v>33380023.309566759</v>
+      </c>
+    </row>
+    <row r="132" spans="2:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>129</v>
       </c>
@@ -4835,10 +4884,19 @@
         <v>379</v>
       </c>
       <c r="J132">
-        <v>11427963.85751439</v>
+        <v>11427963.857514391</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J132" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Copper Mountain"/>
+        <filter val="Mount Milligan"/>
+        <filter val="Mount Polley"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>